--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -37,10 +37,10 @@
     <t>U. x Caja</t>
   </si>
   <si>
-    <t>Stock VES</t>
-  </si>
-  <si>
-    <t>Alerta</t>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Estado</t>
   </si>
   <si>
     <t>2210</t>
@@ -52,7 +52,7 @@
     <t>FORRO N VINIFAN OFICIO CRISTAL 26</t>
   </si>
   <si>
-    <t>🟢</t>
+    <t>✓ OK</t>
   </si>
   <si>
     <t>2211</t>
@@ -73,7 +73,7 @@
     <t>FORRO N VINIFANCITO CRISTAL 26</t>
   </si>
   <si>
-    <t>🔴</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>2182</t>
@@ -136,7 +136,7 @@
     <t>PORTAPAPELES VINIFAN OFICIO X 10 UND - 2013</t>
   </si>
   <si>
-    <t>🟡</t>
+    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>78455</t>
@@ -4223,7 +4223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -4237,6 +4237,22 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4279,7 +4295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4287,13 +4303,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4638,13 +4660,12 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4758,7 +4779,7 @@
       <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4981,13 +5002,12 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5216,7 +5236,7 @@
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5538,7 +5558,7 @@
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5561,7 +5581,7 @@
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5607,7 +5627,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5676,7 +5696,7 @@
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5715,13 +5735,12 @@
   <dimension ref="A1:G266"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5763,10 +5782,10 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5809,10 +5828,10 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>2</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5901,10 +5920,10 @@
       <c r="E8">
         <v>50</v>
       </c>
-      <c r="F8" s="5">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="6">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6177,10 +6196,10 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="6">
         <v>6</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6571,7 +6590,7 @@
       <c r="F37" s="4">
         <v>0</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6683,10 +6702,10 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="6">
         <v>9</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6709,7 +6728,7 @@
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7215,7 +7234,7 @@
       <c r="F65" s="4">
         <v>0</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7603,10 +7622,10 @@
       <c r="E82">
         <v>100</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="6">
         <v>9</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8040,10 +8059,10 @@
       <c r="E101">
         <v>120</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="6">
         <v>6</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8270,10 +8289,10 @@
       <c r="E111">
         <v>120</v>
       </c>
-      <c r="F111" s="5">
-        <v>8</v>
-      </c>
-      <c r="G111" s="3" t="s">
+      <c r="F111" s="6">
+        <v>8</v>
+      </c>
+      <c r="G111" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8365,7 +8384,7 @@
       <c r="F115" s="4">
         <v>0</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8385,10 +8404,10 @@
       <c r="E116">
         <v>24</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="6">
         <v>3</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8408,10 +8427,10 @@
       <c r="E117">
         <v>24</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="6">
         <v>1</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8618,7 +8637,7 @@
       <c r="F126" s="4">
         <v>0</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="G126" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8779,7 +8798,7 @@
       <c r="F133" s="4">
         <v>0</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G133" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8825,7 +8844,7 @@
       <c r="F135" s="4">
         <v>0</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8871,7 +8890,7 @@
       <c r="F137" s="4">
         <v>0</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G137" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8894,7 +8913,7 @@
       <c r="F138" s="4">
         <v>0</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G138" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8986,7 +9005,7 @@
       <c r="F142" s="4">
         <v>0</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9006,10 +9025,10 @@
       <c r="E143">
         <v>24</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="6">
         <v>3</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="G143" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9032,7 +9051,7 @@
       <c r="F144" s="4">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9075,10 +9094,10 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="5">
+      <c r="F146" s="6">
         <v>5</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G146" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9098,10 +9117,10 @@
       <c r="E147">
         <v>24</v>
       </c>
-      <c r="F147" s="5">
+      <c r="F147" s="6">
         <v>4</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="G147" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9400,7 +9419,7 @@
       <c r="F160" s="4">
         <v>0</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9535,10 +9554,10 @@
       <c r="E166">
         <v>24</v>
       </c>
-      <c r="F166" s="5">
+      <c r="F166" s="6">
         <v>1</v>
       </c>
-      <c r="G166" s="3" t="s">
+      <c r="G166" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9627,10 +9646,10 @@
       <c r="E170">
         <v>36</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170" s="6">
         <v>3</v>
       </c>
-      <c r="G170" s="3" t="s">
+      <c r="G170" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9653,7 +9672,7 @@
       <c r="F171" s="4">
         <v>0</v>
       </c>
-      <c r="G171" s="3" t="s">
+      <c r="G171" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9676,7 +9695,7 @@
       <c r="F172" s="4">
         <v>0</v>
       </c>
-      <c r="G172" s="3" t="s">
+      <c r="G172" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9745,7 +9764,7 @@
       <c r="F175" s="4">
         <v>0</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G175" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9860,7 +9879,7 @@
       <c r="F180" s="4">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9883,7 +9902,7 @@
       <c r="F181" s="4">
         <v>0</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10113,7 +10132,7 @@
       <c r="F191" s="4">
         <v>0</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="G191" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10136,7 +10155,7 @@
       <c r="F192" s="4">
         <v>0</v>
       </c>
-      <c r="G192" s="3" t="s">
+      <c r="G192" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10228,7 +10247,7 @@
       <c r="F196" s="4">
         <v>0</v>
       </c>
-      <c r="G196" s="3" t="s">
+      <c r="G196" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10251,7 +10270,7 @@
       <c r="F197" s="4">
         <v>0</v>
       </c>
-      <c r="G197" s="3" t="s">
+      <c r="G197" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10550,7 +10569,7 @@
       <c r="F210" s="4">
         <v>0</v>
       </c>
-      <c r="G210" s="3" t="s">
+      <c r="G210" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10754,10 +10773,10 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="5">
+      <c r="F219" s="6">
         <v>1</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G219" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -10780,7 +10799,7 @@
       <c r="F220" s="4">
         <v>0</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="G220" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10964,7 +10983,7 @@
       <c r="F228" s="4">
         <v>0</v>
       </c>
-      <c r="G228" s="3" t="s">
+      <c r="G228" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11033,7 +11052,7 @@
       <c r="F231" s="4">
         <v>0</v>
       </c>
-      <c r="G231" s="3" t="s">
+      <c r="G231" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11283,10 +11302,10 @@
       <c r="E242">
         <v>5</v>
       </c>
-      <c r="F242" s="5">
+      <c r="F242" s="6">
         <v>1</v>
       </c>
-      <c r="G242" s="3" t="s">
+      <c r="G242" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -11355,7 +11374,7 @@
       <c r="F245" s="4">
         <v>0</v>
       </c>
-      <c r="G245" s="3" t="s">
+      <c r="G245" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11444,10 +11463,10 @@
       <c r="E249">
         <v>5</v>
       </c>
-      <c r="F249" s="5">
+      <c r="F249" s="6">
         <v>1</v>
       </c>
-      <c r="G249" s="3" t="s">
+      <c r="G249" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -11516,7 +11535,7 @@
       <c r="F252" s="4">
         <v>0</v>
       </c>
-      <c r="G252" s="3" t="s">
+      <c r="G252" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11539,7 +11558,7 @@
       <c r="F253" s="4">
         <v>0</v>
       </c>
-      <c r="G253" s="3" t="s">
+      <c r="G253" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11854,13 +11873,12 @@
   <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11928,7 +11946,7 @@
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11951,7 +11969,7 @@
       <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12066,7 +12084,7 @@
       <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12319,7 +12337,7 @@
       <c r="F20" s="4">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12342,7 +12360,7 @@
       <c r="F21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12848,7 +12866,7 @@
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13259,10 +13277,10 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="6">
         <v>1</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13285,7 +13303,7 @@
       <c r="F62" s="4">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13305,10 +13323,10 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="6">
         <v>4</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13328,10 +13346,10 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="6">
         <v>9</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13351,10 +13369,10 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="6">
         <v>3</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13400,7 +13418,7 @@
       <c r="F67" s="4">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13423,7 +13441,7 @@
       <c r="F68" s="4">
         <v>0</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13446,7 +13464,7 @@
       <c r="F69" s="4">
         <v>0</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13469,7 +13487,7 @@
       <c r="F70" s="4">
         <v>0</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13492,7 +13510,7 @@
       <c r="F71" s="4">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13646,13 +13664,12 @@
   <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -14177,10 +14194,10 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="6">
         <v>3</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -14430,10 +14447,10 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="6">
         <v>6</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -14660,10 +14677,10 @@
       <c r="E44">
         <v>72</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="6">
         <v>2</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15054,7 +15071,7 @@
       <c r="F61" s="4">
         <v>0</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15120,10 +15137,10 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="6">
         <v>5</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15304,10 +15321,10 @@
       <c r="E72">
         <v>200</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="6">
         <v>5</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15330,7 +15347,7 @@
       <c r="F73" s="4">
         <v>0</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15376,7 +15393,7 @@
       <c r="F75" s="4">
         <v>0</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15422,7 +15439,7 @@
       <c r="F77" s="4">
         <v>0</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15445,7 +15462,7 @@
       <c r="F78" s="4">
         <v>0</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15488,10 +15505,10 @@
       <c r="E80">
         <v>200</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="6">
         <v>3</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15514,7 +15531,7 @@
       <c r="F81" s="4">
         <v>0</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15580,10 +15597,10 @@
       <c r="E84">
         <v>1152</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="6">
         <v>7</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15741,10 +15758,10 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="6">
         <v>3</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15810,10 +15827,10 @@
       <c r="E94">
         <v>576</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="6">
         <v>4</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15836,7 +15853,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15928,7 +15945,7 @@
       <c r="F99" s="4">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15971,10 +15988,10 @@
       <c r="E101">
         <v>144</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="6">
         <v>2</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -16089,7 +16106,7 @@
       <c r="F106" s="4">
         <v>0</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="G106" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -16388,7 +16405,7 @@
       <c r="F119" s="4">
         <v>0</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -16979,13 +16996,12 @@
   <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -17030,7 +17046,7 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17145,7 +17161,7 @@
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17283,7 +17299,7 @@
       <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17329,7 +17345,7 @@
       <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17349,10 +17365,10 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <v>3</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -17375,7 +17391,7 @@
       <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17398,7 +17414,7 @@
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17605,7 +17621,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17720,7 +17736,7 @@
       <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18226,7 +18242,7 @@
       <c r="F54" s="4">
         <v>0</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18249,7 +18265,7 @@
       <c r="F55" s="4">
         <v>0</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18295,7 +18311,7 @@
       <c r="F57" s="4">
         <v>0</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18318,7 +18334,7 @@
       <c r="F58" s="4">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18410,7 +18426,7 @@
       <c r="F62" s="4">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18476,10 +18492,10 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="6">
         <v>5</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -18545,10 +18561,10 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="6">
         <v>4</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -18617,7 +18633,7 @@
       <c r="F71" s="4">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18640,7 +18656,7 @@
       <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18729,10 +18745,10 @@
       <c r="E76">
         <v>180</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="6">
         <v>4</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -18824,7 +18840,7 @@
       <c r="F80" s="4">
         <v>0</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18939,7 +18955,7 @@
       <c r="F85" s="4">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -19097,10 +19113,10 @@
       <c r="E92">
         <v>144</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="6">
         <v>4</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -19143,10 +19159,10 @@
       <c r="E94">
         <v>144</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="6">
         <v>3</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -19169,7 +19185,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -19208,13 +19224,12 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -19344,13 +19359,12 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -20082,10 +20096,10 @@
       <c r="E32">
         <v>48</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="6">
         <v>2</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20101,13 +20115,12 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -20333,10 +20346,10 @@
       <c r="E10">
         <v>36</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <v>2</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20359,7 +20372,7 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20494,10 +20507,10 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <v>1</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20586,10 +20599,10 @@
       <c r="E21">
         <v>144</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <v>6</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20628,13 +20641,12 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -20863,7 +20875,7 @@
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20886,7 +20898,7 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20929,10 +20941,10 @@
       <c r="E13">
         <v>500</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="7" t="s">
         <v>38</v>
       </c>
     </row>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7518,11 +7518,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <v>1775</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>49</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -8044,11 +8044,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>471</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8067,11 +8067,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>445</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>49</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8964,11 +8964,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="2">
         <v>751</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>49</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -9102,11 +9102,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="2">
         <v>645</v>
       </c>
-      <c r="G60" s="7" t="s">
-        <v>49</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -9838,11 +9838,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="2">
         <v>940</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>49</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -10344,11 +10344,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="2">
         <v>137</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>49</v>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -10942,11 +10942,11 @@
       <c r="E140">
         <v>30</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="2">
         <v>297</v>
       </c>
-      <c r="G140" s="7" t="s">
-        <v>49</v>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -10965,11 +10965,11 @@
       <c r="E141">
         <v>30</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="2">
         <v>180</v>
       </c>
-      <c r="G141" s="7" t="s">
-        <v>49</v>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -11379,11 +11379,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="6">
+      <c r="F159" s="2">
         <v>130</v>
       </c>
-      <c r="G159" s="7" t="s">
-        <v>49</v>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11839,11 +11839,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="6">
+      <c r="F179" s="2">
         <v>218</v>
       </c>
-      <c r="G179" s="7" t="s">
-        <v>49</v>
+      <c r="G179" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -12299,11 +12299,11 @@
       <c r="E199">
         <v>10</v>
       </c>
-      <c r="F199" s="6">
+      <c r="F199" s="2">
         <v>69</v>
       </c>
-      <c r="G199" s="7" t="s">
-        <v>49</v>
+      <c r="G199" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -12506,11 +12506,11 @@
       <c r="E208">
         <v>720</v>
       </c>
-      <c r="F208" s="6">
+      <c r="F208" s="2">
         <v>5462</v>
       </c>
-      <c r="G208" s="7" t="s">
-        <v>49</v>
+      <c r="G208" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -12529,11 +12529,11 @@
       <c r="E209">
         <v>720</v>
       </c>
-      <c r="F209" s="6">
+      <c r="F209" s="2">
         <v>6036</v>
       </c>
-      <c r="G209" s="7" t="s">
-        <v>49</v>
+      <c r="G209" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -12598,11 +12598,11 @@
       <c r="E212">
         <v>720</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F212" s="2">
         <v>4603</v>
       </c>
-      <c r="G212" s="7" t="s">
-        <v>49</v>
+      <c r="G212" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -12644,11 +12644,11 @@
       <c r="E214">
         <v>720</v>
       </c>
-      <c r="F214" s="6">
+      <c r="F214" s="2">
         <v>3947</v>
       </c>
-      <c r="G214" s="7" t="s">
-        <v>49</v>
+      <c r="G214" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -13817,11 +13817,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="6">
+      <c r="F265" s="2">
         <v>27</v>
       </c>
-      <c r="G265" s="7" t="s">
-        <v>49</v>
+      <c r="G265" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -13840,11 +13840,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="6">
+      <c r="F266" s="2">
         <v>26</v>
       </c>
-      <c r="G266" s="7" t="s">
-        <v>49</v>
+      <c r="G266" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -13998,11 +13998,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="2">
         <v>115</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -16157,11 +16157,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="2">
         <v>1033</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>49</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16410,11 +16410,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="2">
         <v>1001</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>49</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16548,11 +16548,11 @@
       <c r="E39">
         <v>144</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="2">
         <v>1014</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>49</v>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -16732,11 +16732,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="2">
         <v>1400</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>49</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -17284,11 +17284,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="2">
         <v>1246</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>49</v>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17468,11 +17468,11 @@
       <c r="E79">
         <v>200</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="2">
         <v>1865</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>49</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17652,11 +17652,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <v>4143</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>49</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17675,11 +17675,11 @@
       <c r="E88">
         <v>576</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="2">
         <v>5653</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>49</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17767,11 +17767,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="2">
         <v>5395</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>49</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -18181,11 +18181,11 @@
       <c r="E110">
         <v>192</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="2">
         <v>1359</v>
       </c>
-      <c r="G110" s="7" t="s">
-        <v>49</v>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -20777,11 +20777,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="2">
         <v>936</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>49</v>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20984,11 +20984,11 @@
       <c r="E87">
         <v>144</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <v>808</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>49</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -21944,11 +21944,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="2">
         <v>202</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>49</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -21967,11 +21967,11 @@
       <c r="E27">
         <v>24</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="2">
         <v>198</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>49</v>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -22950,11 +22950,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>1904</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22973,11 +22973,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>1063</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>49</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6786,7 +6786,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>3927</v>
+        <v>3627</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6924,7 +6924,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25578</v>
+        <v>25453</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14965,7 +14965,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49384</v>
+        <v>49096</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -19927,7 +19927,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7902</v>
+        <v>7758</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -21393,7 +21393,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21462,7 +21462,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>3927</v>
+        <v>3627</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25578</v>
+        <v>25453</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49384</v>
+        <v>49096</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7902</v>
+        <v>7758</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21463,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15579</v>
+        <v>15578</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>13509</v>
+        <v>13508</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>38451</v>
+        <v>38450</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>37794</v>
+        <v>37793</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7743</v>
+        <v>7742</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>16218</v>
+        <v>16216</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>40774</v>
+        <v>40773</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22998,7 +22998,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="2">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46870</v>
+        <v>46970</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>18563</v>
+        <v>17813</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3743</v>
+        <v>3643</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>5110</v>
+        <v>5010</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>3109</v>
+        <v>3009</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4475</v>
+        <v>4375</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="2">
-        <v>271</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="6">
+        <v>171</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>5117</v>
+        <v>5017</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8232</v>
+        <v>8132</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15719</v>
+        <v>15619</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>2347</v>
+        <v>2247</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>743</v>
+        <v>643</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15505</v>
+        <v>15289</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>53217</v>
+        <v>52785</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>12442</v>
+        <v>12202</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37693</v>
+        <v>37845</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>189582</v>
+        <v>190794</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -18965,7 +18965,7 @@
         <v>192</v>
       </c>
       <c r="F144" s="6">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>49</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7442</v>
+        <v>7394</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>4054</v>
+        <v>4006</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>10180</v>
+        <v>10132</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>15509</v>
+        <v>15461</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5656</v>
+        <v>5608</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>5151</v>
+        <v>5079</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6526</v>
+        <v>6454</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>6337</v>
+        <v>6289</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>120176</v>
+        <v>120032</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>215690</v>
+        <v>215642</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22564,7 +22564,7 @@
         <v>144</v>
       </c>
       <c r="F20" s="2">
-        <v>14675</v>
+        <v>16675</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>11065</v>
+        <v>10065</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>75638</v>
+        <v>73138</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>235977</v>
+        <v>230977</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>1627</v>
+        <v>1127</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>29604</v>
+        <v>28524</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25453</v>
+        <v>24203</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>128213</v>
+        <v>123213</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>15802</v>
+        <v>11802</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>10090</v>
+        <v>9770</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15289</v>
+        <v>14569</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>98101</v>
+        <v>95941</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>8011</v>
+        <v>6571</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>12202</v>
+        <v>10762</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>74607</v>
+        <v>73167</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>37793</v>
+        <v>37073</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -16158,11 +16158,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="2">
-        <v>1030</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="6">
+        <v>646</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16181,11 +16181,11 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>19</v>
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3510</v>
+        <v>3318</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>11901</v>
+        <v>11709</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190794</v>
+        <v>190506</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>8629</v>
+        <v>8557</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -19215,7 +19215,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>11508</v>
+        <v>11268</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>153771</v>
+        <v>139371</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>39992</v>
+        <v>39392</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19790,7 +19790,7 @@
         <v>120</v>
       </c>
       <c r="F35" s="6">
-        <v>568</v>
+        <v>88</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>27575</v>
+        <v>26375</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>10930</v>
+        <v>9730</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>101256</v>
+        <v>101016</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>16346</v>
+        <v>16226</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>2448</v>
+        <v>2088</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20848,7 +20848,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="6">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>49</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>215642</v>
+        <v>212042</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21486,7 +21486,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>721</v>
+        <v>553</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -21509,7 +21509,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="2">
-        <v>433</v>
+        <v>313</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -21670,7 +21670,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="2">
-        <v>486</v>
+        <v>342</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -21693,7 +21693,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>692</v>
+        <v>548</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -21762,7 +21762,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="2">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -21900,7 +21900,7 @@
         <v>24</v>
       </c>
       <c r="F24" s="2">
-        <v>616</v>
+        <v>472</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -21923,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2">
-        <v>427</v>
+        <v>235</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>37974</v>
+        <v>34134</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>92896</v>
+        <v>91168</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>91771</v>
+        <v>82171</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>11105</v>
+        <v>1505</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>15916</v>
+        <v>8716</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>40773</v>
+        <v>34773</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22998,7 +22998,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="2">
-        <v>2747</v>
+        <v>2347</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>73138</v>
+        <v>72138</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>230977</v>
+        <v>230477</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>82862</v>
+        <v>82312</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>1127</v>
+        <v>752</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83857</v>
+        <v>83713</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>28524</v>
+        <v>28416</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>24203</v>
+        <v>23578</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>11704</v>
+        <v>20254</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7539</v>
+        <v>7239</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3643</v>
+        <v>3543</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4375</v>
+        <v>4325</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8132</v>
+        <v>8032</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15619</v>
+        <v>15519</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>4321</v>
+        <v>4261</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -9334,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="2">
-        <v>5067</v>
+        <v>3567</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -11035,11 +11035,11 @@
       <c r="E144">
         <v>24</v>
       </c>
-      <c r="F144" s="4">
-        <v>0</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>19</v>
+      <c r="F144" s="6">
+        <v>17</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>543</v>
+        <v>2559</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>922</v>
+        <v>898</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>1843</v>
+        <v>1747</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11473,7 +11473,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="2">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -11496,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="2">
-        <v>996</v>
+        <v>948</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>104051</v>
+        <v>104049</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14569</v>
+        <v>14567</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32615</v>
+        <v>32613</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71458</v>
+        <v>71446</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>73167</v>
+        <v>73166</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="2">
-        <v>4930</v>
+        <v>4906</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>7447</v>
+        <v>7347</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19918</v>
+        <v>19868</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="2">
-        <v>4243</v>
+        <v>4231</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -17792,7 +17792,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="2">
-        <v>14255</v>
+        <v>14231</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190506</v>
+        <v>190504</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>25660</v>
+        <v>25656</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>139371</v>
+        <v>139363</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -20848,7 +20848,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>49</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21440,7 +21440,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21486,7 +21486,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>65701</v>
+        <v>65501</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>82171</v>
+        <v>82069</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>10065</v>
+        <v>9965</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>34773</v>
+        <v>34772</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>72138</v>
+        <v>71888</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>230477</v>
+        <v>229877</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>9975</v>
+        <v>7425</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>28416</v>
+        <v>28293</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>23578</v>
+        <v>23453</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>123213</v>
+        <v>123127</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>39569</v>
+        <v>39469</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>47755</v>
+        <v>47255</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>24084</v>
+        <v>23584</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7239</v>
+        <v>7139</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3543</v>
+        <v>3493</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13854</v>
+        <v>13754</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>5010</v>
+        <v>4960</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="2">
-        <v>295</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>5017</v>
+        <v>4892</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>2247</v>
+        <v>2197</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>643</v>
+        <v>593</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>9626</v>
+        <v>9625</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>7031</v>
+        <v>6981</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8736,7 +8736,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="2">
-        <v>3139</v>
+        <v>3339</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -8782,7 +8782,7 @@
         <v>100</v>
       </c>
       <c r="F46" s="2">
-        <v>4764</v>
+        <v>4664</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2713</v>
+        <v>2913</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>1189</v>
+        <v>1389</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8897,7 +8897,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="2">
-        <v>1192</v>
+        <v>1492</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>817</v>
+        <v>1017</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -9334,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="2">
-        <v>3567</v>
+        <v>1967</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>936</v>
+        <v>900</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="2">
-        <v>22562</v>
+        <v>22490</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>4260</v>
+        <v>4188</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -11611,7 +11611,7 @@
         <v>36</v>
       </c>
       <c r="F169" s="2">
-        <v>1404</v>
+        <v>1332</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>2283</v>
+        <v>2259</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>104049</v>
+        <v>103185</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14567</v>
+        <v>14495</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>73166</v>
+        <v>73106</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>9494</v>
+        <v>9488</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2">
-        <v>14861</v>
+        <v>14855</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3794</v>
+        <v>3746</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>7067</v>
+        <v>6779</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>139363</v>
+        <v>138643</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>48824</v>
+        <v>48704</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>26375</v>
+        <v>26255</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>9730</v>
+        <v>9490</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8923</v>
+        <v>8851</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20342,7 +20342,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="2">
-        <v>4550</v>
+        <v>4514</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -20365,7 +20365,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="2">
-        <v>3902</v>
+        <v>3866</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1764</v>
+        <v>1656</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -21032,7 +21032,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="2">
-        <v>6626</v>
+        <v>6578</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -21055,7 +21055,7 @@
         <v>144</v>
       </c>
       <c r="F90" s="2">
-        <v>18282</v>
+        <v>18222</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>32978</v>
+        <v>32954</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22768,7 +22768,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="6">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>49</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>752</v>
+        <v>502</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>28293</v>
+        <v>27933</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>123127</v>
+        <v>122627</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46970</v>
+        <v>46720</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20254</v>
+        <v>18254</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>25116</v>
+        <v>22716</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95941</v>
+        <v>95653</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>6571</v>
+        <v>6427</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>13508</v>
+        <v>13268</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -15768,7 +15768,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="6">
-        <v>1038</v>
+        <v>750</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>49</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>13300</v>
+        <v>12943</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14685</v>
+        <v>14589</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -19375,11 +19375,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>19</v>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -19398,11 +19398,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>19</v>
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7394</v>
+        <v>7250</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>82312</v>
+        <v>80312</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>7425</v>
+        <v>6425</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>69708</v>
+        <v>68748</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>27933</v>
+        <v>27213</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>23453</v>
+        <v>18203</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>122627</v>
+        <v>117627</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7175,7 +7175,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>10052</v>
+        <v>9956</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7198,7 +7198,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>2036</v>
+        <v>1940</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>39469</v>
+        <v>38969</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>2310</v>
+        <v>2094</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>14034</v>
+        <v>13746</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -7404,11 +7404,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="6">
-        <v>542</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>49</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>47255</v>
+        <v>45255</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>23584</v>
+        <v>22084</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7519,11 +7519,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="2">
-        <v>1775</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="F23" s="6">
+        <v>1175</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>3104</v>
+        <v>2864</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7704,7 +7704,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="2">
-        <v>1351</v>
+        <v>1251</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>18254</v>
+        <v>15754</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7139</v>
+        <v>6939</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13754</v>
+        <v>13654</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>3009</v>
+        <v>2859</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="6">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>49</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8032</v>
+        <v>7882</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15519</v>
+        <v>15119</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>2197</v>
+        <v>1897</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="2">
-        <v>550</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="6">
+        <v>100</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>593</v>
+        <v>493</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8736,7 +8736,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="2">
-        <v>3339</v>
+        <v>3289</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -8759,7 +8759,7 @@
         <v>100</v>
       </c>
       <c r="F45" s="2">
-        <v>2776</v>
+        <v>2726</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2913</v>
+        <v>2813</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>1389</v>
+        <v>1339</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8874,7 +8874,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="2">
-        <v>2223</v>
+        <v>2173</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>1017</v>
+        <v>917</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>43324</v>
+        <v>42324</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9564,7 +9564,7 @@
         <v>100</v>
       </c>
       <c r="F80" s="2">
-        <v>16423</v>
+        <v>15923</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -9587,7 +9587,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="2">
-        <v>10217</v>
+        <v>9717</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -9656,7 +9656,7 @@
         <v>100</v>
       </c>
       <c r="F84" s="2">
-        <v>3092</v>
+        <v>2592</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>2487</v>
+        <v>2247</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="2">
-        <v>1340</v>
+        <v>1100</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -10530,7 +10530,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="2">
-        <v>3713</v>
+        <v>3593</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>10</v>
@@ -10599,7 +10599,7 @@
         <v>24</v>
       </c>
       <c r="F125" s="2">
-        <v>595</v>
+        <v>475</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9834</v>
+        <v>9762</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -11380,11 +11380,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="2">
-        <v>130</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="6">
+        <v>34</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>898</v>
+        <v>778</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11473,7 +11473,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="2">
-        <v>562</v>
+        <v>490</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -11519,7 +11519,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="2">
-        <v>1246</v>
+        <v>1126</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -11703,7 +11703,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="2">
-        <v>1193</v>
+        <v>1121</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="F177" s="6">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>49</v>
@@ -11818,7 +11818,7 @@
         <v>48</v>
       </c>
       <c r="F178" s="2">
-        <v>520</v>
+        <v>424</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -11840,11 +11840,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="2">
-        <v>218</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>10</v>
+      <c r="F179" s="6">
+        <v>146</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -11910,7 +11910,7 @@
         <v>36</v>
       </c>
       <c r="F182" s="2">
-        <v>922</v>
+        <v>850</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>9770</v>
+        <v>9450</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1705</v>
+        <v>1695</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -13497,7 +13497,7 @@
         <v>40</v>
       </c>
       <c r="F251" s="2">
-        <v>4427</v>
+        <v>3227</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>141054</v>
+        <v>135054</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -13908,7 +13908,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>25237</v>
+        <v>24949</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>15523</v>
+        <v>14383</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="2">
-        <v>10060</v>
+        <v>9628</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>5063</v>
+        <v>4991</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>13268</v>
+        <v>12968</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>10762</v>
+        <v>9802</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32613</v>
+        <v>32313</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71446</v>
+        <v>71146</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49096</v>
+        <v>46936</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -15035,7 +15035,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="2">
-        <v>27538</v>
+        <v>23938</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -15883,7 +15883,7 @@
         <v>288</v>
       </c>
       <c r="F10" s="2">
-        <v>9360</v>
+        <v>9072</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>9345</v>
+        <v>9249</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>7647</v>
+        <v>7551</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16159,7 +16159,7 @@
         <v>192</v>
       </c>
       <c r="F22" s="6">
-        <v>646</v>
+        <v>454</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>49</v>
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3318</v>
+        <v>3222</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -16803,7 +16803,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>15140</v>
+        <v>14996</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14589</v>
+        <v>14109</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>9581</v>
+        <v>8581</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>60988</v>
+        <v>57988</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>61922</v>
+        <v>56162</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17654,7 +17654,7 @@
         <v>576</v>
       </c>
       <c r="F87" s="2">
-        <v>4143</v>
+        <v>2991</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11431</v>
+        <v>11181</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5385</v>
+        <v>5313</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19629,7 +19629,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="2">
-        <v>3655</v>
+        <v>3583</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>5310</v>
+        <v>5166</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>39392</v>
+        <v>38192</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>48704</v>
+        <v>47264</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19789,11 +19789,11 @@
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="F35" s="6">
-        <v>88</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>49</v>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>9490</v>
+        <v>7090</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>101016</v>
+        <v>100416</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>16226</v>
+        <v>15746</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>2088</v>
+        <v>888</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7250</v>
+        <v>6242</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>11077</v>
+        <v>10645</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>9827</v>
+        <v>9539</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>10489</v>
+        <v>10201</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10890</v>
+        <v>10602</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8851</v>
+        <v>8563</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>4006</v>
+        <v>3286</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>10132</v>
+        <v>9412</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>15461</v>
+        <v>15029</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5608</v>
+        <v>5176</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>5079</v>
+        <v>4215</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6454</v>
+        <v>5734</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>6289</v>
+        <v>6001</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -20226,11 +20226,11 @@
       <c r="E54">
         <v>144</v>
       </c>
-      <c r="F54" s="6">
-        <v>432</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>49</v>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>3245</v>
+        <v>3053</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>9041</v>
+        <v>8681</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="2">
-        <v>7340</v>
+        <v>6980</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>120032</v>
+        <v>119312</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>212042</v>
+        <v>207042</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1170</v>
+        <v>1146</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21463,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>857</v>
+        <v>737</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -21578,7 +21578,7 @@
         <v>48</v>
       </c>
       <c r="F10" s="2">
-        <v>2084</v>
+        <v>2036</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -21601,7 +21601,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="2">
-        <v>2119</v>
+        <v>2071</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -21624,7 +21624,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="2">
-        <v>2795</v>
+        <v>2747</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -21647,7 +21647,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="2">
-        <v>1630</v>
+        <v>1582</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -21808,7 +21808,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="2">
-        <v>1202</v>
+        <v>1154</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -21831,7 +21831,7 @@
         <v>24</v>
       </c>
       <c r="F21" s="2">
-        <v>1344</v>
+        <v>1296</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -21854,7 +21854,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="2">
-        <v>1112</v>
+        <v>1064</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -21877,7 +21877,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="2">
-        <v>1048</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -22061,7 +22061,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="2">
-        <v>613</v>
+        <v>553</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>65501</v>
+        <v>62141</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22242,7 +22242,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="2">
-        <v>94120</v>
+        <v>92200</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22265,7 +22265,7 @@
         <v>384</v>
       </c>
       <c r="F7" s="2">
-        <v>57680</v>
+        <v>56528</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>34134</v>
+        <v>30294</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>91168</v>
+        <v>90016</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>82069</v>
+        <v>79669</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>9965</v>
+        <v>6965</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>16723</v>
+        <v>16323</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>34772</v>
+        <v>33772</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22952,7 +22952,7 @@
         <v>200</v>
       </c>
       <c r="F14" s="2">
-        <v>1904</v>
+        <v>1504</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22997,11 +22997,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="2">
-        <v>2347</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="6">
+        <v>347</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>71888</v>
+        <v>71588</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>229877</v>
+        <v>229477</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68748</v>
+        <v>68700</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83713</v>
+        <v>83665</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>27213</v>
+        <v>27141</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>18203</v>
+        <v>18153</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>117627</v>
+        <v>117527</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>22084</v>
+        <v>21084</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2864</v>
+        <v>2840</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15754</v>
+        <v>15604</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6939</v>
+        <v>6914</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3493</v>
+        <v>3468</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13654</v>
+        <v>13629</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>4960</v>
+        <v>4935</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>2859</v>
+        <v>2834</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4325</v>
+        <v>4300</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="6">
-        <v>21</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>4892</v>
+        <v>4867</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7882</v>
+        <v>7857</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15119</v>
+        <v>15094</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1897</v>
+        <v>1872</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="6">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>49</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>41458</v>
+        <v>41408</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>42324</v>
+        <v>42274</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>43284</v>
+        <v>43234</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>22716</v>
+        <v>22476</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>211687</v>
+        <v>211487</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95653</v>
+        <v>95509</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32313</v>
+        <v>32301</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19868</v>
+        <v>19832</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3709</v>
+        <v>3703</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>47264</v>
+        <v>47204</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>26255</v>
+        <v>26195</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>7090</v>
+        <v>7030</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>6242</v>
+        <v>6170</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20365,7 +20365,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="2">
-        <v>3866</v>
+        <v>3830</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -21923,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79669</v>
+        <v>79549</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22676,7 +22676,7 @@
         <v>1000</v>
       </c>
       <c r="F2" s="6">
-        <v>3238</v>
+        <v>3088</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>49</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>6965</v>
+        <v>8815</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>16323</v>
+        <v>16273</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33772</v>
+        <v>33722</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>229477</v>
+        <v>226977</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>6425</v>
+        <v>5675</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>18153</v>
+        <v>15778</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3468</v>
+        <v>3168</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>19</v>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>22476</v>
+        <v>17391</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14495</v>
+        <v>14493</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95509</v>
+        <v>95221</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>4991</v>
+        <v>4989</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>18308</v>
+        <v>17948</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -15929,7 +15929,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>11851</v>
+        <v>11850</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6779</v>
+        <v>6491</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="2">
-        <v>4906</v>
+        <v>3046</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>7347</v>
+        <v>5657</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="2">
-        <v>33638</v>
+        <v>32678</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>8581</v>
+        <v>7171</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17285,11 +17285,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="2">
-        <v>1246</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="F71" s="6">
+        <v>966</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17768,11 +17768,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="2">
-        <v>4231</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="F92" s="6">
+        <v>2731</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11181</v>
+        <v>11081</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3513</v>
+        <v>3453</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>9539</v>
+        <v>9251</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>10201</v>
+        <v>9913</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10602</v>
+        <v>10314</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8563</v>
+        <v>8274</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -21147,7 +21147,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>49</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>207042</v>
+        <v>206682</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>34348</v>
+        <v>33580</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68700</v>
+        <v>68604</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>21084</v>
+        <v>18584</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6914</v>
+        <v>6864</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3168</v>
+        <v>3118</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13629</v>
+        <v>13579</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7857</v>
+        <v>7807</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>468</v>
+        <v>418</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>38116</v>
+        <v>37916</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>41408</v>
+        <v>41208</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9356,11 +9356,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="6">
-        <v>100</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>49</v>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,7 +10668,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="2">
-        <v>5534</v>
+        <v>5486</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -10691,7 +10691,7 @@
         <v>24</v>
       </c>
       <c r="F129" s="2">
-        <v>8160</v>
+        <v>8112</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -10714,7 +10714,7 @@
         <v>24</v>
       </c>
       <c r="F130" s="2">
-        <v>15659</v>
+        <v>15611</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9762</v>
+        <v>9714</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="2">
-        <v>917</v>
+        <v>857</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>10</v>
@@ -13060,7 +13060,7 @@
         <v>5</v>
       </c>
       <c r="F232" s="2">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>10</v>
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="2">
-        <v>72</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>10</v>
+      <c r="F234" s="6">
+        <v>22</v>
+      </c>
+      <c r="G234" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="F235" s="2">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>10</v>
@@ -13152,7 +13152,7 @@
         <v>5</v>
       </c>
       <c r="F236" s="2">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>10</v>
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="F237" s="2">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>10</v>
@@ -13198,7 +13198,7 @@
         <v>5</v>
       </c>
       <c r="F238" s="2">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>10</v>
@@ -13221,7 +13221,7 @@
         <v>5</v>
       </c>
       <c r="F239" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1695</v>
+        <v>1515</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="2">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>52785</v>
+        <v>52784</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95221</v>
+        <v>94973</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>12968</v>
+        <v>12967</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>51222</v>
+        <v>51102</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14943,7 +14943,7 @@
         <v>288</v>
       </c>
       <c r="F47" s="2">
-        <v>8672</v>
+        <v>8472</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -15311,7 +15311,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>49</v>
@@ -16021,7 +16021,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="2">
-        <v>9579</v>
+        <v>9479</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -16044,7 +16044,7 @@
         <v>192</v>
       </c>
       <c r="F17" s="2">
-        <v>14522</v>
+        <v>14322</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>9266</v>
+        <v>9265</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3746</v>
+        <v>3650</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>13781</v>
+        <v>13681</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="2">
-        <v>30886</v>
+        <v>30786</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14109</v>
+        <v>14009</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>56162</v>
+        <v>55802</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19832</v>
+        <v>19831</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="6">
-        <v>2731</v>
+        <v>1231</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>49</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190504</v>
+        <v>186903</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5384</v>
+        <v>5348</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>15898</v>
+        <v>15798</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>138643</v>
+        <v>137620</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>100416</v>
+        <v>99906</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9913</v>
+        <v>9912</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79549</v>
+        <v>79309</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33722</v>
+        <v>33522</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>229477</v>
+        <v>226977</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>6425</v>
+        <v>5675</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68700</v>
+        <v>68604</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>18153</v>
+        <v>15778</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>21084</v>
+        <v>18584</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6914</v>
+        <v>6864</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3468</v>
+        <v>3118</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13629</v>
+        <v>13579</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>19</v>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7857</v>
+        <v>7807</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>468</v>
+        <v>418</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>38116</v>
+        <v>37916</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>41408</v>
+        <v>41208</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9356,11 +9356,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="6">
-        <v>100</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>49</v>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>22476</v>
+        <v>17391</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -10668,7 +10668,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="2">
-        <v>5534</v>
+        <v>5486</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -10691,7 +10691,7 @@
         <v>24</v>
       </c>
       <c r="F129" s="2">
-        <v>8160</v>
+        <v>8112</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -10714,7 +10714,7 @@
         <v>24</v>
       </c>
       <c r="F130" s="2">
-        <v>15659</v>
+        <v>15611</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9762</v>
+        <v>9714</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="2">
-        <v>917</v>
+        <v>857</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>10</v>
@@ -13060,7 +13060,7 @@
         <v>5</v>
       </c>
       <c r="F232" s="2">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>10</v>
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="2">
-        <v>72</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>10</v>
+      <c r="F234" s="6">
+        <v>22</v>
+      </c>
+      <c r="G234" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="F235" s="2">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>10</v>
@@ -13152,7 +13152,7 @@
         <v>5</v>
       </c>
       <c r="F236" s="2">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>10</v>
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="F237" s="2">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>10</v>
@@ -13198,7 +13198,7 @@
         <v>5</v>
       </c>
       <c r="F238" s="2">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>10</v>
@@ -13221,7 +13221,7 @@
         <v>5</v>
       </c>
       <c r="F239" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1695</v>
+        <v>1515</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="2">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14495</v>
+        <v>14493</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>52785</v>
+        <v>52784</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95509</v>
+        <v>94973</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>4991</v>
+        <v>4989</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>12968</v>
+        <v>12967</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>18308</v>
+        <v>17948</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>51222</v>
+        <v>51102</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14943,7 +14943,7 @@
         <v>288</v>
       </c>
       <c r="F47" s="2">
-        <v>8672</v>
+        <v>8472</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -15311,7 +15311,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>49</v>
@@ -15929,7 +15929,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>11851</v>
+        <v>11850</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -16021,7 +16021,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="2">
-        <v>9579</v>
+        <v>9479</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -16044,7 +16044,7 @@
         <v>192</v>
       </c>
       <c r="F17" s="2">
-        <v>14522</v>
+        <v>14322</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>9266</v>
+        <v>9265</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3746</v>
+        <v>3650</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>13781</v>
+        <v>13681</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="2">
-        <v>30886</v>
+        <v>30786</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6779</v>
+        <v>6491</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14109</v>
+        <v>14009</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="2">
-        <v>4906</v>
+        <v>3046</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>7347</v>
+        <v>5657</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="2">
-        <v>33638</v>
+        <v>32678</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>8581</v>
+        <v>7171</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17285,11 +17285,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="2">
-        <v>1246</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="F71" s="6">
+        <v>966</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>56162</v>
+        <v>55802</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19832</v>
+        <v>19831</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17768,11 +17768,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="2">
-        <v>4231</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="F92" s="6">
+        <v>1231</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190504</v>
+        <v>186903</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11181</v>
+        <v>11081</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5384</v>
+        <v>5348</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>15898</v>
+        <v>15798</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3513</v>
+        <v>3453</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>138643</v>
+        <v>137620</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>100416</v>
+        <v>99906</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>9539</v>
+        <v>9251</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>10201</v>
+        <v>9912</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10602</v>
+        <v>10314</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8563</v>
+        <v>8274</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -21147,7 +21147,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>49</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>207042</v>
+        <v>206682</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>34348</v>
+        <v>33580</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79549</v>
+        <v>79309</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33722</v>
+        <v>33522</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>71588</v>
+        <v>71338</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>226977</v>
+        <v>226677</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>23011</v>
+        <v>22981</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>1747</v>
+        <v>1735</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11496,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="2">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>2259</v>
+        <v>2307</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14000,7 +14000,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>103185</v>
+        <v>103184</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>52784</v>
+        <v>52782</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94973</v>
+        <v>94919</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71146</v>
+        <v>71144</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>46936</v>
+        <v>46934</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37845</v>
+        <v>37843</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15334,7 +15334,7 @@
         <v>12</v>
       </c>
       <c r="F64" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>49</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>73106</v>
+        <v>73105</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15791,7 +15791,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="2">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>9249</v>
+        <v>9248</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>7551</v>
+        <v>7550</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3650</v>
+        <v>3647</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16780,7 +16780,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="2">
-        <v>12651</v>
+        <v>12650</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6491</v>
+        <v>6455</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14009</v>
+        <v>14008</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -16895,7 +16895,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="2">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -17837,11 +17837,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="4">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>19</v>
+      <c r="F95" s="6">
+        <v>3</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>25656</v>
+        <v>25654</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -19169,7 +19169,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>17891</v>
+        <v>17890</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>38192</v>
+        <v>38191</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>47204</v>
+        <v>46104</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>99906</v>
+        <v>99816</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>8681</v>
+        <v>8680</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="2">
-        <v>6980</v>
+        <v>6979</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -20848,7 +20848,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>49</v>
@@ -21147,7 +21147,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>49</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>119312</v>
+        <v>119309</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21808,7 +21808,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="2">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -22288,7 +22288,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22334,7 +22334,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>49</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>226677</v>
+        <v>226077</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>80312</v>
+        <v>80112</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68604</v>
+        <v>68599</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>17813</v>
+        <v>17713</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>17391</v>
+        <v>22791</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="2">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>103184</v>
+        <v>102896</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>14383</v>
+        <v>14243</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94919</v>
+        <v>94853</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37843</v>
+        <v>37807</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>37073</v>
+        <v>36593</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3647</v>
+        <v>3503</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>12943</v>
+        <v>12823</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>30294</v>
+        <v>30102</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79309</v>
+        <v>78778</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>16273</v>
+        <v>16023</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>80112</v>
+        <v>79612</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68599</v>
+        <v>68359</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83665</v>
+        <v>83425</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>15378</v>
+        <v>15253</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>38769</v>
+        <v>38369</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15604</v>
+        <v>15454</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>47692</v>
+        <v>49492</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>22981</v>
+        <v>22731</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>8903</v>
+        <v>8803</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>6190</v>
+        <v>6090</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>23250</v>
+        <v>23249</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>9625</v>
+        <v>9525</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>1199</v>
+        <v>1149</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>5477</v>
+        <v>5427</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>8399</v>
+        <v>8299</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>18661</v>
+        <v>18611</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>4261</v>
+        <v>4260</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>2722</v>
+        <v>2622</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -10644,11 +10644,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="6">
-        <v>56</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>49</v>
+      <c r="F127" s="2">
+        <v>176</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>2559</v>
+        <v>2675</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>211487</v>
+        <v>211187</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>102896</v>
+        <v>102895</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>13881</v>
+        <v>13737</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94832</v>
+        <v>94831</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>6427</v>
+        <v>6403</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71144</v>
+        <v>70724</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="2">
-        <v>48805</v>
+        <v>48565</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -14782,7 +14782,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="2">
-        <v>40056</v>
+        <v>39816</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -14874,7 +14874,7 @@
         <v>576</v>
       </c>
       <c r="F44" s="6">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>49</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37374</v>
+        <v>37373</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>5657</v>
+        <v>5457</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17792,7 +17792,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="2">
-        <v>14231</v>
+        <v>13655</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>2703</v>
+        <v>2653</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5348</v>
+        <v>5312</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5313</v>
+        <v>5277</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>137620</v>
+        <v>137044</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>38071</v>
+        <v>37830</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>888</v>
+        <v>768</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>6170</v>
+        <v>6134</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>5734</v>
+        <v>5698</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>3053</v>
+        <v>2957</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>206681</v>
+        <v>206536</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22288,7 +22288,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22745,7 +22745,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="2">
-        <v>10493</v>
+        <v>10492</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33522</v>
+        <v>33221</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>5800</v>
+        <v>9300</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68359</v>
+        <v>68311</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>22800</v>
+        <v>22764</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>27141</v>
+        <v>27129</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>117527</v>
+        <v>130127</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7198,7 +7198,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>1860</v>
+        <v>1836</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>2094</v>
+        <v>2070</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>14019</v>
+        <v>14007</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>45254</v>
+        <v>45154</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15454</v>
+        <v>15354</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>17713</v>
+        <v>17663</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6864</v>
+        <v>6814</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3118</v>
+        <v>3068</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13579</v>
+        <v>13529</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>4935</v>
+        <v>4885</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>2834</v>
+        <v>2784</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>4867</v>
+        <v>4817</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7807</v>
+        <v>7757</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15094</v>
+        <v>15044</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1872</v>
+        <v>1822</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="6">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>49</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>418</v>
+        <v>368</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8252,11 +8252,11 @@
       <c r="E23">
         <v>50</v>
       </c>
-      <c r="F23" s="6">
-        <v>14</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>49</v>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>42274</v>
+        <v>42174</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>43234</v>
+        <v>43134</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="2">
-        <v>39649</v>
+        <v>39549</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -9702,7 +9702,7 @@
         <v>100</v>
       </c>
       <c r="F86" s="2">
-        <v>38853</v>
+        <v>38753</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>2247</v>
+        <v>2207</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -10001,7 +10001,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="2">
-        <v>1686</v>
+        <v>1646</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="2">
-        <v>1100</v>
+        <v>1060</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -10046,11 +10046,11 @@
       <c r="E101">
         <v>120</v>
       </c>
-      <c r="F101" s="6">
-        <v>5</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>49</v>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -11841,7 +11841,7 @@
         <v>36</v>
       </c>
       <c r="F179" s="6">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>49</v>
@@ -11910,7 +11910,7 @@
         <v>36</v>
       </c>
       <c r="F182" s="2">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>10</v>
@@ -12416,7 +12416,7 @@
         <v>160</v>
       </c>
       <c r="F204" s="2">
-        <v>4873</v>
+        <v>4853</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>135054</v>
+        <v>134954</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>52782</v>
+        <v>52758</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14368,7 +14368,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="2">
-        <v>4895</v>
+        <v>4889</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32301</v>
+        <v>32265</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3503</v>
+        <v>3443</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11081</v>
+        <v>11077</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3703</v>
+        <v>3699</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>3129</v>
+        <v>3125</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19375,11 +19375,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>49</v>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -19398,11 +19398,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="6">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>49</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -19422,7 +19422,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="2">
-        <v>4472</v>
+        <v>4468</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>15798</v>
+        <v>15794</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3453</v>
+        <v>3447</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19629,7 +19629,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="2">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>5166</v>
+        <v>5162</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>2957</v>
+        <v>2945</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>32954</v>
+        <v>32930</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>78180</v>
+        <v>78120</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>8815</v>
+        <v>8765</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15354</v>
+        <v>14354</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -9103,11 +9103,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="2">
-        <v>645</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="6">
+        <v>145</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10530,7 +10530,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="2">
-        <v>3593</v>
+        <v>3982</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>14354</v>
+        <v>28754</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -15264,11 +15264,11 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="6">
-        <v>1</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>49</v>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -15310,11 +15310,11 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="6">
-        <v>3</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>49</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>22791</v>
+        <v>15591</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>14007</v>
+        <v>14001</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>28104</v>
+        <v>28084</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>37710</v>
+        <v>37640</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>35637</v>
+        <v>35529</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>14478</v>
+        <v>14466</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>129977</v>
+        <v>129952</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7520,7 +7520,7 @@
         <v>300</v>
       </c>
       <c r="F23" s="6">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>49</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2840</v>
+        <v>2834</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>22631</v>
+        <v>22627</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>8703</v>
+        <v>8700</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>6090</v>
+        <v>6087</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>9525</v>
+        <v>9522</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>5427</v>
+        <v>5424</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>23639</v>
+        <v>23637</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>8199</v>
+        <v>8198</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>24283</v>
+        <v>24279</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>4160</v>
+        <v>4153</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>8234</v>
+        <v>8229</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>2167</v>
+        <v>2161</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -10001,7 +10001,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="2">
-        <v>1626</v>
+        <v>1620</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="2">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -11703,7 +11703,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="2">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="F177" s="6">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>49</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>9274</v>
+        <v>9271</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -12416,7 +12416,7 @@
         <v>160</v>
       </c>
       <c r="F204" s="2">
-        <v>4853</v>
+        <v>4850</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>10</v>
@@ -12508,7 +12508,7 @@
         <v>720</v>
       </c>
       <c r="F208" s="2">
-        <v>5234</v>
+        <v>5233</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>10</v>
@@ -12531,7 +12531,7 @@
         <v>720</v>
       </c>
       <c r="F209" s="2">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>10</v>
@@ -12577,7 +12577,7 @@
         <v>720</v>
       </c>
       <c r="F211" s="6">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G211" s="7" t="s">
         <v>49</v>
@@ -12600,7 +12600,7 @@
         <v>720</v>
       </c>
       <c r="F212" s="2">
-        <v>4373</v>
+        <v>4372</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>10</v>
@@ -12623,7 +12623,7 @@
         <v>720</v>
       </c>
       <c r="F213" s="6">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G213" s="7" t="s">
         <v>49</v>
@@ -12646,7 +12646,7 @@
         <v>720</v>
       </c>
       <c r="F214" s="2">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>10</v>
@@ -13908,7 +13908,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>24949</v>
+        <v>24946</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="2">
-        <v>9628</v>
+        <v>9622</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="2">
-        <v>5424</v>
+        <v>5418</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -14230,7 +14230,7 @@
         <v>144</v>
       </c>
       <c r="F16" s="2">
-        <v>15369</v>
+        <v>15363</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94759</v>
+        <v>94756</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>4977</v>
+        <v>4974</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -15012,7 +15012,7 @@
         <v>360</v>
       </c>
       <c r="F50" s="2">
-        <v>10954</v>
+        <v>10951</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -15035,7 +15035,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="2">
-        <v>23938</v>
+        <v>23934</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -15058,7 +15058,7 @@
         <v>360</v>
       </c>
       <c r="F52" s="2">
-        <v>11816</v>
+        <v>11813</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -15081,7 +15081,7 @@
         <v>360</v>
       </c>
       <c r="F53" s="2">
-        <v>41666</v>
+        <v>41661</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -15104,7 +15104,7 @@
         <v>360</v>
       </c>
       <c r="F54" s="2">
-        <v>43030</v>
+        <v>43027</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -15127,7 +15127,7 @@
         <v>360</v>
       </c>
       <c r="F55" s="2">
-        <v>11280</v>
+        <v>11277</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -15150,7 +15150,7 @@
         <v>360</v>
       </c>
       <c r="F56" s="2">
-        <v>33274</v>
+        <v>33271</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -15173,7 +15173,7 @@
         <v>360</v>
       </c>
       <c r="F57" s="2">
-        <v>34223</v>
+        <v>34220</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -15196,7 +15196,7 @@
         <v>360</v>
       </c>
       <c r="F58" s="2">
-        <v>37101</v>
+        <v>37098</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -15745,7 +15745,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="2">
-        <v>27707</v>
+        <v>27704</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3215</v>
+        <v>3210</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16803,7 +16803,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>14972</v>
+        <v>14966</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>13372</v>
+        <v>13366</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17124,11 +17124,11 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="6">
-        <v>5</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>49</v>
+      <c r="F64" s="4">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -19422,7 +19422,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="2">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5310</v>
+        <v>5309</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19468,7 +19468,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="2">
-        <v>35635</v>
+        <v>35634</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>15794</v>
+        <v>15792</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19514,7 +19514,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19560,7 +19560,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="2">
-        <v>13016</v>
+        <v>13015</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>133000</v>
+        <v>132988</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19790,7 +19790,7 @@
         <v>120</v>
       </c>
       <c r="F35" s="6">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>15746</v>
+        <v>15740</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>5950</v>
+        <v>5944</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10633</v>
+        <v>10627</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>9239</v>
+        <v>9233</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9900</v>
+        <v>9894</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10302</v>
+        <v>10296</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8262</v>
+        <v>8256</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>3261</v>
+        <v>3255</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>205960</v>
+        <v>205957</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>15598</v>
+        <v>15573</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>32721</v>
+        <v>32696</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22906,7 +22906,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>15181</v>
+        <v>15156</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22952,7 +22952,7 @@
         <v>200</v>
       </c>
       <c r="F14" s="2">
-        <v>1054</v>
+        <v>1029</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22975,7 +22975,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="2">
-        <v>1063</v>
+        <v>1038</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22997,11 +22997,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="6">
-        <v>22</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>49</v>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>39096</v>
+        <v>37896</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>45408</v>
+        <v>44208</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>60013</v>
+        <v>59963</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>220827</v>
+        <v>220627</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>74612</v>
+        <v>74512</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>12960</v>
+        <v>12910</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>129952</v>
+        <v>129852</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>28084</v>
+        <v>28034</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>802</v>
+        <v>1234</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>9271</v>
+        <v>8631</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>9416</v>
+        <v>9404</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2">
-        <v>14807</v>
+        <v>14795</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>5021</v>
+        <v>5011</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17240,7 +17240,7 @@
         <v>200</v>
       </c>
       <c r="F69" s="2">
-        <v>24779</v>
+        <v>24769</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>6762</v>
+        <v>10362</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>5824</v>
+        <v>5788</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>3219</v>
+        <v>3183</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>4191</v>
+        <v>4155</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>5674</v>
+        <v>5638</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>5989</v>
+        <v>5953</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -20572,7 +20572,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="2">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>77028</v>
+        <v>79428</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>1234</v>
+        <v>1450</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>8600</v>
+        <v>7850</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>67447</v>
+        <v>67159</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>11860</v>
+        <v>11710</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>128352</v>
+        <v>127802</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>113884</v>
+        <v>111084</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>38259</v>
+        <v>37959</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>31626</v>
+        <v>30626</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>4580</v>
+        <v>4530</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>11832</v>
+        <v>9852</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="2">
-        <v>857</v>
+        <v>737</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>10</v>
@@ -13060,7 +13060,7 @@
         <v>5</v>
       </c>
       <c r="F232" s="2">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>10</v>
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="6">
-        <v>12</v>
-      </c>
-      <c r="G234" s="7" t="s">
-        <v>49</v>
+      <c r="F234" s="2">
+        <v>42</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="F235" s="2">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>10</v>
@@ -13152,7 +13152,7 @@
         <v>5</v>
       </c>
       <c r="F236" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>10</v>
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="F237" s="2">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>10</v>
@@ -13198,7 +13198,7 @@
         <v>5</v>
       </c>
       <c r="F238" s="2">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>10</v>
@@ -13221,7 +13221,7 @@
         <v>5</v>
       </c>
       <c r="F239" s="2">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1515</v>
+        <v>1535</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>10</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="2">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -13428,7 +13428,7 @@
         <v>5</v>
       </c>
       <c r="F248" s="2">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>10</v>
@@ -13474,7 +13474,7 @@
         <v>5</v>
       </c>
       <c r="F250" s="2">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>10</v>
@@ -13908,7 +13908,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>24946</v>
+        <v>22066</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>2295</v>
+        <v>2175</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>102602</v>
+        <v>101682</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14161,7 +14161,7 @@
         <v>144</v>
       </c>
       <c r="F13" s="2">
-        <v>1939</v>
+        <v>1795</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94459</v>
+        <v>94259</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>6349</v>
+        <v>6205</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>12452</v>
+        <v>12332</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>8805</v>
+        <v>8709</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>36325</v>
+        <v>39165</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15242,7 +15242,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>8941</v>
+        <v>8787</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>2826</v>
+        <v>2730</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -16389,7 +16389,7 @@
         <v>72</v>
       </c>
       <c r="F32" s="2">
-        <v>925</v>
+        <v>709</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -16411,11 +16411,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
-        <v>1001</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="F33" s="6">
+        <v>713</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16458,7 +16458,7 @@
         <v>144</v>
       </c>
       <c r="F35" s="6">
-        <v>258</v>
+        <v>114</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -16504,7 +16504,7 @@
         <v>144</v>
       </c>
       <c r="F37" s="6">
-        <v>344</v>
+        <v>56</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>49</v>
@@ -16527,7 +16527,7 @@
         <v>72</v>
       </c>
       <c r="F38" s="6">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>49</v>
@@ -16550,7 +16550,7 @@
         <v>144</v>
       </c>
       <c r="F39" s="2">
-        <v>1014</v>
+        <v>870</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -16596,7 +16596,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="6">
-        <v>454</v>
+        <v>166</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>49</v>
@@ -16642,7 +16642,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="6">
-        <v>400</v>
+        <v>256</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>49</v>
@@ -16711,7 +16711,7 @@
         <v>72</v>
       </c>
       <c r="F46" s="2">
-        <v>842</v>
+        <v>698</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -16734,7 +16734,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>1400</v>
+        <v>1256</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>5135</v>
+        <v>4991</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>12405</v>
+        <v>12213</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>3866</v>
+        <v>3366</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>2124</v>
+        <v>2074</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10627</v>
+        <v>10577</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>131099</v>
+        <v>130863</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>119309</v>
+        <v>116509</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>34665</v>
+        <v>34377</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>14073</v>
+        <v>13673</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>58938</v>
+        <v>58913</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>219224</v>
+        <v>219174</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>74512</v>
+        <v>74412</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>67159</v>
+        <v>67111</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>82944</v>
+        <v>82896</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>22716</v>
+        <v>22698</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>27093</v>
+        <v>27057</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>10602</v>
+        <v>10202</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>37959</v>
+        <v>37859</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>2021</v>
+        <v>1949</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>13745</v>
+        <v>13673</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>14001</v>
+        <v>13953</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -7451,7 +7451,7 @@
         <v>72</v>
       </c>
       <c r="F20" s="2">
-        <v>2892</v>
+        <v>2820</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>45114</v>
+        <v>44614</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>18444</v>
+        <v>17944</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7520,7 +7520,7 @@
         <v>300</v>
       </c>
       <c r="F23" s="6">
-        <v>269</v>
+        <v>29</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>49</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2834</v>
+        <v>2714</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="2">
-        <v>24419</v>
+        <v>24319</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -7658,7 +7658,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>2566</v>
+        <v>2516</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -7704,7 +7704,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="2">
-        <v>1251</v>
+        <v>1151</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46420</v>
+        <v>46370</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>30526</v>
+        <v>30476</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6602</v>
+        <v>6352</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3043</v>
+        <v>2943</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>4885</v>
+        <v>4835</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7507</v>
+        <v>7457</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>14856</v>
+        <v>14606</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1822</v>
+        <v>1772</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8229,11 +8229,11 @@
       <c r="E22">
         <v>50</v>
       </c>
-      <c r="F22" s="2">
-        <v>268</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="6">
+        <v>218</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>48292</v>
+        <v>48192</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8966,7 +8966,7 @@
         <v>100</v>
       </c>
       <c r="F54" s="6">
-        <v>451</v>
+        <v>351</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>49</v>
@@ -9380,7 +9380,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="2">
-        <v>30071</v>
+        <v>29971</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -9403,7 +9403,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="2">
-        <v>16334</v>
+        <v>16234</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="2">
-        <v>46773</v>
+        <v>46673</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -9449,7 +9449,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="2">
-        <v>22976</v>
+        <v>22876</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="2">
-        <v>2637</v>
+        <v>2537</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -9909,7 +9909,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="2">
-        <v>6223</v>
+        <v>6123</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="2">
-        <v>15169</v>
+        <v>15069</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>959</v>
+        <v>839</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -10001,7 +10001,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="6">
-        <v>419</v>
+        <v>299</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>49</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="6">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>49</v>
@@ -13908,7 +13908,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>22066</v>
+        <v>21778</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>2175</v>
+        <v>2151</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -13999,11 +13999,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="2">
-        <v>106</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="F6" s="6">
+        <v>88</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>101682</v>
+        <v>101538</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14381</v>
+        <v>14309</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14092,7 +14092,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>2004</v>
+        <v>1986</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>49866</v>
+        <v>49722</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>13485</v>
+        <v>13341</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14161,7 +14161,7 @@
         <v>144</v>
       </c>
       <c r="F13" s="2">
-        <v>1795</v>
+        <v>1651</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94259</v>
+        <v>94187</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>6205</v>
+        <v>6133</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>4866</v>
+        <v>4830</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14506,7 +14506,7 @@
         <v>576</v>
       </c>
       <c r="F28" s="2">
-        <v>32012</v>
+        <v>31436</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>50466</v>
+        <v>49890</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14552,7 +14552,7 @@
         <v>576</v>
       </c>
       <c r="F30" s="2">
-        <v>34247</v>
+        <v>33671</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -14575,7 +14575,7 @@
         <v>576</v>
       </c>
       <c r="F31" s="2">
-        <v>12803</v>
+        <v>12227</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -14598,7 +14598,7 @@
         <v>576</v>
       </c>
       <c r="F32" s="2">
-        <v>11641</v>
+        <v>11065</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -14621,7 +14621,7 @@
         <v>576</v>
       </c>
       <c r="F33" s="2">
-        <v>7951</v>
+        <v>7375</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="2">
-        <v>48565</v>
+        <v>47989</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -14667,7 +14667,7 @@
         <v>576</v>
       </c>
       <c r="F35" s="6">
-        <v>2304</v>
+        <v>1728</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -14690,7 +14690,7 @@
         <v>576</v>
       </c>
       <c r="F36" s="2">
-        <v>54994</v>
+        <v>54418</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -14713,7 +14713,7 @@
         <v>576</v>
       </c>
       <c r="F37" s="6">
-        <v>1457</v>
+        <v>881</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>49</v>
@@ -14759,7 +14759,7 @@
         <v>576</v>
       </c>
       <c r="F39" s="2">
-        <v>6556</v>
+        <v>5980</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -14782,7 +14782,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="2">
-        <v>39816</v>
+        <v>39240</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -14805,7 +14805,7 @@
         <v>576</v>
       </c>
       <c r="F41" s="6">
-        <v>2846</v>
+        <v>2270</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>49</v>
@@ -14828,7 +14828,7 @@
         <v>576</v>
       </c>
       <c r="F42" s="6">
-        <v>981</v>
+        <v>405</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>49</v>
@@ -14897,7 +14897,7 @@
         <v>72</v>
       </c>
       <c r="F45" s="2">
-        <v>24449</v>
+        <v>24377</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -14920,7 +14920,7 @@
         <v>72</v>
       </c>
       <c r="F46" s="2">
-        <v>2201</v>
+        <v>2129</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -14943,7 +14943,7 @@
         <v>288</v>
       </c>
       <c r="F47" s="2">
-        <v>8472</v>
+        <v>8184</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>44615</v>
+        <v>44471</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>39165</v>
+        <v>39129</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>70560</v>
+        <v>70416</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>35955</v>
+        <v>35811</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -15745,7 +15745,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="2">
-        <v>26479</v>
+        <v>26335</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -15768,7 +15768,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="6">
-        <v>677</v>
+        <v>389</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>49</v>
@@ -15790,11 +15790,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="6">
-        <v>141</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -15814,7 +15814,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>18107</v>
+        <v>17963</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -15837,7 +15837,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>4638</v>
+        <v>4494</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>9185</v>
+        <v>9089</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>7523</v>
+        <v>7427</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -17079,7 +17079,7 @@
         <v>576</v>
       </c>
       <c r="F62" s="2">
-        <v>21418</v>
+        <v>20842</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -17102,7 +17102,7 @@
         <v>576</v>
       </c>
       <c r="F63" s="2">
-        <v>14524</v>
+        <v>13948</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>3366</v>
+        <v>3166</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17286,7 +17286,7 @@
         <v>200</v>
       </c>
       <c r="F71" s="6">
-        <v>686</v>
+        <v>486</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>49</v>
@@ -17355,7 +17355,7 @@
         <v>200</v>
       </c>
       <c r="F74" s="6">
-        <v>932</v>
+        <v>732</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>49</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>59968</v>
+        <v>59768</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -17470,7 +17470,7 @@
         <v>200</v>
       </c>
       <c r="F79" s="2">
-        <v>1855</v>
+        <v>1655</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>55778</v>
+        <v>54626</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17562,7 +17562,7 @@
         <v>1152</v>
       </c>
       <c r="F83" s="6">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>49</v>
@@ -17608,7 +17608,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="6">
-        <v>3058</v>
+        <v>1906</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>49</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>18645</v>
+        <v>18069</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17654,7 +17654,7 @@
         <v>576</v>
       </c>
       <c r="F87" s="6">
-        <v>1881</v>
+        <v>1305</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>49</v>
@@ -17677,7 +17677,7 @@
         <v>576</v>
       </c>
       <c r="F88" s="2">
-        <v>4691</v>
+        <v>4115</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -17723,7 +17723,7 @@
         <v>576</v>
       </c>
       <c r="F90" s="6">
-        <v>826</v>
+        <v>250</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>49</v>
@@ -17745,11 +17745,11 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="6">
-        <v>3</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>49</v>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="6">
-        <v>1231</v>
+        <v>655</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>49</v>
@@ -17792,7 +17792,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="2">
-        <v>13655</v>
+        <v>13079</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>186876</v>
+        <v>186732</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>2074</v>
+        <v>2024</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10577</v>
+        <v>10527</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19100,7 +19100,7 @@
         <v>144</v>
       </c>
       <c r="F5" s="2">
-        <v>24478</v>
+        <v>24334</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -19123,7 +19123,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="2">
-        <v>10148</v>
+        <v>10004</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -19169,7 +19169,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>17745</v>
+        <v>17601</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>8485</v>
+        <v>8413</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -19215,7 +19215,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>11268</v>
+        <v>11148</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -19238,7 +19238,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>12846</v>
+        <v>12816</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3339</v>
+        <v>3303</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>2692</v>
+        <v>2656</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>130863</v>
+        <v>130719</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>116509</v>
+        <v>116437</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>203756</v>
+        <v>203684</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21305,7 +21305,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2">
-        <v>66729</v>
+        <v>66657</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>29706</v>
+        <v>29634</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>58997</v>
+        <v>58709</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22242,7 +22242,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="2">
-        <v>87590</v>
+        <v>87206</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22265,7 +22265,7 @@
         <v>384</v>
       </c>
       <c r="F7" s="2">
-        <v>54608</v>
+        <v>54224</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -22288,7 +22288,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>1686</v>
+        <v>1542</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22311,7 +22311,7 @@
         <v>144</v>
       </c>
       <c r="F9" s="2">
-        <v>22934</v>
+        <v>22790</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>22230</v>
+        <v>22038</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>87064</v>
+        <v>86488</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>92793</v>
+        <v>92781</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>40233</v>
+        <v>40209</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>8716</v>
+        <v>8668</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22676,7 +22676,7 @@
         <v>1000</v>
       </c>
       <c r="F2" s="6">
-        <v>1088</v>
+        <v>88</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>49</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>4515</v>
+        <v>4015</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22722,7 +22722,7 @@
         <v>1000</v>
       </c>
       <c r="F4" s="6">
-        <v>971</v>
+        <v>21</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>49</v>
@@ -22745,7 +22745,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="2">
-        <v>5342</v>
+        <v>4842</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22768,7 +22768,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="6">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>49</v>
@@ -22791,7 +22791,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="2">
-        <v>6429</v>
+        <v>5929</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>13673</v>
+        <v>13273</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>30292</v>
+        <v>30092</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22906,7 +22906,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>12631</v>
+        <v>12131</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22975,7 +22975,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="6">
-        <v>438</v>
+        <v>318</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>49</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>30476</v>
+        <v>30469</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="2">
-        <v>1937</v>
+        <v>1930</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>101538</v>
+        <v>101531</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="2">
-        <v>4818</v>
+        <v>4815</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>93899</v>
+        <v>93896</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>5629</v>
+        <v>5625</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32175</v>
+        <v>32171</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>42311</v>
+        <v>42303</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -15906,7 +15906,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>6471</v>
+        <v>6468</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>6659</v>
+        <v>6656</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16274,7 +16274,7 @@
         <v>192</v>
       </c>
       <c r="F27" s="2">
-        <v>31026</v>
+        <v>31022</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>10821</v>
+        <v>10817</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -16803,7 +16803,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>13238</v>
+        <v>13234</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -16987,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="2">
-        <v>3743</v>
+        <v>3740</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>18427</v>
+        <v>18423</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -17907,7 +17907,7 @@
         <v>144</v>
       </c>
       <c r="F98" s="6">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G98" s="7" t="s">
         <v>49</v>
@@ -17953,7 +17953,7 @@
         <v>144</v>
       </c>
       <c r="F100" s="2">
-        <v>16155</v>
+        <v>16152</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -17999,7 +17999,7 @@
         <v>144</v>
       </c>
       <c r="F102" s="2">
-        <v>17806</v>
+        <v>17802</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -18114,7 +18114,7 @@
         <v>144</v>
       </c>
       <c r="F107" s="2">
-        <v>19861</v>
+        <v>19857</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -18919,7 +18919,7 @@
         <v>192</v>
       </c>
       <c r="F142" s="6">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>49</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>114779</v>
+        <v>114775</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20664,7 +20664,7 @@
         <v>240</v>
       </c>
       <c r="F73" s="2">
-        <v>13497</v>
+        <v>13490</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -21078,7 +21078,7 @@
         <v>144</v>
       </c>
       <c r="F91" s="2">
-        <v>11784</v>
+        <v>11780</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>201524</v>
+        <v>201517</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>30921</v>
+        <v>30918</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>33580</v>
+        <v>33576</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>92481</v>
+        <v>92474</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7198,7 +7198,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>1428</v>
+        <v>1380</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>30319</v>
+        <v>30119</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>5287</v>
+        <v>5037</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>8319</v>
+        <v>8169</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>870</v>
+        <v>370</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>5422</v>
+        <v>5272</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>2476</v>
+        <v>2226</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>7429</v>
+        <v>7279</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>70472</v>
+        <v>70328</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -17262,11 +17262,11 @@
       <c r="E70">
         <v>200</v>
       </c>
-      <c r="F70" s="2">
-        <v>2851</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="6">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>8413</v>
+        <v>8341</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>6350</v>
+        <v>5725</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>63127</v>
+        <v>62983</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>21618</v>
+        <v>21546</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>4235</v>
+        <v>4185</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -13497,7 +13497,7 @@
         <v>40</v>
       </c>
       <c r="F251" s="2">
-        <v>3227</v>
+        <v>3067</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>130954</v>
+        <v>130154</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -19215,7 +19215,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>11148</v>
+        <v>11028</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -19238,7 +19238,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>12816</v>
+        <v>12756</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>27980</v>
+        <v>27860</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>44364</v>
+        <v>44244</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>21563</v>
+        <v>21443</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>6760</v>
+        <v>6640</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>2548</v>
+        <v>2524</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10627</v>
+        <v>10603</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>8981</v>
+        <v>8957</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9858</v>
+        <v>9834</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10296</v>
+        <v>10272</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8112</v>
+        <v>8088</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>1598</v>
+        <v>1574</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>3170</v>
+        <v>3146</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>2139</v>
+        <v>2115</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>2470</v>
+        <v>2446</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>5953</v>
+        <v>5929</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>210920</v>
+        <v>210420</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>10202</v>
+        <v>9802</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>36559</v>
+        <v>36059</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>1721</v>
+        <v>1361</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>13649</v>
+        <v>13289</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -7451,7 +7451,7 @@
         <v>72</v>
       </c>
       <c r="F20" s="2">
-        <v>2172</v>
+        <v>1452</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>44614</v>
+        <v>42614</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>17944</v>
+        <v>15944</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2714</v>
+        <v>2234</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>29919</v>
+        <v>29619</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>5272</v>
+        <v>5269</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8966,7 +8966,7 @@
         <v>100</v>
       </c>
       <c r="F54" s="6">
-        <v>351</v>
+        <v>151</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>49</v>
@@ -11059,7 +11059,7 @@
         <v>24</v>
       </c>
       <c r="F145" s="2">
-        <v>538</v>
+        <v>418</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>10</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="2">
-        <v>15566</v>
+        <v>15182</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -16204,11 +16204,11 @@
       <c r="E24">
         <v>96</v>
       </c>
-      <c r="F24" s="2">
-        <v>714</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="F24" s="6">
+        <v>426</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>12310</v>
+        <v>12190</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>185796</v>
+        <v>185508</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19675,7 +19675,7 @@
         <v>48</v>
       </c>
       <c r="F30" s="2">
-        <v>5914</v>
+        <v>5910</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>114199</v>
+        <v>113623</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>2524</v>
+        <v>2236</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>8667</v>
+        <v>8379</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>1539</v>
+        <v>1251</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -22288,7 +22288,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>1542</v>
+        <v>822</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -20572,7 +20572,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>210420</v>
+        <v>210270</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>4500</v>
+        <v>4425</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>126502</v>
+        <v>126402</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>29269</v>
+        <v>29119</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>15463</v>
+        <v>15363</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>47392</v>
+        <v>47242</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -10346,7 +10346,7 @@
         <v>24</v>
       </c>
       <c r="F114" s="6">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G114" s="7" t="s">
         <v>23</v>
@@ -10438,7 +10438,7 @@
         <v>24</v>
       </c>
       <c r="F118" s="2">
-        <v>2134</v>
+        <v>2122</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -11772,7 +11772,7 @@
         <v>48</v>
       </c>
       <c r="F176" s="6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>23</v>
@@ -15242,7 +15242,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>8787</v>
+        <v>8763</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -15380,7 +15380,7 @@
         <v>12</v>
       </c>
       <c r="F66" s="2">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>2031</v>
+        <v>1983</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>114997</v>
+        <v>114781</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>28464</v>
+        <v>28176</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>56038</v>
+        <v>55738</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>210270</v>
+        <v>208770</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>4425</v>
+        <v>4050</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>62695</v>
+        <v>62647</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>126402</v>
+        <v>125402</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>29119</v>
+        <v>28269</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>47242</v>
+        <v>46942</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>1606</v>
+        <v>1546</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11334,11 +11334,11 @@
       <c r="E157">
         <v>6</v>
       </c>
-      <c r="F157" s="4">
-        <v>0</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>19</v>
+      <c r="F157" s="2">
+        <v>71</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>98939</v>
+        <v>98219</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>93800</v>
+        <v>93440</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>5623</v>
+        <v>5587</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>11312</v>
+        <v>11288</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>5930</v>
+        <v>5822</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>35025</v>
+        <v>34593</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15518,7 +15518,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="2">
-        <v>4783</v>
+        <v>4759</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>9719</v>
+        <v>9647</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>185328</v>
+        <v>184932</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="2">
-        <v>17853</v>
+        <v>17613</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -18206,7 +18206,7 @@
         <v>192</v>
       </c>
       <c r="F111" s="2">
-        <v>22290</v>
+        <v>22074</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -18252,7 +18252,7 @@
         <v>192</v>
       </c>
       <c r="F113" s="2">
-        <v>27080</v>
+        <v>26912</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>21101</v>
+        <v>20933</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>6310</v>
+        <v>6082</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>2128</v>
+        <v>2068</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>1202</v>
+        <v>1154</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>3008</v>
+        <v>2942</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>1191</v>
+        <v>1167</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>2422</v>
+        <v>2362</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>6508</v>
+        <v>6460</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="2">
-        <v>4315</v>
+        <v>4267</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -21055,7 +21055,7 @@
         <v>144</v>
       </c>
       <c r="F90" s="2">
-        <v>15066</v>
+        <v>14838</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -21124,7 +21124,7 @@
         <v>144</v>
       </c>
       <c r="F93" s="2">
-        <v>14752</v>
+        <v>14680</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>200965</v>
+        <v>200821</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>28434</v>
+        <v>28326</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>91370</v>
+        <v>89930</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>39579</v>
+        <v>39099</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>27492</v>
+        <v>26492</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>55738</v>
+        <v>49838</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>208770</v>
+        <v>197970</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>4050</v>
+        <v>3575</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>62647</v>
+        <v>61735</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>79236</v>
+        <v>78900</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>21510</v>
+        <v>21294</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>26080</v>
+        <v>25432</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>36009</v>
+        <v>35209</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="2">
-        <v>24319</v>
+        <v>24119</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>45370</v>
+        <v>45220</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>28269</v>
+        <v>20269</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>4402</v>
+        <v>4252</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>12317</v>
+        <v>12167</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>6357</v>
+        <v>6307</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>46942</v>
+        <v>45142</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>21699</v>
+        <v>21599</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>19285</v>
+        <v>19185</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>22915</v>
+        <v>22865</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>35696</v>
+        <v>32496</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>42108</v>
+        <v>39408</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="6">
-        <v>20</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>23</v>
+      <c r="F119" s="2">
+        <v>1820</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>8631</v>
+        <v>8375</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -14000,7 +14000,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="6">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>23</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>98219</v>
+        <v>95195</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>48138</v>
+        <v>47274</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>11613</v>
+        <v>11325</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="2">
-        <v>9598</v>
+        <v>8878</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="2">
-        <v>4815</v>
+        <v>4095</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -14230,7 +14230,7 @@
         <v>144</v>
       </c>
       <c r="F16" s="2">
-        <v>13635</v>
+        <v>12195</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>93434</v>
+        <v>89906</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>5587</v>
+        <v>3283</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>4290</v>
+        <v>3822</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14368,7 +14368,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="2">
-        <v>4888</v>
+        <v>4744</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>11285</v>
+        <v>10865</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>5819</v>
+        <v>4043</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>31808</v>
+        <v>31208</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>70328</v>
+        <v>70028</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14506,7 +14506,7 @@
         <v>576</v>
       </c>
       <c r="F28" s="2">
-        <v>31436</v>
+        <v>28556</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>49890</v>
+        <v>47010</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14552,7 +14552,7 @@
         <v>576</v>
       </c>
       <c r="F30" s="2">
-        <v>33671</v>
+        <v>30791</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -14575,7 +14575,7 @@
         <v>576</v>
       </c>
       <c r="F31" s="2">
-        <v>12227</v>
+        <v>11651</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>42243</v>
+        <v>42183</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -15242,7 +15242,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>8763</v>
+        <v>8583</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
-        <v>141</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="6">
+        <v>9</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>205</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -15518,7 +15518,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="2">
-        <v>4759</v>
+        <v>4327</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>9647</v>
+        <v>9359</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>67172</v>
+        <v>66596</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15814,7 +15814,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>16592</v>
+        <v>16448</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -15906,7 +15906,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>6395</v>
+        <v>5963</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -17147,11 +17147,11 @@
       <c r="E65">
         <v>200</v>
       </c>
-      <c r="F65" s="6">
-        <v>395</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>23</v>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>3921</v>
+        <v>2421</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="2">
-        <v>31718</v>
+        <v>30218</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -17240,7 +17240,7 @@
         <v>200</v>
       </c>
       <c r="F69" s="2">
-        <v>24769</v>
+        <v>23769</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>482</v>
+        <v>2</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>17829</v>
+        <v>16101</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17654,7 +17654,7 @@
         <v>576</v>
       </c>
       <c r="F87" s="6">
-        <v>1065</v>
+        <v>489</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>23</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>184932</v>
+        <v>183492</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="2">
-        <v>17613</v>
+        <v>16653</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -18206,7 +18206,7 @@
         <v>192</v>
       </c>
       <c r="F111" s="2">
-        <v>22074</v>
+        <v>21114</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -18252,7 +18252,7 @@
         <v>192</v>
       </c>
       <c r="F113" s="2">
-        <v>26912</v>
+        <v>25952</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -19422,7 +19422,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="2">
-        <v>4384</v>
+        <v>4264</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -19514,7 +19514,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="6">
-        <v>245</v>
+        <v>155</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>23</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3085</v>
+        <v>2995</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19560,7 +19560,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="2">
-        <v>12943</v>
+        <v>12799</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -19629,7 +19629,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="2">
-        <v>3506</v>
+        <v>3434</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>5041</v>
+        <v>4969</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>113179</v>
+        <v>106699</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>26866</v>
+        <v>25786</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>44210</v>
+        <v>43250</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>20933</v>
+        <v>20813</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>6082</v>
+        <v>5962</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>2065</v>
+        <v>1777</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>8957</v>
+        <v>8813</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9834</v>
+        <v>9546</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8088</v>
+        <v>7800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>1154</v>
+        <v>866</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>2939</v>
+        <v>2651</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>200821</v>
+        <v>199381</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21305,7 +21305,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2">
-        <v>65361</v>
+        <v>65073</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>28326</v>
+        <v>27606</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>28176</v>
+        <v>27888</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>30744</v>
+        <v>29592</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>20622</v>
+        <v>18702</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>89870</v>
+        <v>86270</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>39099</v>
+        <v>37875</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22791,7 +22791,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="2">
-        <v>4857</v>
+        <v>4457</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>26492</v>
+        <v>24492</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>49638</v>
+        <v>48638</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>196870</v>
+        <v>192864</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>61783</v>
+        <v>61639</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>19849</v>
+        <v>16849</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>19927</v>
+        <v>19677</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>5050</v>
+        <v>4550</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8436,11 +8436,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="2">
-        <v>360</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="F31" s="6">
+        <v>60</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>1593</v>
+        <v>1093</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>6751</v>
+        <v>6501</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>7279</v>
+        <v>7029</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -9150,7 +9150,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="2">
-        <v>2618</v>
+        <v>2606</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -9380,7 +9380,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="2">
-        <v>29971</v>
+        <v>27971</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -10668,7 +10668,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="2">
-        <v>5338</v>
+        <v>5332</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -10691,7 +10691,7 @@
         <v>24</v>
       </c>
       <c r="F129" s="2">
-        <v>7960</v>
+        <v>7954</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -10714,7 +10714,7 @@
         <v>24</v>
       </c>
       <c r="F130" s="2">
-        <v>15355</v>
+        <v>15349</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9566</v>
+        <v>9560</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="2">
-        <v>21842</v>
+        <v>21830</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>8375</v>
+        <v>8311</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>1911</v>
+        <v>1887</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14092,7 +14092,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>1241</v>
+        <v>1223</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>46842</v>
+        <v>46698</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>89258</v>
+        <v>88994</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>3066</v>
+        <v>2994</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3642</v>
+        <v>3606</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>4091</v>
+        <v>3941</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>31208</v>
+        <v>31076</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>69596</v>
+        <v>69344</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>41463</v>
+        <v>41175</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>34125</v>
+        <v>34053</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>65876</v>
+        <v>65732</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>12116</v>
+        <v>12110</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>10814</v>
+        <v>10790</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>9754</v>
+        <v>9718</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17355,7 +17355,7 @@
         <v>200</v>
       </c>
       <c r="F74" s="6">
-        <v>732</v>
+        <v>244</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>23</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10474</v>
+        <v>10424</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>103963</v>
+        <v>103939</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>1776</v>
+        <v>1632</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>866</v>
+        <v>722</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>2651</v>
+        <v>2507</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20664,7 +20664,7 @@
         <v>240</v>
       </c>
       <c r="F73" s="2">
-        <v>12735</v>
+        <v>10335</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -20802,7 +20802,7 @@
         <v>144</v>
       </c>
       <c r="F79" s="6">
-        <v>359</v>
+        <v>215</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>23</v>
@@ -20847,11 +20847,11 @@
       <c r="E81">
         <v>144</v>
       </c>
-      <c r="F81" s="6">
-        <v>15</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>23</v>
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1448</v>
+        <v>1304</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -20894,7 +20894,7 @@
         <v>144</v>
       </c>
       <c r="F83" s="2">
-        <v>7667</v>
+        <v>7523</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>10</v>
@@ -20985,11 +20985,11 @@
       <c r="E87">
         <v>144</v>
       </c>
-      <c r="F87" s="6">
-        <v>52</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>23</v>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -21078,7 +21078,7 @@
         <v>144</v>
       </c>
       <c r="F91" s="2">
-        <v>11780</v>
+        <v>11636</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -21946,7 +21946,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -21969,7 +21969,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="2">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>84422</v>
+        <v>84278</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22698,11 +22698,11 @@
       <c r="E3">
         <v>500</v>
       </c>
-      <c r="F3" s="6">
-        <v>1015</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>8472</v>
+        <v>8072</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>23692</v>
+        <v>22492</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="6">
-        <v>4</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>23</v>
+      <c r="F119" s="2">
+        <v>6604</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -11334,11 +11334,11 @@
       <c r="E157">
         <v>6</v>
       </c>
-      <c r="F157" s="6">
-        <v>13</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>23</v>
+      <c r="F157" s="2">
+        <v>445</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>48626</v>
+        <v>48326</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>193052</v>
+        <v>187852</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>74411</v>
+        <v>73111</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>14200</v>
+        <v>17400</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>61636</v>
+        <v>60436</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>78708</v>
+        <v>77748</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>21292</v>
+        <v>21112</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>25037</v>
+        <v>24677</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>9135</v>
+        <v>8675</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>122702</v>
+        <v>124502</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>111084</v>
+        <v>111184</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>35629</v>
+        <v>35529</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15849</v>
+        <v>14599</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8091,11 +8091,11 @@
       <c r="E16">
         <v>50</v>
       </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>19</v>
+      <c r="F16" s="6">
+        <v>30</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>19</v>
+      <c r="F21" s="6">
+        <v>24</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>45142</v>
+        <v>44742</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8436,11 +8436,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="6">
-        <v>60</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>23</v>
+      <c r="F31" s="2">
+        <v>1860</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>1222</v>
+        <v>3022</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>1339</v>
+        <v>1303</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>817</v>
+        <v>517</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -9196,7 +9196,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="6">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>23</v>
@@ -9633,7 +9633,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="2">
-        <v>11105</v>
+        <v>11005</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>10</v>
@@ -10070,7 +10070,7 @@
         <v>120</v>
       </c>
       <c r="F102" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G102" s="7" t="s">
         <v>23</v>
@@ -10093,7 +10093,7 @@
         <v>120</v>
       </c>
       <c r="F103" s="6">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="G103" s="7" t="s">
         <v>23</v>
@@ -10162,7 +10162,7 @@
         <v>120</v>
       </c>
       <c r="F106" s="2">
-        <v>5924</v>
+        <v>5914</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -10231,7 +10231,7 @@
         <v>120</v>
       </c>
       <c r="F109" s="2">
-        <v>5028</v>
+        <v>5018</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>6380</v>
+        <v>5756</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -10966,11 +10966,11 @@
       <c r="E141">
         <v>30</v>
       </c>
-      <c r="F141" s="4">
-        <v>0</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>19</v>
+      <c r="F141" s="2">
+        <v>694</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -11035,11 +11035,11 @@
       <c r="E144">
         <v>24</v>
       </c>
-      <c r="F144" s="4">
-        <v>0</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>19</v>
+      <c r="F144" s="6">
+        <v>26</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="2">
-        <v>445</v>
+        <v>637</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -13497,7 +13497,7 @@
         <v>40</v>
       </c>
       <c r="F251" s="2">
-        <v>3067</v>
+        <v>3167</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>130034</v>
+        <v>130134</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -13635,7 +13635,7 @@
         <v>5</v>
       </c>
       <c r="F257" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G257" s="3" t="s">
         <v>10</v>
@@ -13658,7 +13658,7 @@
         <v>5</v>
       </c>
       <c r="F258" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G258" s="3" t="s">
         <v>10</v>
@@ -13681,7 +13681,7 @@
         <v>5</v>
       </c>
       <c r="F259" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G259" s="3" t="s">
         <v>10</v>
@@ -13704,7 +13704,7 @@
         <v>5</v>
       </c>
       <c r="F260" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G260" s="3" t="s">
         <v>10</v>
@@ -13727,7 +13727,7 @@
         <v>5</v>
       </c>
       <c r="F261" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>10</v>
@@ -13750,7 +13750,7 @@
         <v>5</v>
       </c>
       <c r="F262" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G262" s="3" t="s">
         <v>10</v>
@@ -13796,7 +13796,7 @@
         <v>5</v>
       </c>
       <c r="F264" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G264" s="3" t="s">
         <v>10</v>
@@ -13819,7 +13819,7 @@
         <v>5</v>
       </c>
       <c r="F265" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G265" s="3" t="s">
         <v>10</v>
@@ -13842,7 +13842,7 @@
         <v>5</v>
       </c>
       <c r="F266" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G266" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>11926</v>
+        <v>12026</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>46266</v>
+        <v>46366</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>88778</v>
+        <v>85443</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>2777</v>
+        <v>2977</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3605</v>
+        <v>3805</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>10385</v>
+        <v>10685</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>3509</v>
+        <v>2953</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>16982</v>
+        <v>17182</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>31016</v>
+        <v>31116</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>69344</v>
+        <v>64709</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14506,7 +14506,7 @@
         <v>576</v>
       </c>
       <c r="F28" s="2">
-        <v>28508</v>
+        <v>28608</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>46962</v>
+        <v>47062</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14552,7 +14552,7 @@
         <v>576</v>
       </c>
       <c r="F30" s="2">
-        <v>30743</v>
+        <v>30943</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -14575,7 +14575,7 @@
         <v>576</v>
       </c>
       <c r="F31" s="2">
-        <v>10451</v>
+        <v>10501</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -14598,7 +14598,7 @@
         <v>576</v>
       </c>
       <c r="F32" s="2">
-        <v>11065</v>
+        <v>11115</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -14621,7 +14621,7 @@
         <v>576</v>
       </c>
       <c r="F33" s="2">
-        <v>7375</v>
+        <v>7425</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="2">
-        <v>47778</v>
+        <v>47878</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -14690,7 +14690,7 @@
         <v>576</v>
       </c>
       <c r="F36" s="2">
-        <v>54394</v>
+        <v>54494</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -14759,7 +14759,7 @@
         <v>576</v>
       </c>
       <c r="F39" s="2">
-        <v>5980</v>
+        <v>6080</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -14782,7 +14782,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="2">
-        <v>39216</v>
+        <v>39316</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>40742</v>
+        <v>39878</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>33511</v>
+        <v>32791</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="6">
-        <v>9</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>23</v>
+      <c r="F66" s="2">
+        <v>181</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -15518,7 +15518,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="2">
-        <v>4327</v>
+        <v>3751</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -15541,7 +15541,7 @@
         <v>144</v>
       </c>
       <c r="F73" s="2">
-        <v>3060</v>
+        <v>2484</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>9359</v>
+        <v>8783</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -15587,7 +15587,7 @@
         <v>144</v>
       </c>
       <c r="F75" s="2">
-        <v>2689</v>
+        <v>2113</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -15610,7 +15610,7 @@
         <v>144</v>
       </c>
       <c r="F76" s="2">
-        <v>5087</v>
+        <v>4799</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -15633,7 +15633,7 @@
         <v>144</v>
       </c>
       <c r="F77" s="2">
-        <v>5923</v>
+        <v>4195</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>8881</v>
+        <v>8497</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16757,7 +16757,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="2">
-        <v>15547</v>
+        <v>15259</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -16918,7 +16918,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="2">
-        <v>16286</v>
+        <v>15902</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>183345</v>
+        <v>180465</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>18423</v>
+        <v>17847</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -17953,7 +17953,7 @@
         <v>144</v>
       </c>
       <c r="F100" s="2">
-        <v>16152</v>
+        <v>15720</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -18022,7 +18022,7 @@
         <v>144</v>
       </c>
       <c r="F103" s="2">
-        <v>16836</v>
+        <v>16260</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -18045,7 +18045,7 @@
         <v>144</v>
       </c>
       <c r="F104" s="2">
-        <v>6667</v>
+        <v>6091</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>10</v>
@@ -18068,7 +18068,7 @@
         <v>144</v>
       </c>
       <c r="F105" s="2">
-        <v>7186</v>
+        <v>6610</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="2">
-        <v>16653</v>
+        <v>15501</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -18206,7 +18206,7 @@
         <v>192</v>
       </c>
       <c r="F111" s="2">
-        <v>21114</v>
+        <v>18810</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -18298,7 +18298,7 @@
         <v>192</v>
       </c>
       <c r="F115" s="2">
-        <v>16122</v>
+        <v>15354</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>10</v>
@@ -18321,7 +18321,7 @@
         <v>192</v>
       </c>
       <c r="F116" s="2">
-        <v>6191</v>
+        <v>5231</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -18367,7 +18367,7 @@
         <v>192</v>
       </c>
       <c r="F118" s="2">
-        <v>4019</v>
+        <v>3443</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -18413,7 +18413,7 @@
         <v>192</v>
       </c>
       <c r="F120" s="6">
-        <v>788</v>
+        <v>212</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>23</v>
@@ -18459,7 +18459,7 @@
         <v>192</v>
       </c>
       <c r="F122" s="2">
-        <v>2338</v>
+        <v>1954</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>10</v>
@@ -18482,7 +18482,7 @@
         <v>192</v>
       </c>
       <c r="F123" s="2">
-        <v>18692</v>
+        <v>16388</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>10</v>
@@ -18505,7 +18505,7 @@
         <v>192</v>
       </c>
       <c r="F124" s="2">
-        <v>5058</v>
+        <v>4482</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -18551,7 +18551,7 @@
         <v>192</v>
       </c>
       <c r="F126" s="2">
-        <v>2481</v>
+        <v>1905</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>1823</v>
+        <v>1723</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>106816</v>
+        <v>107016</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>23626</v>
+        <v>23726</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>43250</v>
+        <v>34766</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>20573</v>
+        <v>20093</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>5602</v>
+        <v>5122</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>97161</v>
+        <v>88677</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>1615</v>
+        <v>1715</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10579</v>
+        <v>10679</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>8357</v>
+        <v>8457</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9533</v>
+        <v>9633</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9816</v>
+        <v>9916</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>7343</v>
+        <v>7443</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="6">
-        <v>566</v>
+        <v>611</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>23</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>8367</v>
+        <v>8467</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>2334</v>
+        <v>1902</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20687,7 +20687,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>4537</v>
+        <v>1657</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -20710,7 +20710,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>5931</v>
+        <v>5451</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -20870,11 +20870,11 @@
       <c r="E82">
         <v>144</v>
       </c>
-      <c r="F82" s="2">
-        <v>1302</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="F82" s="6">
+        <v>438</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -21193,7 +21193,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>32228</v>
+        <v>31652</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>27312</v>
+        <v>27512</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>29208</v>
+        <v>29408</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22196,7 +22196,7 @@
         <v>384</v>
       </c>
       <c r="F4" s="2">
-        <v>20951</v>
+        <v>21151</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>58709</v>
+        <v>58909</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22242,7 +22242,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="2">
-        <v>87204</v>
+        <v>87404</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22265,7 +22265,7 @@
         <v>384</v>
       </c>
       <c r="F7" s="2">
-        <v>49616</v>
+        <v>49816</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -22287,11 +22287,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="6">
-        <v>531</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>23</v>
+      <c r="F8" s="2">
+        <v>731</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -22311,7 +22311,7 @@
         <v>144</v>
       </c>
       <c r="F9" s="2">
-        <v>22790</v>
+        <v>22990</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>17355</v>
+        <v>17455</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>84758</v>
+        <v>84858</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>7079</v>
+        <v>7179</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>22492</v>
+        <v>22292</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>45451</v>
+        <v>45526</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>213402</v>
+        <v>213502</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>7225</v>
+        <v>7300</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>135402</v>
+        <v>135502</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>47050</v>
+        <v>47150</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>47899</v>
+        <v>47999</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>180030</v>
+        <v>179910</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>105720</v>
+        <v>105864</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>9704</v>
+        <v>10712</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -15242,7 +15242,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>8499</v>
+        <v>6699</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
-        <v>109</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="6">
-        <v>4</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>23</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -17837,11 +17837,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="6">
-        <v>2</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>40526</v>
+        <v>39526</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>209496</v>
+        <v>207996</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>6785</v>
+        <v>5785</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>42291</v>
+        <v>41291</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>19515</v>
+        <v>19415</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>31996</v>
+        <v>30996</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>38908</v>
+        <v>37908</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9449,7 +9449,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="2">
-        <v>22270</v>
+        <v>22170</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="2">
-        <v>1098</v>
+        <v>998</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>41514</v>
+        <v>41414</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>41884</v>
+        <v>41784</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -11772,7 +11772,7 @@
         <v>48</v>
       </c>
       <c r="F176" s="6">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>23</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="F177" s="6">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>23</v>
@@ -11818,7 +11818,7 @@
         <v>48</v>
       </c>
       <c r="F178" s="2">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>7671</v>
+        <v>7543</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>88857</v>
+        <v>88425</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>82533</v>
+        <v>82245</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>2809</v>
+        <v>2713</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>101544</v>
+        <v>101256</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>23722</v>
+        <v>23602</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>18881</v>
+        <v>18281</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>2110</v>
+        <v>1510</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>30791</v>
+        <v>32291</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>1494</v>
+        <v>1894</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>1593</v>
+        <v>1793</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>10457</v>
+        <v>10657</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>3485</v>
+        <v>3685</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>5404</v>
+        <v>5704</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>11536</v>
+        <v>11936</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2613</v>
+        <v>2713</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>803</v>
+        <v>903</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="6">
-        <v>317</v>
+        <v>417</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -9012,7 +9012,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="2">
-        <v>5882</v>
+        <v>5982</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -9333,11 +9333,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-      <c r="F70" s="6">
-        <v>467</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>23</v>
+      <c r="F70" s="2">
+        <v>2067</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>13452</v>
+        <v>13451</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -13931,7 +13931,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="6">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>82064</v>
+        <v>82062</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>30807</v>
+        <v>30805</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15860,7 +15860,7 @@
         <v>144</v>
       </c>
       <c r="F9" s="2">
-        <v>12528</v>
+        <v>12527</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -20664,7 +20664,7 @@
         <v>240</v>
       </c>
       <c r="F73" s="2">
-        <v>10335</v>
+        <v>10333</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -21101,7 +21101,7 @@
         <v>144</v>
       </c>
       <c r="F92" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>23</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>71885</v>
+        <v>71883</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>20490</v>
+        <v>20488</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>19312</v>
+        <v>19112</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>4445</v>
+        <v>4345</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>2155</v>
+        <v>2055</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>18902</v>
+        <v>18702</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>4616</v>
+        <v>4416</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>21759</v>
+        <v>21659</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>3105</v>
+        <v>3005</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="6">
-        <v>218</v>
+        <v>118</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>23</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>6336</v>
+        <v>6236</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8897,7 +8897,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -11127,11 +11127,11 @@
       <c r="E148">
         <v>12</v>
       </c>
-      <c r="F148" s="6">
-        <v>40</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>23</v>
+      <c r="F148" s="4">
+        <v>0</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>2469</v>
+        <v>2253</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14506,7 +14506,7 @@
         <v>576</v>
       </c>
       <c r="F28" s="2">
-        <v>28604</v>
+        <v>28028</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>46482</v>
+        <v>47058</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>30805</v>
+        <v>30489</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>65152</v>
+        <v>64864</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>10190</v>
+        <v>9998</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -17147,11 +17147,11 @@
       <c r="E65">
         <v>200</v>
       </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>19</v>
+      <c r="F65" s="6">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>23</v>
@@ -17608,7 +17608,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="6">
-        <v>1906</v>
+        <v>2196</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>23</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>12068</v>
+        <v>12066</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17677,7 +17677,7 @@
         <v>576</v>
       </c>
       <c r="F88" s="2">
-        <v>3634</v>
+        <v>3624</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -17723,7 +17723,7 @@
         <v>576</v>
       </c>
       <c r="F90" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>23</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10423</v>
+        <v>10273</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>80564</v>
+        <v>80408</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>81039</v>
+        <v>80967</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>60045</v>
+        <v>59865</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>8421</v>
+        <v>8037</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2">
-        <v>14412</v>
+        <v>14028</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -16987,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="2">
-        <v>2780</v>
+        <v>2684</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -17010,7 +17010,7 @@
         <v>48</v>
       </c>
       <c r="F59" s="2">
-        <v>5901</v>
+        <v>5853</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -19422,7 +19422,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="2">
-        <v>4224</v>
+        <v>4204</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>198926</v>
+        <v>198854</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22038,7 +22038,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="2">
-        <v>663</v>
+        <v>603</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -22061,7 +22061,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="2">
-        <v>553</v>
+        <v>493</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>21341</v>
+        <v>11341</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>7296</v>
+        <v>6796</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>6198</v>
+        <v>5698</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8436,11 +8436,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="2">
-        <v>505</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="F31" s="6">
+        <v>5</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>16130</v>
+        <v>15630</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>2906</v>
+        <v>2406</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>14546</v>
+        <v>14046</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>17629</v>
+        <v>17129</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>990</v>
+        <v>490</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>5736</v>
+        <v>5236</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="6">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>23</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>24389</v>
+        <v>24353</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>3235</v>
+        <v>3210</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>18549</v>
+        <v>18546</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>5698</v>
+        <v>5695</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>15630</v>
+        <v>15605</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>14046</v>
+        <v>14043</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>5236</v>
+        <v>5233</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>36008</v>
+        <v>35958</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="2">
-        <v>45745</v>
+        <v>45695</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="2">
-        <v>998</v>
+        <v>948</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>40784</v>
+        <v>40764</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="2">
-        <v>37349</v>
+        <v>37339</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -9633,7 +9633,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="2">
-        <v>10505</v>
+        <v>10495</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>10</v>
@@ -9678,11 +9678,11 @@
       <c r="E85">
         <v>100</v>
       </c>
-      <c r="F85" s="6">
-        <v>13</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>23</v>
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,7 +9748,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="2">
-        <v>5968</v>
+        <v>5948</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -9771,7 +9771,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="2">
-        <v>12293</v>
+        <v>12283</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -9794,7 +9794,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>7600</v>
+        <v>7597</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -9863,7 +9863,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="2">
-        <v>10346</v>
+        <v>10333</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -9909,7 +9909,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="2">
-        <v>5123</v>
+        <v>5120</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>80264</v>
+        <v>80258</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>46150</v>
+        <v>46114</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14230,7 +14230,7 @@
         <v>144</v>
       </c>
       <c r="F16" s="2">
-        <v>11187</v>
+        <v>11181</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>2037</v>
+        <v>2013</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>10561</v>
+        <v>10537</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>2593</v>
+        <v>2569</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>16952</v>
+        <v>16904</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>31053</v>
+        <v>31005</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>34149</v>
+        <v>34143</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -15745,7 +15745,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="2">
-        <v>24446</v>
+        <v>24440</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -15790,11 +15790,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="6">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -15860,7 +15860,7 @@
         <v>144</v>
       </c>
       <c r="F9" s="2">
-        <v>12527</v>
+        <v>12521</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -15906,7 +15906,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>5099</v>
+        <v>5093</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -15929,7 +15929,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>8163</v>
+        <v>8157</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -15952,7 +15952,7 @@
         <v>144</v>
       </c>
       <c r="F13" s="6">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>23</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>5308</v>
+        <v>5302</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>8013</v>
+        <v>7437</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>8387</v>
+        <v>8363</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16159,7 +16159,7 @@
         <v>192</v>
       </c>
       <c r="F22" s="6">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>23</v>
@@ -16227,11 +16227,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
-        <v>8</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>11941</v>
+        <v>11869</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>11538</v>
+        <v>11526</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -19330,7 +19330,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>23</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>23</v>
@@ -19422,7 +19422,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="2">
-        <v>4164</v>
+        <v>4161</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -19560,7 +19560,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="2">
-        <v>12763</v>
+        <v>12761</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5129</v>
+        <v>5126</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="6">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>23</v>
@@ -22038,7 +22038,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="2">
-        <v>603</v>
+        <v>363</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -22061,7 +22061,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="2">
-        <v>493</v>
+        <v>253</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -11357,11 +11357,11 @@
       <c r="E158">
         <v>24</v>
       </c>
-      <c r="F158" s="4">
-        <v>0</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>19</v>
+      <c r="F158" s="6">
+        <v>5</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>17081</v>
+        <v>16937</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>14263</v>
+        <v>14258</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -13931,7 +13931,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="6">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>31005</v>
+        <v>31000</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>6878</v>
+        <v>6873</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -16803,7 +16803,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>12202</v>
+        <v>12197</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -17999,7 +17999,7 @@
         <v>144</v>
       </c>
       <c r="F102" s="2">
-        <v>17800</v>
+        <v>17795</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -18114,7 +18114,7 @@
         <v>144</v>
       </c>
       <c r="F107" s="2">
-        <v>19857</v>
+        <v>19852</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>89602</v>
+        <v>89597</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -20687,7 +20687,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>113387</v>
+        <v>113382</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22242,7 +22242,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="2">
-        <v>87404</v>
+        <v>87399</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>70890</v>
+        <v>70885</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22791,7 +22791,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="2">
-        <v>3447</v>
+        <v>3442</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>114080</v>
+        <v>113930</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>1341</v>
+        <v>965</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8989,7 +8989,7 @@
         <v>100</v>
       </c>
       <c r="F55" s="2">
-        <v>2386</v>
+        <v>2341</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>59865</v>
+        <v>59779</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>29697</v>
+        <v>29662</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15242,7 +15242,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>6699</v>
+        <v>6079</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="2">
-        <v>355</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>1521</v>
+        <v>1202</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17240,7 +17240,7 @@
         <v>200</v>
       </c>
       <c r="F69" s="2">
-        <v>23319</v>
+        <v>23212</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>89909</v>
+        <v>88265</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="2">
-        <v>8589</v>
+        <v>8586</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="2">
-        <v>3519</v>
+        <v>3516</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -14230,7 +14230,7 @@
         <v>144</v>
       </c>
       <c r="F16" s="2">
-        <v>11181</v>
+        <v>11178</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>64516</v>
+        <v>64510</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15790,11 +15790,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
+      <c r="F6" s="6">
+        <v>9</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -15814,7 +15814,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>15440</v>
+        <v>15437</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="2">
-        <v>14607</v>
+        <v>14604</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>7437</v>
+        <v>7434</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2">
-        <v>14028</v>
+        <v>14025</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>8363</v>
+        <v>8357</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>54536</v>
+        <v>54516</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>81978</v>
+        <v>81954</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>50060</v>
+        <v>49100</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>66273</v>
+        <v>65793</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>9882</v>
+        <v>9832</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>3235</v>
+        <v>3185</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>5154</v>
+        <v>5104</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>11311</v>
+        <v>11211</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1512</v>
+        <v>1462</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="2">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>10</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="F235" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>10</v>
@@ -13221,7 +13221,7 @@
         <v>5</v>
       </c>
       <c r="F239" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1535</v>
+        <v>1505</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -13428,7 +13428,7 @@
         <v>5</v>
       </c>
       <c r="F248" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>20040</v>
+        <v>19640</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>61346</v>
+        <v>65346</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6809,11 +6809,11 @@
       <c r="E7">
         <v>25</v>
       </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>19</v>
+      <c r="F7" s="6">
+        <v>75</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>107172</v>
+        <v>106672</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>13295</v>
+        <v>13245</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>965</v>
+        <v>865</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>13958</v>
+        <v>13708</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>1333</v>
+        <v>1283</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>3185</v>
+        <v>3135</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>1690</v>
+        <v>1540</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="6">
-        <v>5</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
+      <c r="F15" s="2">
+        <v>3005</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1462</v>
+        <v>1412</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8183,11 +8183,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>19</v>
+      <c r="F20" s="2">
+        <v>1500</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="6">
-        <v>18</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>23</v>
+      <c r="F21" s="2">
+        <v>1518</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>15887</v>
+        <v>15787</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>3207</v>
+        <v>3107</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>18521</v>
+        <v>18371</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>5442</v>
+        <v>5842</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8436,11 +8436,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>19</v>
+      <c r="F31" s="2">
+        <v>500</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3850</v>
+        <v>3750</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>15596</v>
+        <v>15996</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>2406</v>
+        <v>2806</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>14043</v>
+        <v>14443</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>17129</v>
+        <v>17529</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>487</v>
+        <v>387</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>5233</v>
+        <v>5133</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>5252</v>
+        <v>5152</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -8989,7 +8989,7 @@
         <v>100</v>
       </c>
       <c r="F55" s="2">
-        <v>2341</v>
+        <v>2321</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -9150,7 +9150,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="2">
-        <v>2606</v>
+        <v>2586</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -9333,11 +9333,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-      <c r="F70" s="2">
-        <v>1267</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="6">
+        <v>467</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -11311,11 +11311,11 @@
       <c r="E156">
         <v>6</v>
       </c>
-      <c r="F156" s="4">
-        <v>0</v>
-      </c>
-      <c r="G156" s="5" t="s">
-        <v>19</v>
+      <c r="F156" s="6">
+        <v>4</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>204267</v>
+        <v>199267</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -13931,7 +13931,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="6">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>77027</v>
+        <v>76977</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>39661</v>
+        <v>39660</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>1059</v>
+        <v>1028</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>7906</v>
+        <v>7900</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="6">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>23</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9321</v>
+        <v>9177</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6843</v>
+        <v>6699</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="6">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>23</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>113370</v>
+        <v>113320</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>198770</v>
+        <v>198575</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>22314</v>
+        <v>21986</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>70714</v>
+        <v>70334</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>13483</v>
+        <v>13183</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7908,7 +7908,7 @@
         <v>50</v>
       </c>
       <c r="F8" s="2">
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>2905</v>
+        <v>2955</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>5004</v>
+        <v>5054</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>11061</v>
+        <v>11111</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>718</v>
+        <v>1468</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>42517</v>
+        <v>42167</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>15287</v>
+        <v>15087</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>17871</v>
+        <v>17671</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>5842</v>
+        <v>5792</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="6">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>23</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>15496</v>
+        <v>15346</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>2556</v>
+        <v>2256</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>14418</v>
+        <v>14268</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>17029</v>
+        <v>16629</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>5052</v>
+        <v>5002</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2613</v>
+        <v>2588</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8874,7 +8874,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="2">
-        <v>1873</v>
+        <v>1848</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -13931,7 +13931,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="6">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>76617</v>
+        <v>76557</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -15288,7 +15288,7 @@
         <v>12</v>
       </c>
       <c r="F62" s="2">
-        <v>113</v>
+        <v>1589</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7838,11 +7838,11 @@
       <c r="E5">
         <v>50</v>
       </c>
-      <c r="F5" s="2">
-        <v>865</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="6">
+        <v>15</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8874,7 +8874,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="2">
-        <v>1848</v>
+        <v>1773</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -9103,11 +9103,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="6">
-        <v>145</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>23</v>
+      <c r="F60" s="2">
+        <v>645</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>14514</v>
+        <v>13264</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>56346</v>
+        <v>52096</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>106672</v>
+        <v>105672</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>23</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>13183</v>
+        <v>12683</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>12887</v>
+        <v>12787</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>6310</v>
+        <v>6160</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>2107</v>
+        <v>2007</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>16421</v>
+        <v>16171</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>6737</v>
+        <v>6637</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>5692</v>
+        <v>5492</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>13746</v>
+        <v>13496</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>1556</v>
+        <v>1306</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>13018</v>
+        <v>12818</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>14829</v>
+        <v>14629</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>5033</v>
+        <v>4933</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>3902</v>
+        <v>3752</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>11526</v>
+        <v>11426</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>7900</v>
+        <v>7914</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -19215,7 +19215,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>11027</v>
+        <v>11045</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -19238,7 +19238,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>12551</v>
+        <v>12600</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>2509</v>
+        <v>2536</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5119</v>
+        <v>5179</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>14965</v>
+        <v>14955</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5125</v>
+        <v>5187</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>84581</v>
+        <v>80981</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>21622</v>
+        <v>21562</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>27907</v>
+        <v>27847</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="6">
-        <v>321</v>
+        <v>177</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>23</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>13749</v>
+        <v>13605</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>1091</v>
+        <v>947</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="6">
-        <v>404</v>
+        <v>260</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>23</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="6">
-        <v>438</v>
+        <v>54</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>13264</v>
+        <v>13139</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>48332</v>
+        <v>47372</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>44370</v>
+        <v>42870</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -10645,7 +10645,7 @@
         <v>24</v>
       </c>
       <c r="F127" s="2">
-        <v>162</v>
+        <v>489</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -12807,7 +12807,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="2">
-        <v>3630</v>
+        <v>3330</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>10</v>
@@ -12830,7 +12830,7 @@
         <v>10</v>
       </c>
       <c r="F222" s="2">
-        <v>994</v>
+        <v>894</v>
       </c>
       <c r="G222" s="3" t="s">
         <v>10</v>
@@ -12853,7 +12853,7 @@
         <v>10</v>
       </c>
       <c r="F223" s="2">
-        <v>2255</v>
+        <v>2155</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>10</v>
@@ -12876,7 +12876,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="2">
-        <v>1779</v>
+        <v>1579</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>10</v>
@@ -12899,7 +12899,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>10</v>
@@ -12922,7 +12922,7 @@
         <v>10</v>
       </c>
       <c r="F226" s="2">
-        <v>1996</v>
+        <v>1796</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>10</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="F227" s="2">
-        <v>361</v>
+        <v>261</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>1965</v>
+        <v>525</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>10536</v>
+        <v>9636</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14413,11 +14413,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="2">
-        <v>534</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="F24" s="6">
+        <v>6</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>29373</v>
+        <v>28293</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15518,7 +15518,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="2">
-        <v>3751</v>
+        <v>2023</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>8783</v>
+        <v>7343</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>178607</v>
+        <v>174287</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="2">
-        <v>15381</v>
+        <v>13845</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -18252,7 +18252,7 @@
         <v>192</v>
       </c>
       <c r="F113" s="2">
-        <v>25952</v>
+        <v>24800</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -20134,11 +20134,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="2">
-        <v>947</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="6">
+        <v>83</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20180,11 +20180,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="2">
-        <v>1144</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="F52" s="6">
+        <v>712</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -21055,7 +21055,7 @@
         <v>144</v>
       </c>
       <c r="F90" s="2">
-        <v>14788</v>
+        <v>13060</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>198551</v>
+        <v>197111</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>26538</v>
+        <v>25458</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>8510</v>
+        <v>15410</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>19</v>
+      <c r="F119" s="2">
+        <v>2520</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>51234</v>
+        <v>51184</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>105672</v>
+        <v>105660</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="2">
-        <v>23919</v>
+        <v>23419</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>42770</v>
+        <v>42720</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7908,7 +7908,7 @@
         <v>50</v>
       </c>
       <c r="F8" s="2">
-        <v>790</v>
+        <v>590</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>9732</v>
+        <v>9532</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>3035</v>
+        <v>2835</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>1364</v>
+        <v>1264</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>1440</v>
+        <v>1190</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>3205</v>
+        <v>3005</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>5054</v>
+        <v>4854</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>11111</v>
+        <v>10911</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1362</v>
+        <v>1162</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>1368</v>
+        <v>1168</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8253,7 +8253,7 @@
         <v>50</v>
       </c>
       <c r="F23" s="2">
-        <v>2250</v>
+        <v>2050</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>12686</v>
+        <v>12436</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>6060</v>
+        <v>6010</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>1997</v>
+        <v>1907</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>16156</v>
+        <v>15971</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>6587</v>
+        <v>6537</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3385</v>
+        <v>3400</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>13296</v>
+        <v>13146</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>1291</v>
+        <v>1206</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>12768</v>
+        <v>12618</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>14529</v>
+        <v>14329</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>3752</v>
+        <v>3652</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="6">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>23</v>
@@ -10001,7 +10001,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>23</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>23</v>
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="2">
-        <v>2376</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -11012,11 +11012,11 @@
       <c r="E143">
         <v>24</v>
       </c>
-      <c r="F143" s="6">
-        <v>3</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>23</v>
+      <c r="F143" s="4">
+        <v>0</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -11035,11 +11035,11 @@
       <c r="E144">
         <v>24</v>
       </c>
-      <c r="F144" s="6">
-        <v>2</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
+      <c r="F144" s="4">
+        <v>0</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>1289</v>
+        <v>1241</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>1202</v>
+        <v>1178</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="2">
-        <v>21486</v>
+        <v>21450</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>3149</v>
+        <v>3125</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -11610,11 +11610,11 @@
       <c r="E169">
         <v>36</v>
       </c>
-      <c r="F169" s="6">
-        <v>10</v>
-      </c>
-      <c r="G169" s="7" t="s">
-        <v>23</v>
+      <c r="F169" s="4">
+        <v>0</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -11633,11 +11633,11 @@
       <c r="E170">
         <v>36</v>
       </c>
-      <c r="F170" s="6">
-        <v>2</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>23</v>
+      <c r="F170" s="4">
+        <v>0</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -11703,7 +11703,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="2">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -11726,7 +11726,7 @@
         <v>72</v>
       </c>
       <c r="F174" s="2">
-        <v>1492</v>
+        <v>1480</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>10</v>
@@ -11772,7 +11772,7 @@
         <v>48</v>
       </c>
       <c r="F176" s="6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>23</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="F177" s="6">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>23</v>
@@ -11818,7 +11818,7 @@
         <v>48</v>
       </c>
       <c r="F178" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -12209,7 +12209,7 @@
         <v>48</v>
       </c>
       <c r="F195" s="2">
-        <v>870</v>
+        <v>846</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>110934</v>
+        <v>110929</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>197767</v>
+        <v>197667</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -13612,7 +13612,7 @@
         <v>100</v>
       </c>
       <c r="F256" s="2">
-        <v>90335</v>
+        <v>90235</v>
       </c>
       <c r="G256" s="3" t="s">
         <v>10</v>
@@ -13931,7 +13931,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="6">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>75981</v>
+        <v>75957</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>28077</v>
+        <v>28065</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15929,7 +15929,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>8155</v>
+        <v>8143</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>2410</v>
+        <v>2404</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>8282</v>
+        <v>8276</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>1029</v>
+        <v>885</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>174257</v>
+        <v>174245</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10643</v>
+        <v>10642</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>8433</v>
+        <v>8432</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9069</v>
+        <v>9068</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9364</v>
+        <v>9363</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6663</v>
+        <v>6662</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>23</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>23</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="6">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>23</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>113392</v>
+        <v>113380</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>59099</v>
+        <v>59095</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22975,7 +22975,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="6">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>23</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>51184</v>
+        <v>57584</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>54511</v>
+        <v>52511</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>111230</v>
+        <v>110230</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>12433</v>
+        <v>12133</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7884,11 +7884,11 @@
       <c r="E7">
         <v>50</v>
       </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>19</v>
+      <c r="F7" s="6">
+        <v>4</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8229,11 +8229,11 @@
       <c r="E22">
         <v>50</v>
       </c>
-      <c r="F22" s="6">
-        <v>18</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>23</v>
+      <c r="F22" s="2">
+        <v>2118</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>40567</v>
+        <v>40517</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>1907</v>
+        <v>1897</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>15971</v>
+        <v>15956</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>5392</v>
+        <v>5382</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3400</v>
+        <v>3385</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>1206</v>
+        <v>1191</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="6">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>23</v>
@@ -10000,11 +10000,11 @@
       <c r="E99">
         <v>120</v>
       </c>
-      <c r="F99" s="6">
-        <v>6</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>23</v>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>23</v>
@@ -14413,11 +14413,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>19</v>
+      <c r="F24" s="6">
+        <v>6</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>413</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -15790,11 +15790,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
+      <c r="F6" s="6">
+        <v>6</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>17424</v>
+        <v>17280</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>107230</v>
+        <v>106230</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5420</v>
+        <v>4920</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>10</v>
@@ -13336,7 +13336,7 @@
         <v>5</v>
       </c>
       <c r="F244" s="2">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G244" s="3" t="s">
         <v>10</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="2">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -13428,7 +13428,7 @@
         <v>5</v>
       </c>
       <c r="F248" s="2">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>10</v>
@@ -13474,7 +13474,7 @@
         <v>5</v>
       </c>
       <c r="F250" s="2">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>10</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="2">
-        <v>14604</v>
+        <v>14556</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>7434</v>
+        <v>7410</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16158,11 +16158,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="6">
-        <v>59</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>23</v>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>11866</v>
+        <v>11794</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16274,7 +16274,7 @@
         <v>192</v>
       </c>
       <c r="F27" s="2">
-        <v>30250</v>
+        <v>30214</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>9962</v>
+        <v>9878</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>284</v>
+        <v>1484</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>13143</v>
+        <v>13113</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -9150,7 +9150,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="2">
-        <v>2586</v>
+        <v>2521</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>7986</v>
+        <v>7983</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>46501</v>
+        <v>46357</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>17607</v>
+        <v>17247</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>42710</v>
+        <v>42210</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>40517</v>
+        <v>40117</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>34658</v>
+        <v>34058</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9380,7 +9380,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="2">
-        <v>25347</v>
+        <v>24747</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>9574</v>
+        <v>9214</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -17355,7 +17355,7 @@
         <v>200</v>
       </c>
       <c r="F74" s="6">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>23</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>52116</v>
+        <v>51296</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>76229</v>
+        <v>73349</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>17558</v>
+        <v>16406</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>50134</v>
+        <v>49834</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>17247</v>
+        <v>17197</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>20582</v>
+        <v>20502</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="6">
-        <v>1779</v>
+        <v>1679</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>23</v>
@@ -9334,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="6">
-        <v>467</v>
+        <v>367</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>23</v>
@@ -9403,7 +9403,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="2">
-        <v>15312</v>
+        <v>15262</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="2">
-        <v>45495</v>
+        <v>45445</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -9471,11 +9471,11 @@
       <c r="E76">
         <v>100</v>
       </c>
-      <c r="F76" s="2">
-        <v>548</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="F76" s="6">
+        <v>498</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>39864</v>
+        <v>39814</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>40664</v>
+        <v>40614</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="2">
-        <v>36839</v>
+        <v>36789</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -9587,7 +9587,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="2">
-        <v>9187</v>
+        <v>9137</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -9702,7 +9702,7 @@
         <v>100</v>
       </c>
       <c r="F86" s="2">
-        <v>36623</v>
+        <v>36573</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -9725,7 +9725,7 @@
         <v>100</v>
       </c>
       <c r="F87" s="2">
-        <v>8379</v>
+        <v>8329</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -9748,7 +9748,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="2">
-        <v>5948</v>
+        <v>5898</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -9771,7 +9771,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="2">
-        <v>12283</v>
+        <v>12233</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -10438,7 +10438,7 @@
         <v>24</v>
       </c>
       <c r="F118" s="2">
-        <v>1834</v>
+        <v>1738</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -10760,7 +10760,7 @@
         <v>24</v>
       </c>
       <c r="F132" s="2">
-        <v>9592</v>
+        <v>9568</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>10</v>
@@ -10806,7 +10806,7 @@
         <v>24</v>
       </c>
       <c r="F134" s="2">
-        <v>4889</v>
+        <v>4865</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -10921,7 +10921,7 @@
         <v>30</v>
       </c>
       <c r="F139" s="6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>23</v>
@@ -10967,7 +10967,7 @@
         <v>30</v>
       </c>
       <c r="F141" s="6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>23</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>650</v>
+        <v>602</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -12163,7 +12163,7 @@
         <v>40</v>
       </c>
       <c r="F193" s="2">
-        <v>8394</v>
+        <v>8370</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -12186,7 +12186,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="6">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>23</v>
@@ -12209,7 +12209,7 @@
         <v>48</v>
       </c>
       <c r="F195" s="2">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>16578</v>
+        <v>16518</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>59299</v>
+        <v>59239</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14897,7 +14897,7 @@
         <v>72</v>
       </c>
       <c r="F45" s="2">
-        <v>22071</v>
+        <v>21999</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -15518,7 +15518,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="2">
-        <v>1159</v>
+        <v>1039</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -15541,7 +15541,7 @@
         <v>144</v>
       </c>
       <c r="F73" s="2">
-        <v>1044</v>
+        <v>924</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>7343</v>
+        <v>7223</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>11548</v>
+        <v>11500</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>1681</v>
+        <v>1633</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16895,7 +16895,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="2">
-        <v>3816</v>
+        <v>3768</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -16918,7 +16918,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="2">
-        <v>15324</v>
+        <v>15276</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -16941,7 +16941,7 @@
         <v>96</v>
       </c>
       <c r="F56" s="2">
-        <v>23290</v>
+        <v>23242</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -16964,7 +16964,7 @@
         <v>96</v>
       </c>
       <c r="F57" s="2">
-        <v>21678</v>
+        <v>21630</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -17033,7 +17033,7 @@
         <v>48</v>
       </c>
       <c r="F60" s="2">
-        <v>5083</v>
+        <v>5035</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>3207</v>
+        <v>3087</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>15332</v>
+        <v>15272</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -20778,11 +20778,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="6">
-        <v>72</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>23</v>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -21305,7 +21305,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2">
-        <v>64269</v>
+        <v>64125</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -22287,11 +22287,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="6">
-        <v>143</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>23</v>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>65192</v>
+        <v>65072</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>14338</v>
+        <v>14138</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>19</v>
+      <c r="F119" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="4">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>19</v>
+      <c r="F62" s="2">
+        <v>756</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>19</v>
+      <c r="F66" s="2">
+        <v>756</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>792</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6809,11 +6809,11 @@
       <c r="E7">
         <v>25</v>
       </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>19</v>
+      <c r="F7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>45157</v>
+        <v>45013</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>63909</v>
+        <v>63765</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>102545</v>
+        <v>101545</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>105660</v>
+        <v>105060</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>25978</v>
+        <v>25878</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>1324</v>
+        <v>1180</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>13113</v>
+        <v>12969</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -7838,11 +7838,11 @@
       <c r="E5">
         <v>50</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>19</v>
+      <c r="F5" s="2">
+        <v>3893</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8183,11 +8183,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>19</v>
+      <c r="F20" s="2">
+        <v>2191</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>19</v>
+      <c r="F21" s="2">
+        <v>1550</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="6">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>23</v>
@@ -10921,7 +10921,7 @@
         <v>30</v>
       </c>
       <c r="F139" s="6">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>23</v>
@@ -10967,7 +10967,7 @@
         <v>30</v>
       </c>
       <c r="F141" s="6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>23</v>
@@ -11381,7 +11381,7 @@
         <v>24</v>
       </c>
       <c r="F159" s="6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>23</v>
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>598</v>
+        <v>550</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>602</v>
+        <v>554</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11496,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>23</v>
@@ -11519,7 +11519,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="2">
-        <v>608</v>
+        <v>560</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>6631</v>
+        <v>6567</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -12669,7 +12669,7 @@
         <v>600</v>
       </c>
       <c r="F215" s="2">
-        <v>5779</v>
+        <v>5479</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1505</v>
+        <v>1455</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="2">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>10</v>
@@ -13336,7 +13336,7 @@
         <v>5</v>
       </c>
       <c r="F244" s="2">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="G244" s="3" t="s">
         <v>10</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="2">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -13428,7 +13428,7 @@
         <v>5</v>
       </c>
       <c r="F248" s="2">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>10</v>
@@ -13474,7 +13474,7 @@
         <v>5</v>
       </c>
       <c r="F250" s="2">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>110769</v>
+        <v>109891</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>1407</v>
+        <v>1335</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>68996</v>
+        <v>68946</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>6687</v>
+        <v>6421</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14092,7 +14092,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>935</v>
+        <v>899</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>74847</v>
+        <v>73623</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="6">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>23</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>26597</v>
+        <v>25877</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>61042</v>
+        <v>60466</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>31491</v>
+        <v>31203</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -15745,7 +15745,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="2">
-        <v>24577</v>
+        <v>24001</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>1633</v>
+        <v>1489</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>7759</v>
+        <v>7663</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17079,7 +17079,7 @@
         <v>576</v>
       </c>
       <c r="F62" s="2">
-        <v>14961</v>
+        <v>13809</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -17102,7 +17102,7 @@
         <v>576</v>
       </c>
       <c r="F63" s="2">
-        <v>4156</v>
+        <v>3580</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="6">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>23</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>51296</v>
+        <v>50496</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -17470,7 +17470,7 @@
         <v>200</v>
       </c>
       <c r="F79" s="2">
-        <v>1713</v>
+        <v>1313</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>174171</v>
+        <v>174051</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="6">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10323</v>
+        <v>10223</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>2495</v>
+        <v>2459</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19330,7 +19330,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="6">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>23</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>23</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5161</v>
+        <v>5125</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>4909</v>
+        <v>4873</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>58760</v>
+        <v>58616</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>15156</v>
+        <v>15096</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10450</v>
+        <v>10306</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>8240</v>
+        <v>8096</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8996</v>
+        <v>8852</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9303</v>
+        <v>9159</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6530</v>
+        <v>6386</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>8023</v>
+        <v>7879</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>13521</v>
+        <v>13377</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>5673</v>
+        <v>5529</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>23</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>2088</v>
+        <v>1608</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="6">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>23</v>
@@ -20503,7 +20503,7 @@
         <v>12</v>
       </c>
       <c r="F66" s="2">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -20526,7 +20526,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="6">
-        <v>6</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>23</v>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20572,7 +20572,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="2">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -20594,11 +20594,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="6">
-        <v>9</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>23</v>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>111724</v>
+        <v>111580</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>195209</v>
+        <v>194777</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>81954</v>
+        <v>79650</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>8108</v>
+        <v>8083</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>47334</v>
+        <v>47310</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>45013</v>
+        <v>44989</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>63765</v>
+        <v>63759</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>20502</v>
+        <v>20391</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -7520,7 +7520,7 @@
         <v>300</v>
       </c>
       <c r="F23" s="6">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>23</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>42170</v>
+        <v>41920</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>3893</v>
+        <v>2093</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>1655</v>
+        <v>1505</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>8306</v>
+        <v>8278</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>13832</v>
+        <v>13805</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>5587</v>
+        <v>5581</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3135</v>
+        <v>3110</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>10540</v>
+        <v>10490</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>10568</v>
+        <v>10543</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>13567</v>
+        <v>13542</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>4783</v>
+        <v>4755</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>1849</v>
+        <v>1843</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -11311,11 +11311,11 @@
       <c r="E156">
         <v>6</v>
       </c>
-      <c r="F156" s="2">
-        <v>76</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>10</v>
+      <c r="F156" s="6">
+        <v>16</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="2">
-        <v>325</v>
+        <v>235</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11473,7 +11473,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>23</v>
@@ -11519,7 +11519,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="2">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>6567</v>
+        <v>6564</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>109891</v>
+        <v>109881</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -13612,7 +13612,7 @@
         <v>100</v>
       </c>
       <c r="F256" s="2">
-        <v>90235</v>
+        <v>90173</v>
       </c>
       <c r="G256" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>45385</v>
+        <v>45241</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>73623</v>
+        <v>73611</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14897,7 +14897,7 @@
         <v>72</v>
       </c>
       <c r="F45" s="2">
-        <v>21999</v>
+        <v>21783</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>37338</v>
+        <v>37194</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -15035,7 +15035,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="2">
-        <v>23567</v>
+        <v>23552</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -15081,7 +15081,7 @@
         <v>360</v>
       </c>
       <c r="F53" s="2">
-        <v>39493</v>
+        <v>39478</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -15768,7 +15768,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>23</v>
@@ -15906,7 +15906,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>4659</v>
+        <v>4647</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -16044,7 +16044,7 @@
         <v>192</v>
       </c>
       <c r="F17" s="2">
-        <v>13828</v>
+        <v>13252</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="2">
-        <v>14553</v>
+        <v>13977</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -16274,7 +16274,7 @@
         <v>192</v>
       </c>
       <c r="F27" s="2">
-        <v>30214</v>
+        <v>30208</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>11317</v>
+        <v>11311</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="2">
-        <v>29518</v>
+        <v>29512</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>7663</v>
+        <v>7654</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17170,11 +17170,11 @@
       <c r="E66">
         <v>200</v>
       </c>
-      <c r="F66" s="2">
-        <v>1002</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="6">
+        <v>992</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>1</v>
+        <v>577</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>174051</v>
+        <v>173331</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10223</v>
+        <v>10221</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19238,7 +19238,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>12558</v>
+        <v>12557</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>14835</v>
+        <v>14833</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>58616</v>
+        <v>57812</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>18202</v>
+        <v>18196</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>27595</v>
+        <v>27589</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8852</v>
+        <v>8840</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9159</v>
+        <v>9147</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6386</v>
+        <v>6374</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -21463,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -21578,7 +21578,7 @@
         <v>48</v>
       </c>
       <c r="F10" s="2">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -21601,7 +21601,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="2">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -21624,7 +21624,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="2">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -21647,7 +21647,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="2">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>14390</v>
+        <v>14378</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>23714</v>
+        <v>23330</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>63956</v>
+        <v>62829</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>14132</v>
+        <v>13932</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>47310</v>
+        <v>46710</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>44989</v>
+        <v>44557</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>17197</v>
+        <v>17143</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>20391</v>
+        <v>20386</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>101545</v>
+        <v>102095</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7244,7 +7244,7 @@
         <v>96</v>
       </c>
       <c r="F11" s="6">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>23</v>
@@ -7267,7 +7267,7 @@
         <v>96</v>
       </c>
       <c r="F12" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>23</v>
@@ -7290,7 +7290,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="2">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>25878</v>
+        <v>25818</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>12969</v>
+        <v>12966</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>10293</v>
+        <v>10283</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>10283</v>
+        <v>9958</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="2">
-        <v>1626</v>
+        <v>1426</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>1505</v>
+        <v>1105</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>2191</v>
+        <v>1991</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>1550</v>
+        <v>1250</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8253,7 +8253,7 @@
         <v>50</v>
       </c>
       <c r="F23" s="2">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>39061</v>
+        <v>38836</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -10507,7 +10507,7 @@
         <v>24</v>
       </c>
       <c r="F121" s="2">
-        <v>4740</v>
+        <v>4596</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>10</v>
@@ -10553,7 +10553,7 @@
         <v>24</v>
       </c>
       <c r="F123" s="2">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>10</v>
@@ -10576,7 +10576,7 @@
         <v>24</v>
       </c>
       <c r="F124" s="2">
-        <v>8509</v>
+        <v>8507</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -10714,7 +10714,7 @@
         <v>24</v>
       </c>
       <c r="F130" s="2">
-        <v>15141</v>
+        <v>15129</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>10</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="2">
-        <v>20010</v>
+        <v>19900</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>6564</v>
+        <v>6436</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -12186,7 +12186,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="6">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>23</v>
@@ -12208,11 +12208,11 @@
       <c r="E195">
         <v>48</v>
       </c>
-      <c r="F195" s="2">
-        <v>246</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="F195" s="6">
+        <v>186</v>
+      </c>
+      <c r="G195" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -12485,7 +12485,7 @@
         <v>240</v>
       </c>
       <c r="F207" s="2">
-        <v>2771</v>
+        <v>2759</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>10</v>
@@ -12600,7 +12600,7 @@
         <v>720</v>
       </c>
       <c r="F212" s="2">
-        <v>4225</v>
+        <v>4190</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>10</v>
@@ -12623,7 +12623,7 @@
         <v>720</v>
       </c>
       <c r="F213" s="6">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="G213" s="7" t="s">
         <v>23</v>
@@ -12646,7 +12646,7 @@
         <v>720</v>
       </c>
       <c r="F214" s="2">
-        <v>3761</v>
+        <v>3642</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>10</v>
@@ -12669,7 +12669,7 @@
         <v>600</v>
       </c>
       <c r="F215" s="2">
-        <v>5479</v>
+        <v>5419</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>45241</v>
+        <v>45427</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="2">
-        <v>3056</v>
+        <v>3008</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>73611</v>
+        <v>73899</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>8608</v>
+        <v>8605</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14413,11 +14413,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>19</v>
+      <c r="F24" s="6">
+        <v>165</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>16518</v>
+        <v>16482</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -14690,7 +14690,7 @@
         <v>576</v>
       </c>
       <c r="F36" s="2">
-        <v>54566</v>
+        <v>54266</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>37194</v>
+        <v>37170</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>25877</v>
+        <v>25619</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>60466</v>
+        <v>60406</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>31203</v>
+        <v>31143</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -15790,11 +15790,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="6">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -15814,7 +15814,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>14269</v>
+        <v>14245</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -15952,7 +15952,7 @@
         <v>144</v>
       </c>
       <c r="F13" s="6">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>23</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>6891</v>
+        <v>6879</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>4954</v>
+        <v>4930</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>11311</v>
+        <v>11203</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>8330</v>
+        <v>8306</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>7654</v>
+        <v>7534</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -16895,7 +16895,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="2">
-        <v>3762</v>
+        <v>3594</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -16987,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="2">
-        <v>2705</v>
+        <v>2657</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -17010,7 +17010,7 @@
         <v>48</v>
       </c>
       <c r="F59" s="2">
-        <v>5642</v>
+        <v>5636</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -17033,7 +17033,7 @@
         <v>48</v>
       </c>
       <c r="F60" s="2">
-        <v>5035</v>
+        <v>5023</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -17079,7 +17079,7 @@
         <v>576</v>
       </c>
       <c r="F62" s="2">
-        <v>13809</v>
+        <v>13797</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>577</v>
+        <v>373</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -17562,7 +17562,7 @@
         <v>1152</v>
       </c>
       <c r="F83" s="6">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>23</v>
@@ -17608,7 +17608,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="6">
-        <v>3048</v>
+        <v>2844</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>23</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="6">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>23</v>
@@ -18160,7 +18160,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="2">
-        <v>13845</v>
+        <v>13725</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -18206,7 +18206,7 @@
         <v>192</v>
       </c>
       <c r="F111" s="2">
-        <v>18762</v>
+        <v>18690</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -18321,7 +18321,7 @@
         <v>192</v>
       </c>
       <c r="F116" s="2">
-        <v>3215</v>
+        <v>3155</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10221</v>
+        <v>10220</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19123,7 +19123,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="2">
-        <v>7220</v>
+        <v>7148</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>7971</v>
+        <v>7969</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -19215,7 +19215,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>11165</v>
+        <v>11163</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19468,7 +19468,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="2">
-        <v>35373</v>
+        <v>35372</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>14833</v>
+        <v>14831</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>57812</v>
+        <v>57716</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>18196</v>
+        <v>18052</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>1608</v>
+        <v>1572</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20686,11 +20686,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="6">
-        <v>12</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>23</v>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -20710,7 +20710,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>2342</v>
+        <v>2258</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -21032,7 +21032,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="2">
-        <v>6299</v>
+        <v>6263</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -21055,7 +21055,7 @@
         <v>144</v>
       </c>
       <c r="F90" s="2">
-        <v>12136</v>
+        <v>12088</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -21193,7 +21193,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>31568</v>
+        <v>31532</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>194777</v>
+        <v>194705</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21305,7 +21305,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2">
-        <v>64125</v>
+        <v>64113</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>25422</v>
+        <v>25386</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>14378</v>
+        <v>14234</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>23330</v>
+        <v>23318</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22196,7 +22196,7 @@
         <v>384</v>
       </c>
       <c r="F4" s="2">
-        <v>20958</v>
+        <v>20934</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>58807</v>
+        <v>58735</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>17274</v>
+        <v>17190</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>62829</v>
+        <v>62793</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22518,7 +22518,7 @@
         <v>144</v>
       </c>
       <c r="F18" s="2">
-        <v>12672</v>
+        <v>12648</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -22564,7 +22564,7 @@
         <v>144</v>
       </c>
       <c r="F20" s="2">
-        <v>16507</v>
+        <v>16399</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -22675,11 +22675,11 @@
       <c r="E2">
         <v>1000</v>
       </c>
-      <c r="F2" s="6">
-        <v>36</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>23</v>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22745,7 +22745,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="2">
-        <v>5292</v>
+        <v>5092</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>13932</v>
+        <v>13907</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22906,7 +22906,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>11006</v>
+        <v>10981</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>8083</v>
+        <v>6433</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46710</v>
+        <v>44210</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>44557</v>
+        <v>44551</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>63759</v>
+        <v>63753</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>20386</v>
+        <v>20278</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>102095</v>
+        <v>101595</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>25818</v>
+        <v>24218</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>13101</v>
+        <v>13053</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="2">
-        <v>23219</v>
+        <v>23019</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -7658,7 +7658,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>2516</v>
+        <v>2466</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>2093</v>
+        <v>393</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>1435</v>
+        <v>1185</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="2">
-        <v>1426</v>
+        <v>1026</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>1105</v>
+        <v>755</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>1991</v>
+        <v>1791</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>1250</v>
+        <v>950</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>1368</v>
+        <v>1118</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8253,7 +8253,7 @@
         <v>50</v>
       </c>
       <c r="F23" s="2">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>8278</v>
+        <v>7978</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>5556</v>
+        <v>5256</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>647</v>
+        <v>344</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>13805</v>
+        <v>13505</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3110</v>
+        <v>2810</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>10543</v>
+        <v>10240</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>13542</v>
+        <v>13242</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>4755</v>
+        <v>4752</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>1843</v>
+        <v>1543</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G156" s="7" t="s">
         <v>23</v>
@@ -11380,11 +11380,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="6">
-        <v>2</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>23</v>
+      <c r="F159" s="4">
+        <v>0</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>553</v>
+        <v>529</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11519,7 +11519,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="2">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>109881</v>
+        <v>109481</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>6421</v>
+        <v>6385</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>45427</v>
+        <v>45355</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>8589</v>
+        <v>8445</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>73899</v>
+        <v>73839</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>8605</v>
+        <v>8545</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="6">
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>23</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>16482</v>
+        <v>16422</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>30819</v>
+        <v>30759</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>59239</v>
+        <v>59179</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14506,7 +14506,7 @@
         <v>576</v>
       </c>
       <c r="F28" s="2">
-        <v>28604</v>
+        <v>28028</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -14943,7 +14943,7 @@
         <v>288</v>
       </c>
       <c r="F47" s="2">
-        <v>6622</v>
+        <v>6334</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>25619</v>
+        <v>25259</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15012,7 +15012,7 @@
         <v>360</v>
       </c>
       <c r="F50" s="2">
-        <v>8785</v>
+        <v>8695</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -15035,7 +15035,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="2">
-        <v>23552</v>
+        <v>23462</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -15058,7 +15058,7 @@
         <v>360</v>
       </c>
       <c r="F52" s="2">
-        <v>9647</v>
+        <v>9557</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -15081,7 +15081,7 @@
         <v>360</v>
       </c>
       <c r="F53" s="2">
-        <v>39478</v>
+        <v>39388</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -15104,7 +15104,7 @@
         <v>360</v>
       </c>
       <c r="F54" s="2">
-        <v>40859</v>
+        <v>40709</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -15127,7 +15127,7 @@
         <v>360</v>
       </c>
       <c r="F55" s="2">
-        <v>9111</v>
+        <v>9051</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -15150,7 +15150,7 @@
         <v>360</v>
       </c>
       <c r="F56" s="2">
-        <v>31104</v>
+        <v>30954</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -15173,7 +15173,7 @@
         <v>360</v>
       </c>
       <c r="F57" s="2">
-        <v>32054</v>
+        <v>31904</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -15196,7 +15196,7 @@
         <v>360</v>
       </c>
       <c r="F58" s="2">
-        <v>34932</v>
+        <v>34782</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -15265,7 +15265,7 @@
         <v>12</v>
       </c>
       <c r="F61" s="2">
-        <v>1428</v>
+        <v>1368</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -15288,7 +15288,7 @@
         <v>12</v>
       </c>
       <c r="F62" s="2">
-        <v>1956</v>
+        <v>1920</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -15311,7 +15311,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="2">
-        <v>405</v>
+        <v>345</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -15380,7 +15380,7 @@
         <v>12</v>
       </c>
       <c r="F66" s="2">
-        <v>2016</v>
+        <v>1956</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -15403,7 +15403,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="2">
-        <v>1560</v>
+        <v>1524</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -15906,7 +15906,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>4647</v>
+        <v>4575</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>4930</v>
+        <v>4906</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>1486</v>
+        <v>1270</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>7534</v>
+        <v>7342</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="6">
-        <v>992</v>
+        <v>792</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>23</v>
@@ -17240,7 +17240,7 @@
         <v>200</v>
       </c>
       <c r="F69" s="2">
-        <v>23128</v>
+        <v>22928</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -17608,7 +17608,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="6">
-        <v>2844</v>
+        <v>2748</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>23</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>173331</v>
+        <v>173211</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19053,11 +19053,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="6">
-        <v>13</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -19238,7 +19238,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>12557</v>
+        <v>12527</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>2459</v>
+        <v>2444</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19330,7 +19330,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>23</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>23</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5125</v>
+        <v>5115</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19629,7 +19629,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="2">
-        <v>2821</v>
+        <v>2797</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>18052</v>
+        <v>17812</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>27589</v>
+        <v>28569</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>84219</v>
+        <v>84699</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10306</v>
+        <v>10282</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>8096</v>
+        <v>8060</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8840</v>
+        <v>8792</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6374</v>
+        <v>6326</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>7879</v>
+        <v>7843</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>13377</v>
+        <v>13329</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20134,11 +20134,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="6">
-        <v>10</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>23</v>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>2668</v>
+        <v>2572</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>1572</v>
+        <v>1452</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -21305,7 +21305,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2">
-        <v>64113</v>
+        <v>64041</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>25386</v>
+        <v>25314</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>14234</v>
+        <v>13658</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>23318</v>
+        <v>22934</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>17190</v>
+        <v>16806</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>79650</v>
+        <v>79626</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>62793</v>
+        <v>62313</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>36121</v>
+        <v>35641</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>13907</v>
+        <v>13807</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22975,7 +22975,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="6">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>23</v>
@@ -23021,7 +23021,7 @@
         <v>120</v>
       </c>
       <c r="F17" s="2">
-        <v>2198</v>
+        <v>2078</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>4643</v>
+        <v>4642</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>1390</v>
+        <v>1290</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>107711</v>
+        <v>106711</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>6313</v>
+        <v>6312</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>23</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5115</v>
+        <v>5111</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>2533</v>
+        <v>2933</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>47160</v>
+        <v>51960</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>9346</v>
+        <v>29346</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>1250</v>
+        <v>2750</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>19</v>
+      <c r="F119" s="2">
+        <v>2400</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>101686</v>
+        <v>99686</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>66816</v>
+        <v>66888</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>60033</v>
+        <v>60177</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>6687</v>
+        <v>6735</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>4521</v>
+        <v>4569</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>50496</v>
+        <v>44496</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>56804</v>
+        <v>56948</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19927,11 +19927,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="4">
-        <v>0</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>19</v>
+      <c r="F41" s="6">
+        <v>48</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8744</v>
+        <v>8792</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9147</v>
+        <v>9183</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6326</v>
+        <v>6362</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20065,11 +20065,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>19</v>
+      <c r="F47" s="6">
+        <v>18</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>13305</v>
+        <v>13341</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20134,11 +20134,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="4">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>19</v>
+      <c r="F50" s="6">
+        <v>36</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20157,11 +20157,11 @@
       <c r="E51">
         <v>144</v>
       </c>
-      <c r="F51" s="4">
-        <v>0</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>19</v>
+      <c r="F51" s="6">
+        <v>48</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>25170</v>
+        <v>25206</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -9012,7 +9012,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="2">
-        <v>5787</v>
+        <v>5667</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>44663</v>
+        <v>44506</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>24323</v>
+        <v>24238</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>28209</v>
+        <v>28052</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>43303</v>
+        <v>39703</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>62937</v>
+        <v>61593</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>41570</v>
+        <v>31570</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>29346</v>
+        <v>29296</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>9458</v>
+        <v>9233</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>38536</v>
+        <v>38261</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>2400</v>
+        <v>864</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>6356</v>
+        <v>6116</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>66888</v>
+        <v>66864</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>44506</v>
+        <v>44470</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>72467</v>
+        <v>72371</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>24238</v>
+        <v>23770</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -16619,7 +16619,7 @@
         <v>72</v>
       </c>
       <c r="F42" s="6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>23</v>
@@ -16642,7 +16642,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="6">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>23</v>
@@ -16688,7 +16688,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="6">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>23</v>
@@ -22745,7 +22745,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="2">
-        <v>5092</v>
+        <v>4742</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>61599</v>
+        <v>61119</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>4437</v>
+        <v>4337</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>7041</v>
+        <v>6891</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>37061</v>
+        <v>36861</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>5231</v>
+        <v>5181</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>2672</v>
+        <v>2472</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>9686</v>
+        <v>9386</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>11677</v>
+        <v>11477</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>1331</v>
+        <v>1131</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>65726</v>
+        <v>59126</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -19053,11 +19053,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -22906,7 +22906,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>10981</v>
+        <v>10956</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>14588</v>
+        <v>19718</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>97445</v>
+        <v>97254</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="2">
-        <v>12855</v>
+        <v>12802</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>31370</v>
+        <v>33770</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>28245</v>
+        <v>33045</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>4337</v>
+        <v>4287</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>2774</v>
+        <v>2724</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>6841</v>
+        <v>6791</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8989,7 +8989,7 @@
         <v>100</v>
       </c>
       <c r="F55" s="2">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>38220</v>
+        <v>39720</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>19</v>
+      <c r="F119" s="2">
+        <v>2760</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>59126</v>
+        <v>59151</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>2160</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -17355,7 +17355,7 @@
         <v>200</v>
       </c>
       <c r="F74" s="6">
-        <v>273</v>
+        <v>28</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>23</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -21146,11 +21146,11 @@
       <c r="E94">
         <v>144</v>
       </c>
-      <c r="F94" s="6">
-        <v>1</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>11935</v>
+        <v>11934</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>12705</v>
+        <v>12704</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>28440</v>
+        <v>33240</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9415</v>
+        <v>9345</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -11197,7 +11197,7 @@
         <v>12</v>
       </c>
       <c r="F151" s="2">
-        <v>459</v>
+        <v>109</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="2">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7290,7 +7290,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="2">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>15508</v>
+        <v>15208</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -11289,7 +11289,7 @@
         <v>6</v>
       </c>
       <c r="F155" s="2">
-        <v>979</v>
+        <v>763</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>44399</v>
+        <v>44387</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>36875</v>
+        <v>36705</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>59167</v>
+        <v>59092</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10146</v>
+        <v>10121</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>7896</v>
+        <v>7893</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -15241,11 +15241,11 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60" s="2">
-        <v>1536</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="2">
-        <v>1512</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -15310,11 +15310,11 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="2">
-        <v>1512</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
-        <v>1512</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
-        <v>1512</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -19490,11 +19490,11 @@
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="6">
-        <v>34</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>23</v>
+      <c r="F22" s="2">
+        <v>14830</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -22037,11 +22037,11 @@
       <c r="E30">
         <v>12</v>
       </c>
-      <c r="F30" s="6">
-        <v>3</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>23</v>
+      <c r="F30" s="2">
+        <v>363</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -22060,11 +22060,11 @@
       <c r="E31">
         <v>12</v>
       </c>
-      <c r="F31" s="6">
-        <v>1</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>23</v>
+      <c r="F31" s="2">
+        <v>253</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -8183,11 +8183,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>23</v>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>6434</v>
+        <v>6430</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>2454</v>
+        <v>2444</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>2545</v>
+        <v>2539</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>8836</v>
+        <v>8832</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -9771,7 +9771,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="2">
-        <v>12233</v>
+        <v>12229</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -9909,7 +9909,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="2">
-        <v>4320</v>
+        <v>4316</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="2">
-        <v>15069</v>
+        <v>15065</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -13612,7 +13612,7 @@
         <v>100</v>
       </c>
       <c r="F256" s="2">
-        <v>90048</v>
+        <v>90036</v>
       </c>
       <c r="G256" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>44387</v>
+        <v>44384</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14230,7 +14230,7 @@
         <v>144</v>
       </c>
       <c r="F16" s="2">
-        <v>11177</v>
+        <v>11171</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>30590</v>
+        <v>30587</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16021,7 +16021,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="2">
-        <v>8974</v>
+        <v>8968</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>7021</v>
+        <v>7017</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>11392</v>
+        <v>11386</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16274,7 +16274,7 @@
         <v>192</v>
       </c>
       <c r="F27" s="2">
-        <v>29625</v>
+        <v>29622</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="2">
-        <v>29512</v>
+        <v>29509</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>8063</v>
+        <v>8060</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>6450</v>
+        <v>6420</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -16941,7 +16941,7 @@
         <v>96</v>
       </c>
       <c r="F56" s="2">
-        <v>23238</v>
+        <v>23232</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -16964,7 +16964,7 @@
         <v>96</v>
       </c>
       <c r="F57" s="2">
-        <v>21530</v>
+        <v>21524</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>11044</v>
+        <v>7748</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>84542</v>
+        <v>83842</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>33180</v>
+        <v>32980</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>39720</v>
+        <v>39722</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>39314</v>
+        <v>39315</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>40214</v>
+        <v>40215</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -11173,11 +11173,11 @@
       <c r="E150">
         <v>12</v>
       </c>
-      <c r="F150" s="6">
-        <v>9</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>23</v>
+      <c r="F150" s="4">
+        <v>0</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -11311,11 +11311,11 @@
       <c r="E156">
         <v>6</v>
       </c>
-      <c r="F156" s="6">
-        <v>4</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>23</v>
+      <c r="F156" s="4">
+        <v>0</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>198167</v>
+        <v>198169</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>32980</v>
+        <v>37780</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="6">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>23</v>
@@ -15241,11 +15241,11 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>19</v>
+      <c r="F60" s="2">
+        <v>1560</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="4">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>19</v>
+      <c r="F62" s="2">
+        <v>1452</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -15310,11 +15310,11 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="4">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>19</v>
+      <c r="F63" s="2">
+        <v>768</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>19</v>
+      <c r="F66" s="2">
+        <v>1500</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>1560</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>7749</v>
+        <v>7113</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>27933</v>
+        <v>27333</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>72548</v>
+        <v>72536</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -15241,11 +15241,11 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60" s="2">
-        <v>1560</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="2">
-        <v>1452</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -15310,11 +15310,11 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="2">
-        <v>768</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
-        <v>1500</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
-        <v>1560</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>22193</v>
+        <v>21193</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>97204</v>
+        <v>97054</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>37780</v>
+        <v>39130</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>562</v>
+        <v>512</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>39722</v>
+        <v>39622</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>33758</v>
+        <v>33658</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="2">
-        <v>36441</v>
+        <v>36341</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>19412</v>
+        <v>21188</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="6">
-        <v>552</v>
+        <v>2052</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>23</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>2320</v>
+        <v>2032</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -12715,7 +12715,7 @@
         <v>5</v>
       </c>
       <c r="F217" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>4144</v>
+        <v>4794</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8183,11 +8183,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="6">
-        <v>51</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>23</v>
+      <c r="F20" s="2">
+        <v>610</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>6430</v>
+        <v>6429</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>8428</v>
+        <v>8427</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -8597,11 +8597,11 @@
       <c r="E38">
         <v>50</v>
       </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>19</v>
+      <c r="F38" s="2">
+        <v>450</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>197569</v>
+        <v>197469</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>45312</v>
+        <v>53376</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>65939</v>
+        <v>68039</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -13931,7 +13931,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
-        <v>792</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
-        <v>792</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>15433</v>
+        <v>15431</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>45087</v>
+        <v>44987</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -7037,7 +7037,7 @@
         <v>96</v>
       </c>
       <c r="F2" s="2">
-        <v>10736</v>
+        <v>10734</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7060,7 +7060,7 @@
         <v>96</v>
       </c>
       <c r="F3" s="2">
-        <v>12216</v>
+        <v>12214</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7083,7 +7083,7 @@
         <v>96</v>
       </c>
       <c r="F4" s="2">
-        <v>11271</v>
+        <v>11269</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -7106,7 +7106,7 @@
         <v>96</v>
       </c>
       <c r="F5" s="2">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7129,7 +7129,7 @@
         <v>48</v>
       </c>
       <c r="F6" s="2">
-        <v>12184</v>
+        <v>12182</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7152,7 +7152,7 @@
         <v>48</v>
       </c>
       <c r="F7" s="2">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7175,7 +7175,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>9794</v>
+        <v>9792</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7290,7 +7290,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="2">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>45630</v>
+        <v>45525</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>39315</v>
+        <v>39310</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>40214</v>
+        <v>40209</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="2">
-        <v>36341</v>
+        <v>36336</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -9564,7 +9564,7 @@
         <v>100</v>
       </c>
       <c r="F80" s="2">
-        <v>15125</v>
+        <v>15120</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -9587,7 +9587,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="2">
-        <v>9138</v>
+        <v>9133</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -9610,7 +9610,7 @@
         <v>100</v>
       </c>
       <c r="F82" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -9633,7 +9633,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="2">
-        <v>9996</v>
+        <v>9991</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>10</v>
@@ -9656,7 +9656,7 @@
         <v>100</v>
       </c>
       <c r="F84" s="2">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>10</v>
@@ -9702,7 +9702,7 @@
         <v>100</v>
       </c>
       <c r="F86" s="2">
-        <v>36323</v>
+        <v>36318</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -11173,11 +11173,11 @@
       <c r="E150">
         <v>12</v>
       </c>
-      <c r="F150" s="4">
-        <v>0</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>19</v>
+      <c r="F150" s="2">
+        <v>2110</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>70252</v>
+        <v>70250</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>18298</v>
+        <v>18261</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15012,7 +15012,7 @@
         <v>360</v>
       </c>
       <c r="F50" s="2">
-        <v>8695</v>
+        <v>8665</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -15035,7 +15035,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="2">
-        <v>23462</v>
+        <v>23432</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -15058,7 +15058,7 @@
         <v>360</v>
       </c>
       <c r="F52" s="2">
-        <v>9557</v>
+        <v>9527</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -15081,7 +15081,7 @@
         <v>360</v>
       </c>
       <c r="F53" s="2">
-        <v>39388</v>
+        <v>39358</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -15104,7 +15104,7 @@
         <v>360</v>
       </c>
       <c r="F54" s="2">
-        <v>40709</v>
+        <v>40679</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -15127,7 +15127,7 @@
         <v>360</v>
       </c>
       <c r="F55" s="2">
-        <v>9051</v>
+        <v>9021</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -15150,7 +15150,7 @@
         <v>360</v>
       </c>
       <c r="F56" s="2">
-        <v>30954</v>
+        <v>30924</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -15173,7 +15173,7 @@
         <v>360</v>
       </c>
       <c r="F57" s="2">
-        <v>31904</v>
+        <v>31874</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -15196,7 +15196,7 @@
         <v>360</v>
       </c>
       <c r="F58" s="2">
-        <v>34782</v>
+        <v>34752</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>59227</v>
+        <v>59222</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="2">
-        <v>29499</v>
+        <v>29487</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>8056</v>
+        <v>8044</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -16481,7 +16481,7 @@
         <v>72</v>
       </c>
       <c r="F36" s="6">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>23</v>
@@ -16573,7 +16573,7 @@
         <v>72</v>
       </c>
       <c r="F40" s="6">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>23</v>
@@ -16987,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="2">
-        <v>2617</v>
+        <v>2605</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>5448</v>
+        <v>5436</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>10121</v>
+        <v>10118</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>7293</v>
+        <v>7281</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>27153</v>
+        <v>27141</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>12686</v>
+        <v>12674</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>83964</v>
+        <v>83952</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>15151</v>
+        <v>15139</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8792</v>
+        <v>8780</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9176</v>
+        <v>9164</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6354</v>
+        <v>6342</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>24342</v>
+        <v>24330</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -21578,7 +21578,7 @@
         <v>48</v>
       </c>
       <c r="F10" s="2">
-        <v>2033</v>
+        <v>2021</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -21601,7 +21601,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="2">
-        <v>2068</v>
+        <v>2056</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -21670,7 +21670,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -21693,7 +21693,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -21923,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>48505</v>
+        <v>48493</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>15108</v>
+        <v>15008</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>45424</v>
+        <v>55024</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="6">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>23</v>
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="2">
-        <v>29024</v>
+        <v>28964</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -11519,7 +11519,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -11703,7 +11703,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="2">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -11818,7 +11818,7 @@
         <v>48</v>
       </c>
       <c r="F178" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -11841,7 +11841,7 @@
         <v>36</v>
       </c>
       <c r="F179" s="6">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>23</v>
@@ -12186,7 +12186,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="6">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>23</v>
@@ -12209,7 +12209,7 @@
         <v>48</v>
       </c>
       <c r="F195" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>23</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>197469</v>
+        <v>197467</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -17079,7 +17079,7 @@
         <v>576</v>
       </c>
       <c r="F62" s="2">
-        <v>13796</v>
+        <v>13784</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -17102,7 +17102,7 @@
         <v>576</v>
       </c>
       <c r="F63" s="2">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -17654,7 +17654,7 @@
         <v>576</v>
       </c>
       <c r="F87" s="6">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>23</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="6">
-        <v>2052</v>
+        <v>2040</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>23</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>171793</v>
+        <v>171792</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>53301</v>
+        <v>53295</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>27141</v>
+        <v>27140</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>12674</v>
+        <v>12673</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>83952</v>
+        <v>83951</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>15139</v>
+        <v>15138</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8780</v>
+        <v>8779</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>9164</v>
+        <v>9163</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>6342</v>
+        <v>6341</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>23</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>23</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>5455</v>
+        <v>5454</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10530,7 +10530,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="2">
-        <v>4369</v>
+        <v>4354</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>10</v>
@@ -10553,7 +10553,7 @@
         <v>24</v>
       </c>
       <c r="F123" s="2">
-        <v>1385</v>
+        <v>1231</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>10</v>
@@ -10599,7 +10599,7 @@
         <v>24</v>
       </c>
       <c r="F125" s="2">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>10</v>
@@ -10645,7 +10645,7 @@
         <v>24</v>
       </c>
       <c r="F127" s="2">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="6">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>23</v>
@@ -17746,7 +17746,7 @@
         <v>576</v>
       </c>
       <c r="F91" s="6">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>23</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="6">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>23</v>
@@ -17815,7 +17815,7 @@
         <v>576</v>
       </c>
       <c r="F94" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>23</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>15430</v>
+        <v>15180</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>59624</v>
+        <v>68724</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -10185,7 +10185,7 @@
         <v>120</v>
       </c>
       <c r="F107" s="2">
-        <v>4865</v>
+        <v>4864</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>6603</v>
+        <v>13203</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -15310,11 +15310,11 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="6">
-        <v>1</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>23</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>7223</v>
+        <v>7222</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -15587,7 +15587,7 @@
         <v>144</v>
       </c>
       <c r="F75" s="2">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -15610,7 +15610,7 @@
         <v>144</v>
       </c>
       <c r="F76" s="2">
-        <v>4367</v>
+        <v>4366</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -18321,7 +18321,7 @@
         <v>192</v>
       </c>
       <c r="F116" s="2">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>53292</v>
+        <v>53291</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -21440,7 +21440,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>922</v>
+        <v>958</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>17062</v>
+        <v>17008</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -10070,7 +10070,7 @@
         <v>120</v>
       </c>
       <c r="F102" s="6">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G102" s="7" t="s">
         <v>23</v>
@@ -10093,7 +10093,7 @@
         <v>120</v>
       </c>
       <c r="F103" s="6">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G103" s="7" t="s">
         <v>23</v>
@@ -10116,7 +10116,7 @@
         <v>120</v>
       </c>
       <c r="F104" s="2">
-        <v>5946</v>
+        <v>5926</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>10</v>
@@ -10139,7 +10139,7 @@
         <v>120</v>
       </c>
       <c r="F105" s="2">
-        <v>5654</v>
+        <v>5634</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -10162,7 +10162,7 @@
         <v>120</v>
       </c>
       <c r="F106" s="2">
-        <v>5715</v>
+        <v>5695</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -10185,7 +10185,7 @@
         <v>120</v>
       </c>
       <c r="F107" s="2">
-        <v>4864</v>
+        <v>4844</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -10208,7 +10208,7 @@
         <v>120</v>
       </c>
       <c r="F108" s="2">
-        <v>2918</v>
+        <v>2898</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -10231,7 +10231,7 @@
         <v>120</v>
       </c>
       <c r="F109" s="2">
-        <v>4817</v>
+        <v>4797</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -10254,7 +10254,7 @@
         <v>120</v>
       </c>
       <c r="F110" s="2">
-        <v>4638</v>
+        <v>4618</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -10300,7 +10300,7 @@
         <v>120</v>
       </c>
       <c r="F112" s="2">
-        <v>2788</v>
+        <v>2768</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -10323,7 +10323,7 @@
         <v>120</v>
       </c>
       <c r="F113" s="2">
-        <v>2880</v>
+        <v>2860</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>11835</v>
+        <v>14235</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="2">
-        <v>16229</v>
+        <v>16226</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
@@ -11703,7 +11703,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -11841,7 +11841,7 @@
         <v>36</v>
       </c>
       <c r="F179" s="6">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>23</v>
@@ -12416,7 +12416,7 @@
         <v>160</v>
       </c>
       <c r="F204" s="2">
-        <v>4628</v>
+        <v>4468</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>10</v>
@@ -12807,7 +12807,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="2">
-        <v>3263</v>
+        <v>3253</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>10</v>
@@ -12876,7 +12876,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="2">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>10</v>
@@ -12922,7 +12922,7 @@
         <v>10</v>
       </c>
       <c r="F226" s="2">
-        <v>1722</v>
+        <v>1712</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>39471</v>
+        <v>38821</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>4499</v>
+        <v>4427</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>8387</v>
+        <v>8267</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="6">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>23</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -9264,11 +9264,11 @@
       <c r="E67">
         <v>100</v>
       </c>
-      <c r="F67" s="6">
-        <v>67</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>23</v>
+      <c r="F67" s="2">
+        <v>11065</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,7 +9380,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="2">
-        <v>24247</v>
+        <v>26690</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>70105</v>
+        <v>69673</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>19</v>
+      <c r="F66" s="2">
+        <v>1524</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+      <c r="F67" s="2">
+        <v>1572</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -22791,7 +22791,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="2">
-        <v>3828</v>
+        <v>3778</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>85124</v>
+        <v>86376</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -13083,7 +13083,7 @@
         <v>5</v>
       </c>
       <c r="F233" s="2">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="G233" s="3" t="s">
         <v>10</v>
@@ -17286,7 +17286,7 @@
         <v>200</v>
       </c>
       <c r="F71" s="6">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>23</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -11358,7 +11358,7 @@
         <v>24</v>
       </c>
       <c r="F158" s="6">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>23</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>4427</v>
+        <v>4595</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -15241,11 +15241,11 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60" s="2">
-        <v>1536</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="2">
-        <v>2508</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
-        <v>1488</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>7017</v>
+        <v>7041</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>10168</v>
+        <v>10216</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>6138</v>
+        <v>6137</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>10281</v>
+        <v>10317</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -20526,7 +20526,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="2">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>19</v>
+      <c r="F68" s="6">
+        <v>48</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20595,7 +20595,7 @@
         <v>12</v>
       </c>
       <c r="F70" s="6">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>23</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>191199</v>
+        <v>191319</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22722,7 +22722,7 @@
         <v>1000</v>
       </c>
       <c r="F4" s="6">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>23</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -52,36 +52,39 @@
     <t>FORRO N VINIFAN OFICIO CRISTAL 26</t>
   </si>
   <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>02211</t>
+  </si>
+  <si>
+    <t>7754807020022</t>
+  </si>
+  <si>
+    <t>FORRO N VINIFAN A4 CRISTAL 26</t>
+  </si>
+  <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>02204</t>
+  </si>
+  <si>
+    <t>7754807020077</t>
+  </si>
+  <si>
+    <t>FORRO N VINIFANCITO CRISTAL 25</t>
+  </si>
+  <si>
+    <t>02212</t>
+  </si>
+  <si>
+    <t>FORRO N VINIFANCITO CRISTAL 26</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
   </si>
   <si>
-    <t>02211</t>
-  </si>
-  <si>
-    <t>7754807020022</t>
-  </si>
-  <si>
-    <t>FORRO N VINIFAN A4 CRISTAL 26</t>
-  </si>
-  <si>
-    <t>✓ OK</t>
-  </si>
-  <si>
-    <t>02204</t>
-  </si>
-  <si>
-    <t>7754807020077</t>
-  </si>
-  <si>
-    <t>FORRO N VINIFANCITO CRISTAL 25</t>
-  </si>
-  <si>
-    <t>02212</t>
-  </si>
-  <si>
-    <t>FORRO N VINIFANCITO CRISTAL 26</t>
-  </si>
-  <si>
     <t>02182</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>FORRO VINIFAN A4 CRISTAL PRECORTADO 25</t>
-  </si>
-  <si>
-    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>02213</t>
@@ -6228,7 +6228,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
@@ -6238,7 +6238,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -6256,7 +6256,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -6266,7 +6266,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6763,11 +6763,11 @@
       <c r="E5">
         <v>100</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6775,22 +6775,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="2">
         <v>13</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6801,7 +6801,7 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7197,11 +7197,11 @@
       <c r="E9">
         <v>48</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="6">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7220,11 +7220,11 @@
       <c r="E10">
         <v>96</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="6">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7244,7 +7244,7 @@
         <v>96</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -7266,11 +7266,11 @@
       <c r="E12">
         <v>96</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="6">
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7312,11 +7312,11 @@
       <c r="E14">
         <v>400</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>1271</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>23</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7405,7 +7405,7 @@
         <v>288</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -7451,7 +7451,7 @@
         <v>72</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -7519,11 +7519,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <v>6</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -7542,11 +7542,11 @@
       <c r="E24">
         <v>240</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -7565,11 +7565,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -7611,11 +7611,11 @@
       <c r="E27">
         <v>60</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="6">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -7680,11 +7680,11 @@
       <c r="E30">
         <v>30</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="2">
         <v>1</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>23</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -7769,11 +7769,11 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>23</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7815,11 +7815,11 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7907,11 +7907,11 @@
       <c r="E8">
         <v>50</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8022,11 +8022,11 @@
       <c r="E13">
         <v>50</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="6">
         <v>0</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="6">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8252,11 +8252,11 @@
       <c r="E23">
         <v>50</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="4">
-        <v>3629</v>
+        <v>3624</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>14</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="4">
-        <v>4456</v>
+        <v>4451</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="4">
-        <v>2402</v>
+        <v>2397</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>14</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="4">
-        <v>2533</v>
+        <v>2528</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>14</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="4">
-        <v>4771</v>
+        <v>4766</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>14</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="4">
-        <v>8993</v>
+        <v>8988</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>14</v>
@@ -8574,11 +8574,11 @@
       <c r="E37">
         <v>50</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="6">
         <v>0</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,11 +8597,11 @@
       <c r="E38">
         <v>50</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="6">
         <v>0</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -8620,11 +8620,11 @@
       <c r="E39">
         <v>50</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="6">
         <v>0</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="4">
-        <v>4599</v>
+        <v>4594</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>14</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -8689,11 +8689,11 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="2">
         <v>9</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>23</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -8712,11 +8712,11 @@
       <c r="E43">
         <v>100</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="6">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>10</v>
+      <c r="G43" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -8827,11 +8827,11 @@
       <c r="E48">
         <v>100</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="6">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,11 +8850,11 @@
       <c r="E49">
         <v>100</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="2">
         <v>267</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>23</v>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,11 +8896,11 @@
       <c r="E51">
         <v>100</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="2">
         <v>98</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>23</v>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -8942,11 +8942,11 @@
       <c r="E53">
         <v>100</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="2">
         <v>101</v>
       </c>
-      <c r="G53" s="7" t="s">
-        <v>23</v>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,11 +8965,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="2">
         <v>251</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>23</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,7 +8989,7 @@
         <v>100</v>
       </c>
       <c r="F55" s="4">
-        <v>1050</v>
+        <v>990</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>14</v>
@@ -9104,7 +9104,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -9195,11 +9195,11 @@
       <c r="E64">
         <v>100</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="2">
         <v>153</v>
       </c>
-      <c r="G64" s="7" t="s">
-        <v>23</v>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -9218,11 +9218,11 @@
       <c r="E65">
         <v>50</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="6">
         <v>0</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,11 +9241,11 @@
       <c r="E66">
         <v>50</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="2">
         <v>84</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>23</v>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,7 +9265,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -9333,11 +9333,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="2">
         <v>67</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>23</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,11 +9356,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="2">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -9609,11 +9609,11 @@
       <c r="E82">
         <v>100</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="2">
         <v>5</v>
       </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,7 +9679,7 @@
         <v>100</v>
       </c>
       <c r="F85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>10</v>
@@ -9839,11 +9839,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="2">
         <v>445</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>23</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -9977,11 +9977,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="2">
         <v>1</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>23</v>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -10001,7 +10001,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -10023,11 +10023,11 @@
       <c r="E100">
         <v>120</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="6">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>10</v>
+      <c r="G100" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -10046,11 +10046,11 @@
       <c r="E101">
         <v>120</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="6">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>10</v>
+      <c r="G101" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,11 +10069,11 @@
       <c r="E102">
         <v>120</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="2">
         <v>2</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>23</v>
+      <c r="G102" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,11 +10092,11 @@
       <c r="E103">
         <v>120</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="2">
         <v>35</v>
       </c>
-      <c r="G103" s="7" t="s">
-        <v>23</v>
+      <c r="G103" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,11 +10276,11 @@
       <c r="E111">
         <v>120</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="2">
         <v>8</v>
       </c>
-      <c r="G111" s="7" t="s">
-        <v>23</v>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,11 +10345,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="2">
         <v>47</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>23</v>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -10368,11 +10368,11 @@
       <c r="E115">
         <v>24</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="6">
         <v>0</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="G115" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -10391,11 +10391,11 @@
       <c r="E116">
         <v>24</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="6">
         <v>0</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="G116" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -10414,11 +10414,11 @@
       <c r="E117">
         <v>24</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="6">
         <v>0</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="G117" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>21555</v>
+        <v>21435</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -10621,11 +10621,11 @@
       <c r="E126">
         <v>24</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="6">
         <v>0</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="G126" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -10782,11 +10782,11 @@
       <c r="E133">
         <v>24</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="6">
         <v>0</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="G133" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -10828,11 +10828,11 @@
       <c r="E135">
         <v>24</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="6">
         <v>0</v>
       </c>
-      <c r="G135" s="3" t="s">
-        <v>10</v>
+      <c r="G135" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -10874,11 +10874,11 @@
       <c r="E137">
         <v>12</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="6">
         <v>0</v>
       </c>
-      <c r="G137" s="3" t="s">
-        <v>10</v>
+      <c r="G137" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -10897,11 +10897,11 @@
       <c r="E138">
         <v>12</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="6">
         <v>0</v>
       </c>
-      <c r="G138" s="3" t="s">
-        <v>10</v>
+      <c r="G138" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -10921,7 +10921,7 @@
         <v>30</v>
       </c>
       <c r="F139" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -10944,7 +10944,7 @@
         <v>30</v>
       </c>
       <c r="F140" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -10966,11 +10966,11 @@
       <c r="E141">
         <v>30</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="6">
         <v>0</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -10989,11 +10989,11 @@
       <c r="E142">
         <v>24</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="6">
         <v>0</v>
       </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="G142" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -11012,11 +11012,11 @@
       <c r="E143">
         <v>24</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="6">
         <v>0</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="G143" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -11035,11 +11035,11 @@
       <c r="E144">
         <v>24</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -11081,11 +11081,11 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="2">
         <v>5</v>
       </c>
-      <c r="G146" s="7" t="s">
-        <v>23</v>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -11105,7 +11105,7 @@
         <v>24</v>
       </c>
       <c r="F147" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>10</v>
@@ -11151,7 +11151,7 @@
         <v>12</v>
       </c>
       <c r="F149" s="4">
-        <v>372</v>
+        <v>96</v>
       </c>
       <c r="G149" s="5" t="s">
         <v>14</v>
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -11196,11 +11196,11 @@
       <c r="E151">
         <v>12</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F151" s="2">
         <v>1</v>
       </c>
-      <c r="G151" s="7" t="s">
-        <v>23</v>
+      <c r="G151" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -11243,7 +11243,7 @@
         <v>12</v>
       </c>
       <c r="F153" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>10</v>
@@ -11266,7 +11266,7 @@
         <v>6</v>
       </c>
       <c r="F154" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -11358,7 +11358,7 @@
         <v>24</v>
       </c>
       <c r="F158" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>10</v>
@@ -11380,11 +11380,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="6">
         <v>0</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="G159" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11403,11 +11403,11 @@
       <c r="E160">
         <v>24</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="6">
         <v>0</v>
       </c>
-      <c r="G160" s="3" t="s">
-        <v>10</v>
+      <c r="G160" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -11426,11 +11426,11 @@
       <c r="E161">
         <v>24</v>
       </c>
-      <c r="F161" s="6">
+      <c r="F161" s="2">
         <v>21</v>
       </c>
-      <c r="G161" s="7" t="s">
-        <v>23</v>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11473,7 +11473,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -11496,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>10</v>
@@ -11541,11 +11541,11 @@
       <c r="E166">
         <v>24</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="6">
         <v>0</v>
       </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="G166" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -11610,11 +11610,11 @@
       <c r="E169">
         <v>36</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="6">
         <v>0</v>
       </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="G169" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -11633,11 +11633,11 @@
       <c r="E170">
         <v>36</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="6">
         <v>0</v>
       </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="G170" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -11656,11 +11656,11 @@
       <c r="E171">
         <v>72</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="6">
         <v>0</v>
       </c>
-      <c r="G171" s="3" t="s">
-        <v>10</v>
+      <c r="G171" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -11679,11 +11679,11 @@
       <c r="E172">
         <v>72</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="6">
         <v>0</v>
       </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="G172" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -11748,11 +11748,11 @@
       <c r="E175">
         <v>48</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="6">
         <v>0</v>
       </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="G175" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -11771,11 +11771,11 @@
       <c r="E176">
         <v>48</v>
       </c>
-      <c r="F176" s="6">
+      <c r="F176" s="2">
         <v>2</v>
       </c>
-      <c r="G176" s="7" t="s">
-        <v>23</v>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -11794,11 +11794,11 @@
       <c r="E177">
         <v>48</v>
       </c>
-      <c r="F177" s="6">
+      <c r="F177" s="2">
         <v>58</v>
       </c>
-      <c r="G177" s="7" t="s">
-        <v>23</v>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -11840,11 +11840,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="6">
+      <c r="F179" s="2">
         <v>126</v>
       </c>
-      <c r="G179" s="7" t="s">
-        <v>23</v>
+      <c r="G179" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -11863,11 +11863,11 @@
       <c r="E180">
         <v>36</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
-        <v>10</v>
+      <c r="G180" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -11886,11 +11886,11 @@
       <c r="E181">
         <v>36</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="6">
         <v>0</v>
       </c>
-      <c r="G181" s="3" t="s">
-        <v>10</v>
+      <c r="G181" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -11978,11 +11978,11 @@
       <c r="E185">
         <v>240</v>
       </c>
-      <c r="F185" s="6">
+      <c r="F185" s="2">
         <v>808</v>
       </c>
-      <c r="G185" s="7" t="s">
-        <v>23</v>
+      <c r="G185" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -12116,11 +12116,11 @@
       <c r="E191">
         <v>48</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="6">
         <v>0</v>
       </c>
-      <c r="G191" s="3" t="s">
-        <v>10</v>
+      <c r="G191" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -12139,11 +12139,11 @@
       <c r="E192">
         <v>96</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="6">
         <v>0</v>
       </c>
-      <c r="G192" s="3" t="s">
-        <v>10</v>
+      <c r="G192" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -12186,7 +12186,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="2">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -12209,7 +12209,7 @@
         <v>48</v>
       </c>
       <c r="F195" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -12231,11 +12231,11 @@
       <c r="E196">
         <v>48</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="6">
         <v>0</v>
       </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="G196" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -12254,11 +12254,11 @@
       <c r="E197">
         <v>48</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="6">
         <v>0</v>
       </c>
-      <c r="G197" s="3" t="s">
-        <v>10</v>
+      <c r="G197" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -12278,7 +12278,7 @@
         <v>10</v>
       </c>
       <c r="F198" s="4">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G198" s="5" t="s">
         <v>14</v>
@@ -12300,11 +12300,11 @@
       <c r="E199">
         <v>10</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="6">
         <v>0</v>
       </c>
-      <c r="G199" s="3" t="s">
-        <v>10</v>
+      <c r="G199" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -12439,7 +12439,7 @@
         <v>280</v>
       </c>
       <c r="F205" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>10</v>
@@ -12553,11 +12553,11 @@
       <c r="E210">
         <v>720</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="6">
         <v>0</v>
       </c>
-      <c r="G210" s="3" t="s">
-        <v>10</v>
+      <c r="G210" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -12576,11 +12576,11 @@
       <c r="E211">
         <v>720</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="6">
         <v>0</v>
       </c>
-      <c r="G211" s="3" t="s">
-        <v>10</v>
+      <c r="G211" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -12622,11 +12622,11 @@
       <c r="E213">
         <v>720</v>
       </c>
-      <c r="F213" s="6">
+      <c r="F213" s="2">
         <v>177</v>
       </c>
-      <c r="G213" s="7" t="s">
-        <v>23</v>
+      <c r="G213" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -12760,11 +12760,11 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="6">
+      <c r="F219" s="2">
         <v>1</v>
       </c>
-      <c r="G219" s="7" t="s">
-        <v>23</v>
+      <c r="G219" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -12783,11 +12783,11 @@
       <c r="E220">
         <v>10</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="6">
         <v>0</v>
       </c>
-      <c r="G220" s="3" t="s">
-        <v>10</v>
+      <c r="G220" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -12967,11 +12967,11 @@
       <c r="E228">
         <v>10</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="6">
         <v>0</v>
       </c>
-      <c r="G228" s="3" t="s">
-        <v>10</v>
+      <c r="G228" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -13036,11 +13036,11 @@
       <c r="E231">
         <v>5</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="6">
         <v>0</v>
       </c>
-      <c r="G231" s="3" t="s">
-        <v>10</v>
+      <c r="G231" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="6">
+      <c r="F234" s="2">
         <v>2</v>
       </c>
-      <c r="G234" s="7" t="s">
-        <v>23</v>
+      <c r="G234" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13289,11 +13289,11 @@
       <c r="E242">
         <v>5</v>
       </c>
-      <c r="F242" s="6">
+      <c r="F242" s="2">
         <v>1</v>
       </c>
-      <c r="G242" s="7" t="s">
-        <v>23</v>
+      <c r="G242" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -13358,11 +13358,11 @@
       <c r="E245">
         <v>5</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="6">
         <v>0</v>
       </c>
-      <c r="G245" s="3" t="s">
-        <v>10</v>
+      <c r="G245" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -13450,11 +13450,11 @@
       <c r="E249">
         <v>5</v>
       </c>
-      <c r="F249" s="6">
+      <c r="F249" s="2">
         <v>1</v>
       </c>
-      <c r="G249" s="7" t="s">
-        <v>23</v>
+      <c r="G249" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -13496,11 +13496,11 @@
       <c r="E251">
         <v>40</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="6">
         <v>0</v>
       </c>
-      <c r="G251" s="3" t="s">
-        <v>10</v>
+      <c r="G251" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -13519,11 +13519,11 @@
       <c r="E252">
         <v>40</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="6">
         <v>0</v>
       </c>
-      <c r="G252" s="3" t="s">
-        <v>10</v>
+      <c r="G252" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -13542,11 +13542,11 @@
       <c r="E253">
         <v>40</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="6">
         <v>0</v>
       </c>
-      <c r="G253" s="3" t="s">
-        <v>10</v>
+      <c r="G253" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -13565,11 +13565,11 @@
       <c r="E254">
         <v>40</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="6">
         <v>0</v>
       </c>
-      <c r="G254" s="3" t="s">
-        <v>10</v>
+      <c r="G254" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -13930,11 +13930,11 @@
       <c r="E3">
         <v>144</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="2">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -13953,11 +13953,11 @@
       <c r="E4">
         <v>72</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -13999,11 +13999,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="2">
         <v>32</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14068,11 +14068,11 @@
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="6">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -14160,11 +14160,11 @@
       <c r="E13">
         <v>144</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="2">
         <v>498</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -14275,11 +14275,11 @@
       <c r="E18">
         <v>72</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="6">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -14321,11 +14321,11 @@
       <c r="E20">
         <v>72</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="6">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -14344,11 +14344,11 @@
       <c r="E21">
         <v>24</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="6">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -14413,11 +14413,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="2">
         <v>49</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -14666,11 +14666,11 @@
       <c r="E35">
         <v>576</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="2">
         <v>2302</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>23</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -14712,11 +14712,11 @@
       <c r="E37">
         <v>576</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="2">
         <v>1457</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>23</v>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -14735,11 +14735,11 @@
       <c r="E38">
         <v>576</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="2">
         <v>63</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>23</v>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -14804,11 +14804,11 @@
       <c r="E41">
         <v>576</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="2">
         <v>2846</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>23</v>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -14827,11 +14827,11 @@
       <c r="E42">
         <v>576</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="2">
         <v>981</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>23</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -14850,11 +14850,11 @@
       <c r="E43">
         <v>576</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="6">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>10</v>
+      <c r="G43" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -14873,11 +14873,11 @@
       <c r="E44">
         <v>576</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="2">
         <v>5</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>23</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -14920,7 +14920,7 @@
         <v>72</v>
       </c>
       <c r="F46" s="4">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>14</v>
@@ -15218,11 +15218,11 @@
       <c r="E59">
         <v>12</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="2">
         <v>4</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>23</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -15241,11 +15241,11 @@
       <c r="E60">
         <v>12</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="6">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -15287,11 +15287,11 @@
       <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="6">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="G62" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -15310,11 +15310,11 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="6">
         <v>0</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="G63" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -15356,11 +15356,11 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="2">
         <v>2</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>23</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -15379,11 +15379,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="6">
         <v>0</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -15402,11 +15402,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -15425,11 +15425,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="6">
         <v>0</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -15448,11 +15448,11 @@
       <c r="E69">
         <v>12</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="6">
         <v>0</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="G69" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -15471,11 +15471,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="6">
         <v>0</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -15494,11 +15494,11 @@
       <c r="E71">
         <v>12</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -15767,11 +15767,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>23</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -15790,11 +15790,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -15951,11 +15951,11 @@
       <c r="E13">
         <v>144</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="2">
         <v>7</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -16158,11 +16158,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="6">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16181,11 +16181,11 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -16204,11 +16204,11 @@
       <c r="E24">
         <v>96</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -16227,11 +16227,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -16296,11 +16296,11 @@
       <c r="E28">
         <v>192</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="6">
         <v>0</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -16411,11 +16411,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="2">
         <v>713</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>23</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16434,11 +16434,11 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="6">
         <v>0</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="G34" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -16457,11 +16457,11 @@
       <c r="E35">
         <v>144</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="2">
         <v>114</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>23</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -16480,11 +16480,11 @@
       <c r="E36">
         <v>72</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="2">
         <v>30</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>23</v>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -16503,11 +16503,11 @@
       <c r="E37">
         <v>144</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="2">
         <v>56</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>23</v>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -16526,11 +16526,11 @@
       <c r="E38">
         <v>72</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="2">
         <v>7</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>23</v>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -16572,11 +16572,11 @@
       <c r="E40">
         <v>72</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="2">
         <v>59</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>23</v>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -16595,11 +16595,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="2">
         <v>166</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>23</v>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16618,11 +16618,11 @@
       <c r="E42">
         <v>72</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="2">
         <v>20</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>23</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16641,11 +16641,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="2">
         <v>253</v>
       </c>
-      <c r="G43" s="7" t="s">
-        <v>23</v>
+      <c r="G43" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -16664,11 +16664,11 @@
       <c r="E44">
         <v>72</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="2">
         <v>13</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>23</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -16687,11 +16687,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="2">
         <v>126</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>23</v>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -16848,11 +16848,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="2">
         <v>541</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>23</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -17055,11 +17055,11 @@
       <c r="E61">
         <v>576</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="6">
         <v>0</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -17079,7 +17079,7 @@
         <v>576</v>
       </c>
       <c r="F62" s="4">
-        <v>13784</v>
+        <v>13760</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>14</v>
@@ -17102,7 +17102,7 @@
         <v>576</v>
       </c>
       <c r="F63" s="4">
-        <v>3579</v>
+        <v>3555</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>14</v>
@@ -17124,11 +17124,11 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="6">
         <v>0</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -17147,11 +17147,11 @@
       <c r="E65">
         <v>200</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="2">
         <v>171</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>23</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -17170,11 +17170,11 @@
       <c r="E66">
         <v>200</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="2">
         <v>488</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>23</v>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -17216,11 +17216,11 @@
       <c r="E68">
         <v>200</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="2">
         <v>2</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>23</v>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -17262,11 +17262,11 @@
       <c r="E70">
         <v>200</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="2">
         <v>513</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>23</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -17285,11 +17285,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="2">
         <v>236</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>23</v>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17308,11 +17308,11 @@
       <c r="E72">
         <v>200</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="2">
         <v>4</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>23</v>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -17331,11 +17331,11 @@
       <c r="E73">
         <v>200</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="6">
         <v>0</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -17354,11 +17354,11 @@
       <c r="E74">
         <v>200</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="2">
         <v>28</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>23</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -17377,11 +17377,11 @@
       <c r="E75">
         <v>200</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="6">
         <v>0</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="G75" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -17423,11 +17423,11 @@
       <c r="E77">
         <v>200</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="6">
         <v>0</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -17446,11 +17446,11 @@
       <c r="E78">
         <v>200</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="6">
         <v>0</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -17492,11 +17492,11 @@
       <c r="E80">
         <v>200</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="2">
         <v>1</v>
       </c>
-      <c r="G80" s="7" t="s">
-        <v>23</v>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -17515,11 +17515,11 @@
       <c r="E81">
         <v>200</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="6">
         <v>0</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>10</v>
+      <c r="G81" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -17538,11 +17538,11 @@
       <c r="E82">
         <v>1152</v>
       </c>
-      <c r="F82" s="6">
-        <v>560</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
+      <c r="F82" s="2">
+        <v>536</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -17561,11 +17561,11 @@
       <c r="E83">
         <v>1152</v>
       </c>
-      <c r="F83" s="6">
-        <v>95</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>23</v>
+      <c r="F83" s="2">
+        <v>71</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -17584,11 +17584,11 @@
       <c r="E84">
         <v>1152</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="6">
         <v>0</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="G84" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -17607,11 +17607,11 @@
       <c r="E85">
         <v>1152</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="2">
         <v>2736</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>23</v>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="4">
-        <v>5436</v>
+        <v>5400</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>14</v>
@@ -17653,11 +17653,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="6">
-        <v>249</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>23</v>
+      <c r="F87" s="2">
+        <v>225</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17677,7 +17677,7 @@
         <v>576</v>
       </c>
       <c r="F88" s="4">
-        <v>3776</v>
+        <v>3572</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>14</v>
@@ -17699,11 +17699,11 @@
       <c r="E89">
         <v>576</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="2">
         <v>111</v>
       </c>
-      <c r="G89" s="7" t="s">
-        <v>23</v>
+      <c r="G89" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -17722,11 +17722,11 @@
       <c r="E90">
         <v>576</v>
       </c>
-      <c r="F90" s="6">
-        <v>556</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>23</v>
+      <c r="F90" s="2">
+        <v>532</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -17745,11 +17745,11 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="6">
-        <v>2787</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>23</v>
+      <c r="F91" s="2">
+        <v>2763</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -17768,11 +17768,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="6">
-        <v>887</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>23</v>
+      <c r="F92" s="2">
+        <v>863</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -17792,7 +17792,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="4">
-        <v>12814</v>
+        <v>12790</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>14</v>
@@ -17814,11 +17814,11 @@
       <c r="E94">
         <v>576</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="2">
         <v>2</v>
       </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -17837,11 +17837,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -17884,10 +17884,10 @@
         <v>288</v>
       </c>
       <c r="F97" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -17907,7 +17907,7 @@
         <v>144</v>
       </c>
       <c r="F98" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -17929,11 +17929,11 @@
       <c r="E99">
         <v>144</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="6">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="G99" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -17975,11 +17975,11 @@
       <c r="E101">
         <v>144</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="2">
         <v>2</v>
       </c>
-      <c r="G101" s="7" t="s">
-        <v>23</v>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -18090,11 +18090,11 @@
       <c r="E106">
         <v>144</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="2">
         <v>300</v>
       </c>
-      <c r="G106" s="7" t="s">
-        <v>23</v>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -18321,7 +18321,7 @@
         <v>192</v>
       </c>
       <c r="F116" s="2">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -18343,11 +18343,11 @@
       <c r="E117">
         <v>192</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="2">
         <v>63</v>
       </c>
-      <c r="G117" s="7" t="s">
-        <v>23</v>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -18389,11 +18389,11 @@
       <c r="E119">
         <v>192</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="6">
         <v>0</v>
       </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="G119" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -18412,11 +18412,11 @@
       <c r="E120">
         <v>192</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="2">
         <v>212</v>
       </c>
-      <c r="G120" s="7" t="s">
-        <v>23</v>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -18435,11 +18435,11 @@
       <c r="E121">
         <v>192</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="2">
         <v>137</v>
       </c>
-      <c r="G121" s="7" t="s">
-        <v>23</v>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -18643,7 +18643,7 @@
         <v>192</v>
       </c>
       <c r="F130" s="4">
-        <v>43733</v>
+        <v>43731</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -18665,11 +18665,11 @@
       <c r="E131">
         <v>192</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F131" s="2">
         <v>287</v>
       </c>
-      <c r="G131" s="7" t="s">
-        <v>23</v>
+      <c r="G131" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -18711,11 +18711,11 @@
       <c r="E133">
         <v>192</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F133" s="2">
         <v>185</v>
       </c>
-      <c r="G133" s="7" t="s">
-        <v>23</v>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -18803,11 +18803,11 @@
       <c r="E137">
         <v>192</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F137" s="2">
         <v>108</v>
       </c>
-      <c r="G137" s="7" t="s">
-        <v>23</v>
+      <c r="G137" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -18826,11 +18826,11 @@
       <c r="E138">
         <v>192</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F138" s="2">
         <v>99</v>
       </c>
-      <c r="G138" s="7" t="s">
-        <v>23</v>
+      <c r="G138" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -18849,11 +18849,11 @@
       <c r="E139">
         <v>192</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F139" s="2">
         <v>125</v>
       </c>
-      <c r="G139" s="7" t="s">
-        <v>23</v>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -18872,11 +18872,11 @@
       <c r="E140">
         <v>192</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="2">
         <v>17</v>
       </c>
-      <c r="G140" s="7" t="s">
-        <v>23</v>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -18895,11 +18895,11 @@
       <c r="E141">
         <v>192</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="2">
         <v>114</v>
       </c>
-      <c r="G141" s="7" t="s">
-        <v>23</v>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -18918,11 +18918,11 @@
       <c r="E142">
         <v>192</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F142" s="2">
         <v>122</v>
       </c>
-      <c r="G142" s="7" t="s">
-        <v>23</v>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -18941,11 +18941,11 @@
       <c r="E143">
         <v>192</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F143" s="2">
         <v>42</v>
       </c>
-      <c r="G143" s="7" t="s">
-        <v>23</v>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -18964,11 +18964,11 @@
       <c r="E144">
         <v>192</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="2">
         <v>66</v>
       </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -19030,11 +19030,11 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="6">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -19053,11 +19053,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="2">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -19145,11 +19145,11 @@
       <c r="E7">
         <v>144</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -19283,11 +19283,11 @@
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="6">
         <v>0</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -19329,11 +19329,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>111</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -19352,11 +19352,11 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="2">
         <v>49</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>23</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -19375,11 +19375,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="6">
         <v>0</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -19398,11 +19398,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="6">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -19514,7 +19514,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -19605,11 +19605,11 @@
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="6">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -19721,7 +19721,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19789,11 +19789,11 @@
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="4">
-        <v>8833</v>
+        <v>8821</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>14</v>
@@ -19835,11 +19835,11 @@
       <c r="E37">
         <v>120</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="6">
         <v>0</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -19927,11 +19927,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="6">
         <v>0</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20134,11 +20134,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="2">
         <v>37</v>
       </c>
-      <c r="G50" s="7" t="s">
-        <v>23</v>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20157,11 +20157,11 @@
       <c r="E51">
         <v>144</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="2">
         <v>48</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>23</v>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -20180,11 +20180,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="2">
         <v>54</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>23</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -20226,11 +20226,11 @@
       <c r="E54">
         <v>144</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="6">
         <v>0</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20249,11 +20249,11 @@
       <c r="E55">
         <v>144</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="6">
         <v>0</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -20272,11 +20272,11 @@
       <c r="E56">
         <v>144</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="2">
         <v>4</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>23</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -20295,11 +20295,11 @@
       <c r="E57">
         <v>144</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="6">
         <v>0</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -20318,11 +20318,11 @@
       <c r="E58">
         <v>144</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="6">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="4">
-        <v>2195</v>
+        <v>2579</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>14</v>
@@ -20410,11 +20410,11 @@
       <c r="E62">
         <v>96</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="6">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="G62" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -20433,11 +20433,11 @@
       <c r="E63">
         <v>120</v>
       </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>1019</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -20456,11 +20456,11 @@
       <c r="E64">
         <v>120</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="6">
         <v>0</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -20479,11 +20479,11 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="2">
         <v>1</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>23</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="2">
         <v>48</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>23</v>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20594,11 +20594,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="2">
         <v>42</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>23</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -20617,11 +20617,11 @@
       <c r="E71">
         <v>144</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -20640,11 +20640,11 @@
       <c r="E72">
         <v>144</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="6">
         <v>0</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -20686,11 +20686,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="2">
         <v>1</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>23</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -20710,7 +20710,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -20732,11 +20732,11 @@
       <c r="E76">
         <v>180</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="2">
         <v>4</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>23</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -20779,7 +20779,7 @@
         <v>144</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -20801,11 +20801,11 @@
       <c r="E79">
         <v>144</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="2">
         <v>10</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>23</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -20824,11 +20824,11 @@
       <c r="E80">
         <v>144</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="6">
         <v>0</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -20847,11 +20847,11 @@
       <c r="E81">
         <v>144</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="6">
         <v>0</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>10</v>
+      <c r="G81" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -20870,11 +20870,11 @@
       <c r="E82">
         <v>144</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="2">
         <v>33</v>
       </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -20939,11 +20939,11 @@
       <c r="E85">
         <v>144</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -20985,11 +20985,11 @@
       <c r="E87">
         <v>144</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>0</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -21101,7 +21101,7 @@
         <v>144</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -21146,11 +21146,11 @@
       <c r="E94">
         <v>144</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="6">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="G94" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -21169,11 +21169,11 @@
       <c r="E95">
         <v>144</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -22083,11 +22083,11 @@
       <c r="E32">
         <v>48</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="2">
         <v>2</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>23</v>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="4">
-        <v>21773</v>
+        <v>21293</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22287,11 +22287,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -22333,11 +22333,11 @@
       <c r="E10">
         <v>36</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="6">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -22356,11 +22356,11 @@
       <c r="E11">
         <v>72</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>88526</v>
+        <v>88514</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="4">
-        <v>34746</v>
+        <v>34722</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="4">
-        <v>22371</v>
+        <v>22323</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -22494,11 +22494,11 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="6">
         <v>0</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -22586,11 +22586,11 @@
       <c r="E21">
         <v>144</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="6">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -22675,11 +22675,11 @@
       <c r="E2">
         <v>1000</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="6">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22698,11 +22698,11 @@
       <c r="E3">
         <v>500</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="6">
         <v>0</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22721,11 +22721,11 @@
       <c r="E4">
         <v>1000</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="2">
         <v>917</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22768,7 +22768,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22813,11 +22813,11 @@
       <c r="E8">
         <v>400</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -22859,11 +22859,11 @@
       <c r="E10">
         <v>100</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="6">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -22882,11 +22882,11 @@
       <c r="E11">
         <v>100</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -22928,11 +22928,11 @@
       <c r="E13">
         <v>500</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="2">
         <v>5</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -22951,11 +22951,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>10</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>23</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22974,11 +22974,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>8</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -22997,11 +22997,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="2">
         <v>2</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>23</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>41426</v>
+        <v>55826</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="4">
-        <v>11938</v>
+        <v>11926</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>14</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="4">
-        <v>30950</v>
+        <v>30914</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="4">
-        <v>26780</v>
+        <v>15780</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>10971</v>
+        <v>10731</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -11426,11 +11426,11 @@
       <c r="E161">
         <v>24</v>
       </c>
-      <c r="F161" s="2">
-        <v>21</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="6">
+        <v>0</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="4">
-        <v>7885</v>
+        <v>7877</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>10112</v>
+        <v>9632</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>88450</v>
+        <v>88426</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>87877</v>
+        <v>88177</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>55976</v>
+        <v>55956</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>20</v>
+      <c r="F21" s="2">
+        <v>11</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="4">
-        <v>3627</v>
+        <v>3577</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>14</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="4">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>14</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="4">
-        <v>11462</v>
+        <v>11412</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -8391,7 +8391,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="4">
-        <v>4451</v>
+        <v>4401</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="4">
-        <v>2397</v>
+        <v>2347</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>14</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="4">
-        <v>2528</v>
+        <v>2478</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>14</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="4">
-        <v>4769</v>
+        <v>4717</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>14</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="4">
-        <v>8994</v>
+        <v>8944</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>14</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="4">
-        <v>10926</v>
+        <v>10876</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>14</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -11059,7 +11059,7 @@
         <v>24</v>
       </c>
       <c r="F145" s="4">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>14</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="4">
-        <v>13989</v>
+        <v>14139</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>69456</v>
+        <v>69462</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -14368,7 +14368,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="4">
-        <v>4713</v>
+        <v>4719</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="4">
-        <v>58517</v>
+        <v>58577</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>14</v>
@@ -14897,7 +14897,7 @@
         <v>72</v>
       </c>
       <c r="F45" s="4">
-        <v>21833</v>
+        <v>21839</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>14</v>
@@ -14920,7 +14920,7 @@
         <v>72</v>
       </c>
       <c r="F46" s="4">
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>14</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="4">
-        <v>6725</v>
+        <v>6731</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="4">
-        <v>4566</v>
+        <v>4572</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="4">
-        <v>14154</v>
+        <v>14160</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="4">
-        <v>7041</v>
+        <v>7047</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>14</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="4">
-        <v>13829</v>
+        <v>13925</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="4">
-        <v>7810</v>
+        <v>7814</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>14</v>
@@ -16274,7 +16274,7 @@
         <v>192</v>
       </c>
       <c r="F27" s="4">
-        <v>29614</v>
+        <v>30022</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>14</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="4">
-        <v>10406</v>
+        <v>10434</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="4">
-        <v>29294</v>
+        <v>29798</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>14</v>
@@ -16389,7 +16389,7 @@
         <v>72</v>
       </c>
       <c r="F32" s="4">
-        <v>709</v>
+        <v>1057</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>14</v>
@@ -16434,11 +16434,11 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="6">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>20</v>
+      <c r="F34" s="2">
+        <v>144</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -16527,7 +16527,7 @@
         <v>72</v>
       </c>
       <c r="F38" s="2">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -16573,7 +16573,7 @@
         <v>72</v>
       </c>
       <c r="F40" s="2">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -16619,7 +16619,7 @@
         <v>72</v>
       </c>
       <c r="F42" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -16711,7 +16711,7 @@
         <v>72</v>
       </c>
       <c r="F46" s="4">
-        <v>673</v>
+        <v>877</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>14</v>
@@ -16780,7 +16780,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="4">
-        <v>11400</v>
+        <v>11404</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>14</v>
@@ -16826,7 +16826,7 @@
         <v>192</v>
       </c>
       <c r="F51" s="4">
-        <v>8998</v>
+        <v>9001</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>14</v>
@@ -16941,7 +16941,7 @@
         <v>96</v>
       </c>
       <c r="F56" s="4">
-        <v>23229</v>
+        <v>23232</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>14</v>
@@ -16987,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="4">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>14</v>
@@ -17355,7 +17355,7 @@
         <v>200</v>
       </c>
       <c r="F74" s="2">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -17377,11 +17377,11 @@
       <c r="E75">
         <v>200</v>
       </c>
-      <c r="F75" s="6">
-        <v>0</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>20</v>
+      <c r="F75" s="2">
+        <v>200</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="4">
-        <v>22323</v>
+        <v>22312</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -22564,7 +22564,7 @@
         <v>144</v>
       </c>
       <c r="F20" s="4">
-        <v>16399</v>
+        <v>16411</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>88177</v>
+        <v>88127</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="6">
-        <v>366</v>
+        <v>66</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>18</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4">
-        <v>1381</v>
+        <v>1231</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>14</v>
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="4">
-        <v>353</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="F14" s="6">
+        <v>203</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="4">
-        <v>2982</v>
+        <v>2732</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -8160,11 +8160,11 @@
       <c r="E19">
         <v>50</v>
       </c>
-      <c r="F19" s="4">
-        <v>462</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="F19" s="6">
+        <v>212</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="4">
-        <v>61822</v>
+        <v>61322</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>14</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="4">
-        <v>27158</v>
+        <v>26658</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>14</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="4">
-        <v>39313</v>
+        <v>39113</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>14</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="4">
-        <v>40209</v>
+        <v>40009</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>14</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="4">
-        <v>36336</v>
+        <v>36136</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>14</v>
@@ -9702,7 +9702,7 @@
         <v>100</v>
       </c>
       <c r="F86" s="4">
-        <v>36318</v>
+        <v>36118</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>14</v>
@@ -19330,7 +19330,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="6">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>18</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>18</v>
@@ -19422,7 +19422,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="4">
-        <v>3815</v>
+        <v>3775</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>14</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="4">
-        <v>5075</v>
+        <v>5039</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="4">
-        <v>843</v>
+        <v>1218</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>55956</v>
+        <v>103956</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="4">
-        <v>26658</v>
+        <v>27658</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>14</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="6">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>18</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="4">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>14</v>
@@ -9012,7 +9012,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="4">
-        <v>3567</v>
+        <v>3572</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>14</v>
@@ -9403,7 +9403,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="4">
-        <v>15238</v>
+        <v>15240</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>14</v>
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="6">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>18</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="4">
-        <v>39113</v>
+        <v>39114</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>14</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="4">
-        <v>40009</v>
+        <v>40010</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>14</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="4">
-        <v>36136</v>
+        <v>36138</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>14</v>
@@ -9564,7 +9564,7 @@
         <v>100</v>
       </c>
       <c r="F80" s="4">
-        <v>15120</v>
+        <v>15127</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>14</v>
@@ -9587,7 +9587,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="4">
-        <v>9133</v>
+        <v>9134</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>14</v>
@@ -9725,7 +9725,7 @@
         <v>100</v>
       </c>
       <c r="F87" s="4">
-        <v>8328</v>
+        <v>8329</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>14</v>
@@ -9748,7 +9748,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="4">
-        <v>5865</v>
+        <v>5878</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>14</v>
@@ -9863,7 +9863,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="4">
-        <v>10329</v>
+        <v>10333</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>14</v>
@@ -9932,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="4">
-        <v>15065</v>
+        <v>15068</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>14</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>10731</v>
+        <v>11811</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -11196,11 +11196,11 @@
       <c r="E151">
         <v>12</v>
       </c>
-      <c r="F151" s="6">
-        <v>1</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>18</v>
+      <c r="F151" s="4">
+        <v>459</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>88127</v>
+        <v>92327</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="6">
-        <v>66</v>
+        <v>266</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>18</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="4">
-        <v>1218</v>
+        <v>968</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>23119</v>
+        <v>22869</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>103956</v>
+        <v>102956</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -7907,11 +7907,11 @@
       <c r="E8">
         <v>50</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="6">
+        <v>5</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8022,11 +8022,11 @@
       <c r="E13">
         <v>50</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>18</v>
@@ -8252,11 +8252,11 @@
       <c r="E23">
         <v>50</v>
       </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="4">
-        <v>2478</v>
+        <v>2484</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>14</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="4">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>14</v>
@@ -9012,7 +9012,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="4">
-        <v>3572</v>
+        <v>3522</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>14</v>
@@ -9403,7 +9403,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="4">
-        <v>15240</v>
+        <v>15238</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>14</v>
@@ -9472,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="6">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>18</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="4">
-        <v>39114</v>
+        <v>39113</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>14</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="4">
-        <v>40010</v>
+        <v>40009</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>14</v>
@@ -9541,7 +9541,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="4">
-        <v>36138</v>
+        <v>36136</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>14</v>
@@ -9564,7 +9564,7 @@
         <v>100</v>
       </c>
       <c r="F80" s="4">
-        <v>15127</v>
+        <v>15120</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>14</v>
@@ -9587,7 +9587,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="4">
-        <v>9134</v>
+        <v>9133</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>14</v>
@@ -9725,7 +9725,7 @@
         <v>100</v>
       </c>
       <c r="F87" s="4">
-        <v>8329</v>
+        <v>8379</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>14</v>
@@ -9748,7 +9748,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="4">
-        <v>5878</v>
+        <v>5865</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>14</v>
@@ -9771,7 +9771,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="4">
-        <v>12229</v>
+        <v>12129</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>14</v>
@@ -9863,7 +9863,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="4">
-        <v>10333</v>
+        <v>10229</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>14</v>
@@ -9932,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="4">
-        <v>15068</v>
+        <v>14965</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>14</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>11811</v>
+        <v>17811</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="4">
-        <v>66973</v>
+        <v>66873</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>69462</v>
+        <v>69442</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="4">
-        <v>18558</v>
+        <v>18713</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>14</v>
@@ -17124,11 +17124,11 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="F64" s="6">
+        <v>200</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="4">
-        <v>25964</v>
+        <v>25764</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>14</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="4">
-        <v>44296</v>
+        <v>44096</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>14</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>18</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="4">
-        <v>110410</v>
+        <v>110554</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>9432</v>
+        <v>9084</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>94077</v>
+        <v>94070</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>17595</v>
+        <v>21915</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="4">
-        <v>4667</v>
+        <v>4661</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>14</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="4">
-        <v>44598</v>
+        <v>44592</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>14</v>
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="4">
-        <v>8440</v>
+        <v>8439</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="4">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="4">
-        <v>8266</v>
+        <v>8260</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="4">
-        <v>36720</v>
+        <v>36714</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>14</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="4">
-        <v>59342</v>
+        <v>59341</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="4">
-        <v>30794</v>
+        <v>30793</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -15745,7 +15745,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="4">
-        <v>23982</v>
+        <v>23981</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="4">
-        <v>7621</v>
+        <v>7620</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>14</v>
@@ -16664,11 +16664,11 @@
       <c r="E44">
         <v>72</v>
       </c>
-      <c r="F44" s="2">
-        <v>1</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="6">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -16895,7 +16895,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="4">
-        <v>2929</v>
+        <v>2923</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>14</v>
@@ -17999,7 +17999,7 @@
         <v>144</v>
       </c>
       <c r="F102" s="4">
-        <v>17348</v>
+        <v>17342</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -18114,7 +18114,7 @@
         <v>144</v>
       </c>
       <c r="F107" s="4">
-        <v>17676</v>
+        <v>17670</v>
       </c>
       <c r="G107" s="5" t="s">
         <v>14</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="4">
-        <v>92615</v>
+        <v>92609</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>14</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="4">
-        <v>9163</v>
+        <v>9157</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>14</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="4">
-        <v>6341</v>
+        <v>6335</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>14</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="4">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>14</v>
@@ -20664,7 +20664,7 @@
         <v>240</v>
       </c>
       <c r="F73" s="4">
-        <v>5518</v>
+        <v>5451</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>14</v>
@@ -20710,7 +20710,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="4">
-        <v>190695</v>
+        <v>190689</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>8940</v>
+        <v>8939</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="4">
-        <v>21293</v>
+        <v>21287</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="4">
-        <v>15937</v>
+        <v>15930</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>88018</v>
+        <v>88012</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="4">
-        <v>9094</v>
+        <v>9017</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>94070</v>
+        <v>93570</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="4">
-        <v>27272</v>
+        <v>26972</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="4">
-        <v>1144</v>
+        <v>844</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>1271</v>
+        <v>471</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="4">
-        <v>14397</v>
+        <v>14197</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="4">
-        <v>22419</v>
+        <v>21419</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>102956</v>
+        <v>102206</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4">
-        <v>1231</v>
+        <v>1131</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>14</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="4">
-        <v>4944</v>
+        <v>4644</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="4">
-        <v>3572</v>
+        <v>3422</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>14</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="4">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>14</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8483,7 +8483,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="4">
-        <v>4614</v>
+        <v>4514</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>14</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="4">
-        <v>10776</v>
+        <v>10676</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>14</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -9403,7 +9403,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="4">
-        <v>15238</v>
+        <v>14938</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>14</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="4">
-        <v>38718</v>
+        <v>38518</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>14</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>21915</v>
+        <v>20595</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -11196,11 +11196,11 @@
       <c r="E151">
         <v>12</v>
       </c>
-      <c r="F151" s="6">
-        <v>0</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>20</v>
+      <c r="F151" s="4">
+        <v>459</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -11288,11 +11288,11 @@
       <c r="E155">
         <v>6</v>
       </c>
-      <c r="F155" s="6">
-        <v>0</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>20</v>
+      <c r="F155" s="4">
+        <v>619</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="4">
-        <v>14019</v>
+        <v>13947</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="4">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>14</v>
@@ -13336,7 +13336,7 @@
         <v>5</v>
       </c>
       <c r="F244" s="4">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>14</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="4">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G246" s="5" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>69297</v>
+        <v>69225</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="4">
-        <v>46660</v>
+        <v>46636</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>
@@ -14782,7 +14782,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="4">
-        <v>39592</v>
+        <v>39568</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>14</v>
@@ -17124,11 +17124,11 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="2">
-        <v>200</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="F64" s="6">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -17746,7 +17746,7 @@
         <v>576</v>
       </c>
       <c r="F91" s="2">
-        <v>2763</v>
+        <v>1611</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="2">
-        <v>863</v>
+        <v>287</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="4">
-        <v>171912</v>
+        <v>171852</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>14</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="4">
-        <v>4870</v>
+        <v>4798</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="4">
-        <v>83951</v>
+        <v>83915</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>14</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="4">
-        <v>24387</v>
+        <v>24315</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>8939</v>
+        <v>8363</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="4">
-        <v>21287</v>
+        <v>20519</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22196,7 +22196,7 @@
         <v>384</v>
       </c>
       <c r="F4" s="4">
-        <v>20525</v>
+        <v>19757</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>88012</v>
+        <v>87772</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="4">
-        <v>9017</v>
+        <v>8817</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>102206</v>
+        <v>101706</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="4">
-        <v>36714</v>
+        <v>36710</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>14</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="4">
-        <v>8817</v>
+        <v>8887</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -17746,7 +17746,7 @@
         <v>576</v>
       </c>
       <c r="F91" s="2">
-        <v>1611</v>
+        <v>2763</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="2">
-        <v>287</v>
+        <v>863</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -20526,7 +20526,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="4">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>14</v>
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="4">
-        <v>81</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>14</v>
+      <c r="F68" s="2">
+        <v>48</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20594,11 +20594,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="4">
-        <v>102</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>14</v>
+      <c r="F70" s="2">
+        <v>42</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="4">
-        <v>26972</v>
+        <v>27222</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="4">
-        <v>844</v>
+        <v>314</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>471</v>
+        <v>1271</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="4">
-        <v>14197</v>
+        <v>14397</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="4">
-        <v>11542</v>
+        <v>11170</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>14</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="4">
-        <v>21419</v>
+        <v>22419</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>101706</v>
+        <v>101206</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4">
-        <v>1131</v>
+        <v>1231</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>14</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="4">
-        <v>4644</v>
+        <v>4944</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>20595</v>
+        <v>21745</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="4">
-        <v>13947</v>
+        <v>14019</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="4">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>14</v>
@@ -13336,7 +13336,7 @@
         <v>5</v>
       </c>
       <c r="F244" s="4">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>14</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="4">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G246" s="5" t="s">
         <v>14</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="4">
-        <v>1310</v>
+        <v>1262</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="4">
-        <v>4661</v>
+        <v>4589</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>14</v>
@@ -14092,7 +14092,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="4">
-        <v>608</v>
+        <v>554</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>14</v>
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="4">
-        <v>8439</v>
+        <v>8391</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -14207,7 +14207,7 @@
         <v>144</v>
       </c>
       <c r="F15" s="4">
-        <v>3042</v>
+        <v>2994</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -14230,7 +14230,7 @@
         <v>144</v>
       </c>
       <c r="F16" s="4">
-        <v>11170</v>
+        <v>11098</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>69225</v>
+        <v>69081</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="4">
-        <v>58577</v>
+        <v>58517</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>14</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="4">
-        <v>47630</v>
+        <v>47198</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -14575,7 +14575,7 @@
         <v>576</v>
       </c>
       <c r="F31" s="4">
-        <v>9627</v>
+        <v>9483</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>14</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="4">
-        <v>46636</v>
+        <v>46624</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>
@@ -14690,7 +14690,7 @@
         <v>576</v>
       </c>
       <c r="F36" s="4">
-        <v>54266</v>
+        <v>54254</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>14</v>
@@ -14736,7 +14736,7 @@
         <v>576</v>
       </c>
       <c r="F38" s="2">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -14759,7 +14759,7 @@
         <v>576</v>
       </c>
       <c r="F39" s="4">
-        <v>6416</v>
+        <v>6404</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>14</v>
@@ -14782,7 +14782,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="4">
-        <v>39568</v>
+        <v>39556</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>14</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="4">
-        <v>11424</v>
+        <v>11352</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>14</v>
@@ -16274,7 +16274,7 @@
         <v>192</v>
       </c>
       <c r="F27" s="4">
-        <v>30267</v>
+        <v>30075</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>14</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="4">
-        <v>10434</v>
+        <v>10242</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="4">
-        <v>30007</v>
+        <v>29935</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>14</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>539</v>
+        <v>395</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="4">
-        <v>6135</v>
+        <v>6039</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>14</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="4">
-        <v>44096</v>
+        <v>43096</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>14</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="4">
-        <v>171852</v>
+        <v>171780</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>14</v>
@@ -18482,7 +18482,7 @@
         <v>192</v>
       </c>
       <c r="F123" s="4">
-        <v>4250</v>
+        <v>4010</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -18505,7 +18505,7 @@
         <v>192</v>
       </c>
       <c r="F124" s="4">
-        <v>1794</v>
+        <v>1674</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>14</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="4">
-        <v>7877</v>
+        <v>7876</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>14</v>
@@ -19330,7 +19330,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -20342,7 +20342,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="4">
-        <v>3795</v>
+        <v>3723</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>14</v>
@@ -20365,7 +20365,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="4">
-        <v>3040</v>
+        <v>2968</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>14</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="4">
-        <v>923</v>
+        <v>803</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>14</v>
@@ -20526,7 +20526,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="4">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>14</v>
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="2">
-        <v>48</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>81</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20594,11 +20594,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="2">
-        <v>42</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>102</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -20870,11 +20870,11 @@
       <c r="E82">
         <v>144</v>
       </c>
-      <c r="F82" s="2">
-        <v>27</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="F82" s="6">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -21305,7 +21305,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="4">
-        <v>64041</v>
+        <v>63969</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="4">
-        <v>24315</v>
+        <v>24243</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>8363</v>
+        <v>8939</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="4">
-        <v>20519</v>
+        <v>21287</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22196,7 +22196,7 @@
         <v>384</v>
       </c>
       <c r="F4" s="4">
-        <v>19757</v>
+        <v>20525</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>87772</v>
+        <v>88012</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="4">
-        <v>17945</v>
+        <v>17942</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>101206</v>
+        <v>115606</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="4">
-        <v>38518</v>
+        <v>42118</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>14</v>
@@ -12899,7 +12899,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>10</v>
@@ -12922,7 +12922,7 @@
         <v>10</v>
       </c>
       <c r="F226" s="4">
-        <v>1701</v>
+        <v>1681</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>14</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="4">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="4">
-        <v>1349</v>
+        <v>1329</v>
       </c>
       <c r="G241" s="5" t="s">
         <v>14</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="4">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>14</v>
@@ -13474,7 +13474,7 @@
         <v>5</v>
       </c>
       <c r="F250" s="4">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G250" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6924,11 +6924,11 @@
       <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" s="4">
-        <v>314</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="F12" s="2">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -11197,7 +11197,7 @@
         <v>12</v>
       </c>
       <c r="F151" s="4">
-        <v>459</v>
+        <v>127</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>14</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="4">
-        <v>46624</v>
+        <v>46264</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>
@@ -19238,7 +19238,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="4">
-        <v>12390</v>
+        <v>12365</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>14</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="4">
-        <v>13854</v>
+        <v>13254</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>93570</v>
+        <v>101970</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="4">
-        <v>27222</v>
+        <v>29672</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="4">
-        <v>17938</v>
+        <v>17935</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>14</v>
@@ -7060,7 +7060,7 @@
         <v>96</v>
       </c>
       <c r="F3" s="4">
-        <v>12213</v>
+        <v>12212</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -7083,7 +7083,7 @@
         <v>96</v>
       </c>
       <c r="F4" s="4">
-        <v>11269</v>
+        <v>11268</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -7106,7 +7106,7 @@
         <v>96</v>
       </c>
       <c r="F5" s="4">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -7290,7 +7290,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="4">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>14</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="4">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>12891</v>
+        <v>12890</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -7428,7 +7428,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="4">
-        <v>11170</v>
+        <v>11091</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>14</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="4">
-        <v>33192</v>
+        <v>33042</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>14</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="4">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>14</v>
@@ -13612,7 +13612,7 @@
         <v>100</v>
       </c>
       <c r="F256" s="4">
-        <v>89837</v>
+        <v>89825</v>
       </c>
       <c r="G256" s="5" t="s">
         <v>14</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="4">
-        <v>18317</v>
+        <v>18305</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>14</v>
@@ -15012,7 +15012,7 @@
         <v>360</v>
       </c>
       <c r="F50" s="4">
-        <v>8665</v>
+        <v>8661</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>14</v>
@@ -15081,7 +15081,7 @@
         <v>360</v>
       </c>
       <c r="F53" s="4">
-        <v>39358</v>
+        <v>39354</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>14</v>
@@ -15104,7 +15104,7 @@
         <v>360</v>
       </c>
       <c r="F54" s="4">
-        <v>40679</v>
+        <v>40675</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>14</v>
@@ -15173,7 +15173,7 @@
         <v>360</v>
       </c>
       <c r="F57" s="4">
-        <v>31874</v>
+        <v>31870</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>14</v>
@@ -15196,7 +15196,7 @@
         <v>360</v>
       </c>
       <c r="F58" s="4">
-        <v>34752</v>
+        <v>34748</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>14</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="4">
-        <v>10242</v>
+        <v>10230</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>14</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="4">
-        <v>29935</v>
+        <v>29923</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>14</v>
@@ -16780,7 +16780,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="4">
-        <v>11404</v>
+        <v>11401</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>14</v>
@@ -16803,7 +16803,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="4">
-        <v>11545</v>
+        <v>11542</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>14</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="4">
-        <v>6039</v>
+        <v>6027</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>14</v>
@@ -16941,7 +16941,7 @@
         <v>96</v>
       </c>
       <c r="F56" s="4">
-        <v>23232</v>
+        <v>23226</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>14</v>
@@ -16964,7 +16964,7 @@
         <v>96</v>
       </c>
       <c r="F57" s="4">
-        <v>21711</v>
+        <v>21705</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>14</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="4">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="4">
-        <v>5039</v>
+        <v>5038</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -19468,7 +19468,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="4">
-        <v>35252</v>
+        <v>35251</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>14</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="4">
-        <v>14828</v>
+        <v>14823</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="4">
-        <v>5181</v>
+        <v>5180</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>14</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="4">
-        <v>13254</v>
+        <v>12254</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>8939</v>
+        <v>8927</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="4">
-        <v>29672</v>
+        <v>29372</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="4">
-        <v>87960</v>
+        <v>87460</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>1271</v>
+        <v>471</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="4">
-        <v>14397</v>
+        <v>14197</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="4">
-        <v>22419</v>
+        <v>21419</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4">
-        <v>1231</v>
+        <v>1131</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>14</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="4">
-        <v>4944</v>
+        <v>4644</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>21745</v>
+        <v>22945</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -11128,7 +11128,7 @@
         <v>12</v>
       </c>
       <c r="F148" s="4">
-        <v>1182</v>
+        <v>1134</v>
       </c>
       <c r="G148" s="5" t="s">
         <v>14</v>
@@ -11289,7 +11289,7 @@
         <v>6</v>
       </c>
       <c r="F155" s="4">
-        <v>619</v>
+        <v>583</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="4">
-        <v>14019</v>
+        <v>13947</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -12508,7 +12508,7 @@
         <v>720</v>
       </c>
       <c r="F208" s="4">
-        <v>4430</v>
+        <v>4250</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -12531,7 +12531,7 @@
         <v>720</v>
       </c>
       <c r="F209" s="4">
-        <v>5232</v>
+        <v>5052</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -12600,7 +12600,7 @@
         <v>720</v>
       </c>
       <c r="F212" s="4">
-        <v>4134</v>
+        <v>3954</v>
       </c>
       <c r="G212" s="5" t="s">
         <v>14</v>
@@ -12623,7 +12623,7 @@
         <v>720</v>
       </c>
       <c r="F213" s="2">
-        <v>177</v>
+        <v>7</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>10</v>
@@ -12646,7 +12646,7 @@
         <v>720</v>
       </c>
       <c r="F214" s="2">
-        <v>3402</v>
+        <v>3222</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="4">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>14</v>
@@ -13336,7 +13336,7 @@
         <v>5</v>
       </c>
       <c r="F244" s="4">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>14</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="4">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G246" s="5" t="s">
         <v>14</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="4">
-        <v>66873</v>
+        <v>66009</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -14092,7 +14092,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="4">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>14</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="4">
-        <v>44592</v>
+        <v>44304</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>69081</v>
+        <v>68721</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="4">
-        <v>8260</v>
+        <v>8140</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="4">
-        <v>36710</v>
+        <v>36422</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>14</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>383</v>
+        <v>239</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="4">
-        <v>6027</v>
+        <v>5931</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>14</v>
@@ -16987,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="4">
-        <v>2575</v>
+        <v>2479</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>14</v>
@@ -17010,7 +17010,7 @@
         <v>48</v>
       </c>
       <c r="F59" s="4">
-        <v>5592</v>
+        <v>5544</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>14</v>
@@ -17033,7 +17033,7 @@
         <v>48</v>
       </c>
       <c r="F60" s="4">
-        <v>4951</v>
+        <v>4903</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>14</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="4">
-        <v>2578</v>
+        <v>2482</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>14</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>8927</v>
+        <v>8351</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="4">
-        <v>21287</v>
+        <v>20519</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22196,7 +22196,7 @@
         <v>384</v>
       </c>
       <c r="F4" s="4">
-        <v>20525</v>
+        <v>19757</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="4">
-        <v>15930</v>
+        <v>14778</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="4">
-        <v>78375</v>
+        <v>74919</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>14</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>88012</v>
+        <v>87772</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <v>101970</v>
+        <v>102278</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>115606</v>
+        <v>115614</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="4">
-        <v>42118</v>
+        <v>45718</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>14</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="4">
-        <v>22945</v>
+        <v>24865</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>14</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="4">
-        <v>4524</v>
+        <v>4523</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>14</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="4">
-        <v>14778</v>
+        <v>14791</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10668,7 +10668,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="4">
-        <v>5190</v>
+        <v>5188</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>14</v>
@@ -10691,7 +10691,7 @@
         <v>24</v>
       </c>
       <c r="F129" s="4">
-        <v>7819</v>
+        <v>7817</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>14</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="4">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="G190" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="4">
-        <v>8351</v>
+        <v>8347</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="4">
-        <v>20519</v>
+        <v>20515</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -22196,7 +22196,7 @@
         <v>384</v>
       </c>
       <c r="F4" s="4">
-        <v>19757</v>
+        <v>19753</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="4">
-        <v>48325</v>
+        <v>48313</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -22242,7 +22242,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="4">
-        <v>81349</v>
+        <v>81337</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>14</v>
@@ -22265,7 +22265,7 @@
         <v>384</v>
       </c>
       <c r="F7" s="4">
-        <v>47704</v>
+        <v>47692</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="4">
-        <v>30667</v>
+        <v>30691</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>14</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -52,28 +52,28 @@
     <t>FORRO N VINIFAN OFICIO CRISTAL 26</t>
   </si>
   <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>02211</t>
+  </si>
+  <si>
+    <t>7754807020022</t>
+  </si>
+  <si>
+    <t>FORRO N VINIFAN A4 CRISTAL 26</t>
+  </si>
+  <si>
+    <t>02204</t>
+  </si>
+  <si>
+    <t>7754807020077</t>
+  </si>
+  <si>
+    <t>FORRO N VINIFANCITO CRISTAL 25</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>02211</t>
-  </si>
-  <si>
-    <t>7754807020022</t>
-  </si>
-  <si>
-    <t>FORRO N VINIFAN A4 CRISTAL 26</t>
-  </si>
-  <si>
-    <t>✓ OK</t>
-  </si>
-  <si>
-    <t>02204</t>
-  </si>
-  <si>
-    <t>7754807020077</t>
-  </si>
-  <si>
-    <t>FORRO N VINIFANCITO CRISTAL 25</t>
   </si>
   <si>
     <t>02212</t>
@@ -6228,12 +6228,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FF065F46"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
@@ -6256,12 +6256,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6717,11 +6717,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>102278</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6729,22 +6729,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>266</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6755,7 +6755,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -6786,11 +6786,11 @@
       <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>13</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6809,11 +6809,11 @@
       <c r="E7">
         <v>25</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>29372</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6832,11 +6832,11 @@
       <c r="E8">
         <v>48</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>17942</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6855,11 +6855,11 @@
       <c r="E9">
         <v>48</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>48292</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6878,11 +6878,11 @@
       <c r="E10">
         <v>18</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>17008</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6901,11 +6901,11 @@
       <c r="E11">
         <v>36</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>17935</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6924,11 +6924,11 @@
       <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>14</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6947,11 +6947,11 @@
       <c r="E13">
         <v>50</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>89799</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6970,11 +6970,11 @@
       <c r="E14">
         <v>100</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>87460</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7036,11 +7036,11 @@
       <c r="E2">
         <v>96</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>10734</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7059,11 +7059,11 @@
       <c r="E3">
         <v>96</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>12212</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7082,11 +7082,11 @@
       <c r="E4">
         <v>96</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>11268</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7105,11 +7105,11 @@
       <c r="E5">
         <v>96</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>3275</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7128,11 +7128,11 @@
       <c r="E6">
         <v>48</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>12182</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7151,11 +7151,11 @@
       <c r="E7">
         <v>48</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>1453</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7174,11 +7174,11 @@
       <c r="E8">
         <v>48</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>9792</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7243,11 +7243,11 @@
       <c r="E11">
         <v>96</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>1</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7289,11 +7289,11 @@
       <c r="E13">
         <v>96</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>1393</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7312,11 +7312,11 @@
       <c r="E14">
         <v>400</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>471</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7335,11 +7335,11 @@
       <c r="E15">
         <v>100</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>14197</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7358,11 +7358,11 @@
       <c r="E16">
         <v>72</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>1099</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7381,11 +7381,11 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>12890</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7404,11 +7404,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>1</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7427,11 +7427,11 @@
       <c r="E19">
         <v>48</v>
       </c>
-      <c r="F19" s="4">
-        <v>11091</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="F19" s="2">
+        <v>10891</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7450,11 +7450,11 @@
       <c r="E20">
         <v>72</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>8</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7473,11 +7473,11 @@
       <c r="E21">
         <v>500</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>37382</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -7496,11 +7496,11 @@
       <c r="E22">
         <v>500</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>8783</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -7519,11 +7519,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="4">
         <v>6</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -7588,11 +7588,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>2098</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -7634,11 +7634,11 @@
       <c r="E28">
         <v>100</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>21419</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
+      <c r="G28" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -7657,11 +7657,11 @@
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>2465</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -7680,11 +7680,11 @@
       <c r="E30">
         <v>30</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>1</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -7703,11 +7703,11 @@
       <c r="E31">
         <v>100</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>1151</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7769,11 +7769,11 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7792,11 +7792,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>22869</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7838,11 +7838,11 @@
       <c r="E5">
         <v>50</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>115614</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7861,11 +7861,11 @@
       <c r="E6">
         <v>50</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>26</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7884,11 +7884,11 @@
       <c r="E7">
         <v>50</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>24</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7930,11 +7930,11 @@
       <c r="E9">
         <v>50</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>3</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7953,11 +7953,11 @@
       <c r="E10">
         <v>50</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>1131</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7976,11 +7976,11 @@
       <c r="E11">
         <v>50</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>19</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7999,11 +7999,11 @@
       <c r="E12">
         <v>50</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>14</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>203</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>4644</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8091,11 +8091,11 @@
       <c r="E16">
         <v>50</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8114,11 +8114,11 @@
       <c r="E17">
         <v>50</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>17</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8137,11 +8137,11 @@
       <c r="E18">
         <v>50</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>2732</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8160,11 +8160,11 @@
       <c r="E19">
         <v>50</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>162</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8183,11 +8183,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>160</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>11</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8229,11 +8229,11 @@
       <c r="E22">
         <v>50</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>18</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -8275,11 +8275,11 @@
       <c r="E24">
         <v>50</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>33042</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>14</v>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -8298,11 +8298,11 @@
       <c r="E25">
         <v>50</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>3422</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -8321,11 +8321,11 @@
       <c r="E26">
         <v>50</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>4950</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -8344,11 +8344,11 @@
       <c r="E27">
         <v>50</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="4">
         <v>7</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -8367,11 +8367,11 @@
       <c r="E28">
         <v>50</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>11356</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
+      <c r="G28" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -8390,11 +8390,11 @@
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>4401</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -8413,11 +8413,11 @@
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>2347</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -8436,11 +8436,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="4">
         <v>105</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="G31" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8459,11 +8459,11 @@
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>2484</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -8482,11 +8482,11 @@
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>4514</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>14</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -8505,11 +8505,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="4">
         <v>6</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="G34" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -8528,11 +8528,11 @@
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>8888</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>14</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -8551,11 +8551,11 @@
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>10676</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>14</v>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,11 +8597,11 @@
       <c r="E38">
         <v>50</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="4">
         <v>50</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -8643,11 +8643,11 @@
       <c r="E40">
         <v>50</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>4594</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>14</v>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -8666,11 +8666,11 @@
       <c r="E41">
         <v>50</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="4">
         <v>1</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -8689,11 +8689,11 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="4">
         <v>9</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -8735,11 +8735,11 @@
       <c r="E44">
         <v>100</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="2">
         <v>1349</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>14</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -8758,11 +8758,11 @@
       <c r="E45">
         <v>100</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>1726</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>14</v>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -8781,11 +8781,11 @@
       <c r="E46">
         <v>100</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>783</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,11 +8804,11 @@
       <c r="E47">
         <v>100</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>711</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>14</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,11 +8850,11 @@
       <c r="E49">
         <v>100</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="4">
         <v>267</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -8873,11 +8873,11 @@
       <c r="E50">
         <v>100</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>1673</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>14</v>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,11 +8896,11 @@
       <c r="E51">
         <v>100</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="4">
         <v>92</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="G51" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -8919,11 +8919,11 @@
       <c r="E52">
         <v>100</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="4">
         <v>5</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,11 +8942,11 @@
       <c r="E53">
         <v>100</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="4">
         <v>101</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="G53" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,11 +8965,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="4">
         <v>251</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -8988,11 +8988,11 @@
       <c r="E55">
         <v>100</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="2">
         <v>990</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>14</v>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -9011,11 +9011,11 @@
       <c r="E56">
         <v>100</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>3517</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>14</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -9034,11 +9034,11 @@
       <c r="E57">
         <v>100</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>8360</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>14</v>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,11 +9057,11 @@
       <c r="E58">
         <v>100</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="2">
         <v>4186</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>14</v>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -9080,11 +9080,11 @@
       <c r="E59">
         <v>100</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>16008</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>14</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -9103,11 +9103,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="4">
         <v>45</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -9126,11 +9126,11 @@
       <c r="E61">
         <v>100</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>1260</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>14</v>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -9149,11 +9149,11 @@
       <c r="E62">
         <v>100</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="2">
         <v>1181</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>14</v>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -9172,11 +9172,11 @@
       <c r="E63">
         <v>100</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="2">
         <v>1254</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>14</v>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -9195,11 +9195,11 @@
       <c r="E64">
         <v>100</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="4">
         <v>153</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,11 +9241,11 @@
       <c r="E66">
         <v>50</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>84</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -9264,11 +9264,11 @@
       <c r="E67">
         <v>100</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="4">
         <v>67</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -9287,11 +9287,11 @@
       <c r="E68">
         <v>100</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="2">
         <v>61322</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>14</v>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,11 +9310,11 @@
       <c r="E69">
         <v>100</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="2">
         <v>27658</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>14</v>
+      <c r="G69" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -9333,11 +9333,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="4">
         <v>67</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,11 +9379,11 @@
       <c r="E72">
         <v>100</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="2">
         <v>24247</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>14</v>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -9402,11 +9402,11 @@
       <c r="E73">
         <v>100</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="2">
         <v>14938</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>14</v>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,11 +9425,11 @@
       <c r="E74">
         <v>100</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>45718</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>14</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,11 +9448,11 @@
       <c r="E75">
         <v>100</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="2">
         <v>17370</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>14</v>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,11 +9471,11 @@
       <c r="E76">
         <v>100</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="4">
         <v>87</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,11 +9494,11 @@
       <c r="E77">
         <v>100</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="2">
         <v>39113</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>14</v>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,11 +9517,11 @@
       <c r="E78">
         <v>100</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="2">
         <v>40009</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>14</v>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,11 +9540,11 @@
       <c r="E79">
         <v>100</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="2">
         <v>36136</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>14</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,11 +9563,11 @@
       <c r="E80">
         <v>100</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="2">
         <v>15120</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>14</v>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,11 +9586,11 @@
       <c r="E81">
         <v>100</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="2">
         <v>9133</v>
       </c>
-      <c r="G81" s="5" t="s">
-        <v>14</v>
+      <c r="G81" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,11 +9609,11 @@
       <c r="E82">
         <v>100</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="4">
         <v>5</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="G82" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,11 +9632,11 @@
       <c r="E83">
         <v>100</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="2">
         <v>9991</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>14</v>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,11 +9655,11 @@
       <c r="E84">
         <v>100</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="2">
         <v>1167</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>14</v>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,11 +9678,11 @@
       <c r="E85">
         <v>100</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="4">
         <v>1</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,11 +9701,11 @@
       <c r="E86">
         <v>100</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>36118</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>14</v>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,11 +9724,11 @@
       <c r="E87">
         <v>100</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="2">
         <v>8384</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>14</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,11 +9747,11 @@
       <c r="E88">
         <v>100</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="2">
         <v>5865</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>14</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,11 +9770,11 @@
       <c r="E89">
         <v>100</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="2">
         <v>12129</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>14</v>
+      <c r="G89" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,11 +9793,11 @@
       <c r="E90">
         <v>100</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="2">
         <v>7597</v>
       </c>
-      <c r="G90" s="5" t="s">
-        <v>14</v>
+      <c r="G90" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -9816,11 +9816,11 @@
       <c r="E91">
         <v>100</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="2">
         <v>7636</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>14</v>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -9839,11 +9839,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="4">
         <v>445</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="G92" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -9862,11 +9862,11 @@
       <c r="E93">
         <v>100</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="2">
         <v>10229</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>14</v>
+      <c r="G93" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -9885,11 +9885,11 @@
       <c r="E94">
         <v>100</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="2">
         <v>2682</v>
       </c>
-      <c r="G94" s="5" t="s">
-        <v>14</v>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -9908,11 +9908,11 @@
       <c r="E95">
         <v>100</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="2">
         <v>4316</v>
       </c>
-      <c r="G95" s="5" t="s">
-        <v>14</v>
+      <c r="G95" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -9931,11 +9931,11 @@
       <c r="E96">
         <v>100</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="2">
         <v>14965</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>14</v>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -9954,11 +9954,11 @@
       <c r="E97">
         <v>120</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="4">
         <v>2</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="G97" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -9977,11 +9977,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="4">
         <v>1</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -10000,11 +10000,11 @@
       <c r="E99">
         <v>120</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="4">
         <v>1</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="G99" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,11 +10069,11 @@
       <c r="E102">
         <v>120</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="4">
         <v>2</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>10</v>
+      <c r="G102" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,11 +10092,11 @@
       <c r="E103">
         <v>120</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="4">
         <v>35</v>
       </c>
-      <c r="G103" s="3" t="s">
-        <v>10</v>
+      <c r="G103" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -10115,11 +10115,11 @@
       <c r="E104">
         <v>120</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>5926</v>
       </c>
-      <c r="G104" s="5" t="s">
-        <v>14</v>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -10138,11 +10138,11 @@
       <c r="E105">
         <v>120</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="2">
         <v>5634</v>
       </c>
-      <c r="G105" s="5" t="s">
-        <v>14</v>
+      <c r="G105" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -10161,11 +10161,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="2">
         <v>5695</v>
       </c>
-      <c r="G106" s="5" t="s">
-        <v>14</v>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -10184,11 +10184,11 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="2">
         <v>4844</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>14</v>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -10207,11 +10207,11 @@
       <c r="E108">
         <v>120</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="2">
         <v>2898</v>
       </c>
-      <c r="G108" s="5" t="s">
-        <v>14</v>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -10230,11 +10230,11 @@
       <c r="E109">
         <v>120</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="2">
         <v>4797</v>
       </c>
-      <c r="G109" s="5" t="s">
-        <v>14</v>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -10253,11 +10253,11 @@
       <c r="E110">
         <v>120</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="2">
         <v>4618</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>14</v>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,11 +10276,11 @@
       <c r="E111">
         <v>120</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="4">
         <v>8</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="G111" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -10299,11 +10299,11 @@
       <c r="E112">
         <v>120</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="2">
         <v>2768</v>
       </c>
-      <c r="G112" s="5" t="s">
-        <v>14</v>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,11 +10322,11 @@
       <c r="E113">
         <v>120</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="2">
         <v>2860</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>14</v>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,11 +10345,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="4">
         <v>47</v>
       </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="G114" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -10437,11 +10437,11 @@
       <c r="E118">
         <v>24</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="2">
         <v>1714</v>
       </c>
-      <c r="G118" s="5" t="s">
-        <v>14</v>
+      <c r="G118" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="4">
-        <v>24865</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>14</v>
+      <c r="F119" s="2">
+        <v>27745</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -10483,11 +10483,11 @@
       <c r="E120">
         <v>24</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>24871</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>14</v>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -10506,11 +10506,11 @@
       <c r="E121">
         <v>24</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="2">
         <v>4500</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>14</v>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -10529,11 +10529,11 @@
       <c r="E122">
         <v>24</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="2">
         <v>4042</v>
       </c>
-      <c r="G122" s="5" t="s">
-        <v>14</v>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -10552,11 +10552,11 @@
       <c r="E123">
         <v>24</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="2">
         <v>1219</v>
       </c>
-      <c r="G123" s="5" t="s">
-        <v>14</v>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -10575,11 +10575,11 @@
       <c r="E124">
         <v>24</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="2">
         <v>8495</v>
       </c>
-      <c r="G124" s="5" t="s">
-        <v>14</v>
+      <c r="G124" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -10598,11 +10598,11 @@
       <c r="E125">
         <v>24</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="2">
         <v>803</v>
       </c>
-      <c r="G125" s="5" t="s">
-        <v>14</v>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -10644,11 +10644,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="2">
         <v>430</v>
       </c>
-      <c r="G127" s="5" t="s">
-        <v>14</v>
+      <c r="G127" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -10667,11 +10667,11 @@
       <c r="E128">
         <v>24</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="2">
         <v>5188</v>
       </c>
-      <c r="G128" s="5" t="s">
-        <v>14</v>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -10690,11 +10690,11 @@
       <c r="E129">
         <v>24</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>7817</v>
       </c>
-      <c r="G129" s="5" t="s">
-        <v>14</v>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -10713,11 +10713,11 @@
       <c r="E130">
         <v>24</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>14625</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>14</v>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -10736,11 +10736,11 @@
       <c r="E131">
         <v>24</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="2">
         <v>9201</v>
       </c>
-      <c r="G131" s="5" t="s">
-        <v>14</v>
+      <c r="G131" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -10759,11 +10759,11 @@
       <c r="E132">
         <v>24</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="2">
         <v>9570</v>
       </c>
-      <c r="G132" s="5" t="s">
-        <v>14</v>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -10805,11 +10805,11 @@
       <c r="E134">
         <v>24</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>4578</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>14</v>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -10851,11 +10851,11 @@
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="2">
         <v>14103</v>
       </c>
-      <c r="G136" s="5" t="s">
-        <v>14</v>
+      <c r="G136" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -10920,11 +10920,11 @@
       <c r="E139">
         <v>30</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="4">
         <v>18</v>
       </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="G139" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -10943,11 +10943,11 @@
       <c r="E140">
         <v>30</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="4">
         <v>27</v>
       </c>
-      <c r="G140" s="3" t="s">
-        <v>10</v>
+      <c r="G140" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -11058,11 +11058,11 @@
       <c r="E145">
         <v>24</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="2">
         <v>408</v>
       </c>
-      <c r="G145" s="5" t="s">
-        <v>14</v>
+      <c r="G145" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -11081,11 +11081,11 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="4">
         <v>5</v>
       </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="G146" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -11104,11 +11104,11 @@
       <c r="E147">
         <v>24</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="4">
         <v>4</v>
       </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="G147" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -11127,11 +11127,11 @@
       <c r="E148">
         <v>12</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="2">
         <v>1134</v>
       </c>
-      <c r="G148" s="5" t="s">
-        <v>14</v>
+      <c r="G148" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -11173,11 +11173,11 @@
       <c r="E150">
         <v>12</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="4">
         <v>2</v>
       </c>
-      <c r="G150" s="3" t="s">
-        <v>10</v>
+      <c r="G150" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -11196,11 +11196,11 @@
       <c r="E151">
         <v>12</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="2">
         <v>127</v>
       </c>
-      <c r="G151" s="5" t="s">
-        <v>14</v>
+      <c r="G151" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -11219,11 +11219,11 @@
       <c r="E152">
         <v>12</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="2">
         <v>291</v>
       </c>
-      <c r="G152" s="5" t="s">
-        <v>14</v>
+      <c r="G152" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -11242,11 +11242,11 @@
       <c r="E153">
         <v>12</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="4">
         <v>3</v>
       </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="G153" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -11265,11 +11265,11 @@
       <c r="E154">
         <v>6</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="4">
         <v>1</v>
       </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="G154" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -11288,11 +11288,11 @@
       <c r="E155">
         <v>6</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="2">
         <v>583</v>
       </c>
-      <c r="G155" s="5" t="s">
-        <v>14</v>
+      <c r="G155" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -11311,11 +11311,11 @@
       <c r="E156">
         <v>6</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="4">
         <v>4</v>
       </c>
-      <c r="G156" s="3" t="s">
-        <v>10</v>
+      <c r="G156" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -11334,11 +11334,11 @@
       <c r="E157">
         <v>6</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="4">
         <v>1</v>
       </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="G157" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -11357,11 +11357,11 @@
       <c r="E158">
         <v>24</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="4">
         <v>5</v>
       </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="G158" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -11449,11 +11449,11 @@
       <c r="E162">
         <v>24</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="4">
         <v>1</v>
       </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="G162" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -11472,11 +11472,11 @@
       <c r="E163">
         <v>24</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="4">
         <v>4</v>
       </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="G163" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -11495,11 +11495,11 @@
       <c r="E164">
         <v>24</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="4">
         <v>2</v>
       </c>
-      <c r="G164" s="3" t="s">
-        <v>10</v>
+      <c r="G164" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -11518,11 +11518,11 @@
       <c r="E165">
         <v>24</v>
       </c>
-      <c r="F165" s="4">
+      <c r="F165" s="2">
         <v>258</v>
       </c>
-      <c r="G165" s="5" t="s">
-        <v>14</v>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -11564,11 +11564,11 @@
       <c r="E167">
         <v>72</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="2">
         <v>13947</v>
       </c>
-      <c r="G167" s="5" t="s">
-        <v>14</v>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -11587,11 +11587,11 @@
       <c r="E168">
         <v>72</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="4">
         <v>1</v>
       </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="G168" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -11702,11 +11702,11 @@
       <c r="E173">
         <v>72</v>
       </c>
-      <c r="F173" s="4">
+      <c r="F173" s="2">
         <v>1099</v>
       </c>
-      <c r="G173" s="5" t="s">
-        <v>14</v>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -11725,11 +11725,11 @@
       <c r="E174">
         <v>72</v>
       </c>
-      <c r="F174" s="4">
+      <c r="F174" s="2">
         <v>1474</v>
       </c>
-      <c r="G174" s="5" t="s">
-        <v>14</v>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -11771,11 +11771,11 @@
       <c r="E176">
         <v>48</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="4">
         <v>2</v>
       </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="G176" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -11794,11 +11794,11 @@
       <c r="E177">
         <v>48</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="4">
         <v>58</v>
       </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="G177" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -11817,11 +11817,11 @@
       <c r="E178">
         <v>48</v>
       </c>
-      <c r="F178" s="4">
+      <c r="F178" s="2">
         <v>386</v>
       </c>
-      <c r="G178" s="5" t="s">
-        <v>14</v>
+      <c r="G178" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -11840,11 +11840,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="4">
         <v>126</v>
       </c>
-      <c r="G179" s="3" t="s">
-        <v>10</v>
+      <c r="G179" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -11909,11 +11909,11 @@
       <c r="E182">
         <v>36</v>
       </c>
-      <c r="F182" s="4">
+      <c r="F182" s="2">
         <v>836</v>
       </c>
-      <c r="G182" s="5" t="s">
-        <v>14</v>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -11932,11 +11932,11 @@
       <c r="E183">
         <v>120</v>
       </c>
-      <c r="F183" s="4">
+      <c r="F183" s="2">
         <v>4041</v>
       </c>
-      <c r="G183" s="5" t="s">
-        <v>14</v>
+      <c r="G183" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -11955,11 +11955,11 @@
       <c r="E184">
         <v>96</v>
       </c>
-      <c r="F184" s="4">
+      <c r="F184" s="2">
         <v>5005</v>
       </c>
-      <c r="G184" s="5" t="s">
-        <v>14</v>
+      <c r="G184" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -11978,11 +11978,11 @@
       <c r="E185">
         <v>240</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="4">
         <v>808</v>
       </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="G185" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -12001,11 +12001,11 @@
       <c r="E186">
         <v>240</v>
       </c>
-      <c r="F186" s="4">
+      <c r="F186" s="2">
         <v>5779</v>
       </c>
-      <c r="G186" s="5" t="s">
-        <v>14</v>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -12024,11 +12024,11 @@
       <c r="E187">
         <v>240</v>
       </c>
-      <c r="F187" s="4">
+      <c r="F187" s="2">
         <v>4796</v>
       </c>
-      <c r="G187" s="5" t="s">
-        <v>14</v>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -12047,11 +12047,11 @@
       <c r="E188">
         <v>240</v>
       </c>
-      <c r="F188" s="4">
+      <c r="F188" s="2">
         <v>3110</v>
       </c>
-      <c r="G188" s="5" t="s">
-        <v>14</v>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -12070,11 +12070,11 @@
       <c r="E189">
         <v>72</v>
       </c>
-      <c r="F189" s="4">
+      <c r="F189" s="2">
         <v>1991</v>
       </c>
-      <c r="G189" s="5" t="s">
-        <v>14</v>
+      <c r="G189" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -12093,11 +12093,11 @@
       <c r="E190">
         <v>64</v>
       </c>
-      <c r="F190" s="4">
+      <c r="F190" s="2">
         <v>2409</v>
       </c>
-      <c r="G190" s="5" t="s">
-        <v>14</v>
+      <c r="G190" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -12162,11 +12162,11 @@
       <c r="E193">
         <v>40</v>
       </c>
-      <c r="F193" s="4">
+      <c r="F193" s="2">
         <v>8371</v>
       </c>
-      <c r="G193" s="5" t="s">
-        <v>14</v>
+      <c r="G193" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -12185,11 +12185,11 @@
       <c r="E194">
         <v>48</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="4">
         <v>11</v>
       </c>
-      <c r="G194" s="3" t="s">
-        <v>10</v>
+      <c r="G194" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -12208,11 +12208,11 @@
       <c r="E195">
         <v>48</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="4">
         <v>8</v>
       </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="G195" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -12277,11 +12277,11 @@
       <c r="E198">
         <v>10</v>
       </c>
-      <c r="F198" s="4">
+      <c r="F198" s="2">
         <v>164</v>
       </c>
-      <c r="G198" s="5" t="s">
-        <v>14</v>
+      <c r="G198" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -12323,11 +12323,11 @@
       <c r="E200">
         <v>120</v>
       </c>
-      <c r="F200" s="4">
+      <c r="F200" s="2">
         <v>1573</v>
       </c>
-      <c r="G200" s="5" t="s">
-        <v>14</v>
+      <c r="G200" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -12346,11 +12346,11 @@
       <c r="E201">
         <v>120</v>
       </c>
-      <c r="F201" s="4">
+      <c r="F201" s="2">
         <v>1831</v>
       </c>
-      <c r="G201" s="5" t="s">
-        <v>14</v>
+      <c r="G201" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -12369,11 +12369,11 @@
       <c r="E202">
         <v>120</v>
       </c>
-      <c r="F202" s="4">
+      <c r="F202" s="2">
         <v>2404</v>
       </c>
-      <c r="G202" s="5" t="s">
-        <v>14</v>
+      <c r="G202" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -12392,11 +12392,11 @@
       <c r="E203">
         <v>120</v>
       </c>
-      <c r="F203" s="4">
+      <c r="F203" s="2">
         <v>2176</v>
       </c>
-      <c r="G203" s="5" t="s">
-        <v>14</v>
+      <c r="G203" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -12415,11 +12415,11 @@
       <c r="E204">
         <v>160</v>
       </c>
-      <c r="F204" s="4">
+      <c r="F204" s="2">
         <v>4468</v>
       </c>
-      <c r="G204" s="5" t="s">
-        <v>14</v>
+      <c r="G204" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -12438,11 +12438,11 @@
       <c r="E205">
         <v>280</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="4">
         <v>40</v>
       </c>
-      <c r="G205" s="3" t="s">
-        <v>10</v>
+      <c r="G205" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -12461,11 +12461,11 @@
       <c r="E206">
         <v>360</v>
       </c>
-      <c r="F206" s="4">
+      <c r="F206" s="2">
         <v>3845</v>
       </c>
-      <c r="G206" s="5" t="s">
-        <v>14</v>
+      <c r="G206" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -12484,11 +12484,11 @@
       <c r="E207">
         <v>240</v>
       </c>
-      <c r="F207" s="4">
+      <c r="F207" s="2">
         <v>2747</v>
       </c>
-      <c r="G207" s="5" t="s">
-        <v>14</v>
+      <c r="G207" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -12507,11 +12507,11 @@
       <c r="E208">
         <v>720</v>
       </c>
-      <c r="F208" s="4">
+      <c r="F208" s="2">
         <v>4250</v>
       </c>
-      <c r="G208" s="5" t="s">
-        <v>14</v>
+      <c r="G208" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -12530,11 +12530,11 @@
       <c r="E209">
         <v>720</v>
       </c>
-      <c r="F209" s="4">
+      <c r="F209" s="2">
         <v>5052</v>
       </c>
-      <c r="G209" s="5" t="s">
-        <v>14</v>
+      <c r="G209" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -12599,11 +12599,11 @@
       <c r="E212">
         <v>720</v>
       </c>
-      <c r="F212" s="4">
+      <c r="F212" s="2">
         <v>3954</v>
       </c>
-      <c r="G212" s="5" t="s">
-        <v>14</v>
+      <c r="G212" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -12622,11 +12622,11 @@
       <c r="E213">
         <v>720</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="4">
         <v>7</v>
       </c>
-      <c r="G213" s="3" t="s">
-        <v>10</v>
+      <c r="G213" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -12645,11 +12645,11 @@
       <c r="E214">
         <v>720</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="4">
         <v>3222</v>
       </c>
-      <c r="G214" s="3" t="s">
-        <v>10</v>
+      <c r="G214" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -12668,11 +12668,11 @@
       <c r="E215">
         <v>600</v>
       </c>
-      <c r="F215" s="4">
+      <c r="F215" s="2">
         <v>5347</v>
       </c>
-      <c r="G215" s="5" t="s">
-        <v>14</v>
+      <c r="G215" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -12691,11 +12691,11 @@
       <c r="E216">
         <v>5</v>
       </c>
-      <c r="F216" s="4">
+      <c r="F216" s="2">
         <v>90</v>
       </c>
-      <c r="G216" s="5" t="s">
-        <v>14</v>
+      <c r="G216" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -12714,11 +12714,11 @@
       <c r="E217">
         <v>5</v>
       </c>
-      <c r="F217" s="4">
+      <c r="F217" s="2">
         <v>384</v>
       </c>
-      <c r="G217" s="5" t="s">
-        <v>14</v>
+      <c r="G217" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -12737,11 +12737,11 @@
       <c r="E218">
         <v>5</v>
       </c>
-      <c r="F218" s="4">
+      <c r="F218" s="2">
         <v>125</v>
       </c>
-      <c r="G218" s="5" t="s">
-        <v>14</v>
+      <c r="G218" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -12760,11 +12760,11 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="4">
         <v>1</v>
       </c>
-      <c r="G219" s="3" t="s">
-        <v>10</v>
+      <c r="G219" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -12806,11 +12806,11 @@
       <c r="E221">
         <v>10</v>
       </c>
-      <c r="F221" s="4">
+      <c r="F221" s="2">
         <v>3242</v>
       </c>
-      <c r="G221" s="5" t="s">
-        <v>14</v>
+      <c r="G221" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -12829,11 +12829,11 @@
       <c r="E222">
         <v>10</v>
       </c>
-      <c r="F222" s="4">
+      <c r="F222" s="2">
         <v>873</v>
       </c>
-      <c r="G222" s="5" t="s">
-        <v>14</v>
+      <c r="G222" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -12852,11 +12852,11 @@
       <c r="E223">
         <v>10</v>
       </c>
-      <c r="F223" s="4">
+      <c r="F223" s="2">
         <v>2154</v>
       </c>
-      <c r="G223" s="5" t="s">
-        <v>14</v>
+      <c r="G223" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -12875,11 +12875,11 @@
       <c r="E224">
         <v>10</v>
       </c>
-      <c r="F224" s="4">
+      <c r="F224" s="2">
         <v>1484</v>
       </c>
-      <c r="G224" s="5" t="s">
-        <v>14</v>
+      <c r="G224" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -12898,11 +12898,11 @@
       <c r="E225">
         <v>10</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="4">
         <v>30</v>
       </c>
-      <c r="G225" s="3" t="s">
-        <v>10</v>
+      <c r="G225" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -12921,11 +12921,11 @@
       <c r="E226">
         <v>10</v>
       </c>
-      <c r="F226" s="4">
+      <c r="F226" s="2">
         <v>1681</v>
       </c>
-      <c r="G226" s="5" t="s">
-        <v>14</v>
+      <c r="G226" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -12944,11 +12944,11 @@
       <c r="E227">
         <v>10</v>
       </c>
-      <c r="F227" s="4">
+      <c r="F227" s="2">
         <v>206</v>
       </c>
-      <c r="G227" s="5" t="s">
-        <v>14</v>
+      <c r="G227" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -12990,11 +12990,11 @@
       <c r="E229">
         <v>10</v>
       </c>
-      <c r="F229" s="4">
+      <c r="F229" s="2">
         <v>444</v>
       </c>
-      <c r="G229" s="5" t="s">
-        <v>14</v>
+      <c r="G229" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -13013,11 +13013,11 @@
       <c r="E230">
         <v>5</v>
       </c>
-      <c r="F230" s="4">
+      <c r="F230" s="2">
         <v>566</v>
       </c>
-      <c r="G230" s="5" t="s">
-        <v>14</v>
+      <c r="G230" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -13059,11 +13059,11 @@
       <c r="E232">
         <v>5</v>
       </c>
-      <c r="F232" s="4">
+      <c r="F232" s="2">
         <v>252</v>
       </c>
-      <c r="G232" s="5" t="s">
-        <v>14</v>
+      <c r="G232" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -13082,11 +13082,11 @@
       <c r="E233">
         <v>5</v>
       </c>
-      <c r="F233" s="4">
+      <c r="F233" s="2">
         <v>170</v>
       </c>
-      <c r="G233" s="5" t="s">
-        <v>14</v>
+      <c r="G233" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="4">
         <v>1</v>
       </c>
-      <c r="G234" s="3" t="s">
-        <v>10</v>
+      <c r="G234" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13128,11 +13128,11 @@
       <c r="E235">
         <v>5</v>
       </c>
-      <c r="F235" s="4">
+      <c r="F235" s="2">
         <v>290</v>
       </c>
-      <c r="G235" s="5" t="s">
-        <v>14</v>
+      <c r="G235" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -13151,11 +13151,11 @@
       <c r="E236">
         <v>5</v>
       </c>
-      <c r="F236" s="4">
+      <c r="F236" s="2">
         <v>222</v>
       </c>
-      <c r="G236" s="5" t="s">
-        <v>14</v>
+      <c r="G236" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -13174,11 +13174,11 @@
       <c r="E237">
         <v>5</v>
       </c>
-      <c r="F237" s="4">
+      <c r="F237" s="2">
         <v>256</v>
       </c>
-      <c r="G237" s="5" t="s">
-        <v>14</v>
+      <c r="G237" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -13197,11 +13197,11 @@
       <c r="E238">
         <v>5</v>
       </c>
-      <c r="F238" s="4">
+      <c r="F238" s="2">
         <v>204</v>
       </c>
-      <c r="G238" s="5" t="s">
-        <v>14</v>
+      <c r="G238" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -13220,11 +13220,11 @@
       <c r="E239">
         <v>5</v>
       </c>
-      <c r="F239" s="4">
+      <c r="F239" s="2">
         <v>262</v>
       </c>
-      <c r="G239" s="5" t="s">
-        <v>14</v>
+      <c r="G239" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -13243,11 +13243,11 @@
       <c r="E240">
         <v>5</v>
       </c>
-      <c r="F240" s="4">
+      <c r="F240" s="2">
         <v>117</v>
       </c>
-      <c r="G240" s="5" t="s">
-        <v>14</v>
+      <c r="G240" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -13266,11 +13266,11 @@
       <c r="E241">
         <v>5</v>
       </c>
-      <c r="F241" s="4">
+      <c r="F241" s="2">
         <v>1329</v>
       </c>
-      <c r="G241" s="5" t="s">
-        <v>14</v>
+      <c r="G241" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -13312,11 +13312,11 @@
       <c r="E243">
         <v>5</v>
       </c>
-      <c r="F243" s="4">
+      <c r="F243" s="2">
         <v>155</v>
       </c>
-      <c r="G243" s="5" t="s">
-        <v>14</v>
+      <c r="G243" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -13335,11 +13335,11 @@
       <c r="E244">
         <v>5</v>
       </c>
-      <c r="F244" s="4">
+      <c r="F244" s="2">
         <v>116</v>
       </c>
-      <c r="G244" s="5" t="s">
-        <v>14</v>
+      <c r="G244" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -13381,11 +13381,11 @@
       <c r="E246">
         <v>5</v>
       </c>
-      <c r="F246" s="4">
+      <c r="F246" s="2">
         <v>91</v>
       </c>
-      <c r="G246" s="5" t="s">
-        <v>14</v>
+      <c r="G246" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -13404,11 +13404,11 @@
       <c r="E247">
         <v>5</v>
       </c>
-      <c r="F247" s="4">
+      <c r="F247" s="2">
         <v>172</v>
       </c>
-      <c r="G247" s="5" t="s">
-        <v>14</v>
+      <c r="G247" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -13427,11 +13427,11 @@
       <c r="E248">
         <v>5</v>
       </c>
-      <c r="F248" s="4">
+      <c r="F248" s="2">
         <v>32</v>
       </c>
-      <c r="G248" s="5" t="s">
-        <v>14</v>
+      <c r="G248" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -13473,11 +13473,11 @@
       <c r="E250">
         <v>5</v>
       </c>
-      <c r="F250" s="4">
+      <c r="F250" s="2">
         <v>214</v>
       </c>
-      <c r="G250" s="5" t="s">
-        <v>14</v>
+      <c r="G250" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -13565,11 +13565,11 @@
       <c r="E254">
         <v>40</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="4">
         <v>11</v>
       </c>
-      <c r="G254" s="3" t="s">
-        <v>10</v>
+      <c r="G254" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -13588,11 +13588,11 @@
       <c r="E255">
         <v>100</v>
       </c>
-      <c r="F255" s="4">
+      <c r="F255" s="2">
         <v>197267</v>
       </c>
-      <c r="G255" s="5" t="s">
-        <v>14</v>
+      <c r="G255" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -13611,11 +13611,11 @@
       <c r="E256">
         <v>100</v>
       </c>
-      <c r="F256" s="4">
+      <c r="F256" s="2">
         <v>89825</v>
       </c>
-      <c r="G256" s="5" t="s">
-        <v>14</v>
+      <c r="G256" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -13634,11 +13634,11 @@
       <c r="E257">
         <v>5</v>
       </c>
-      <c r="F257" s="4">
+      <c r="F257" s="2">
         <v>606</v>
       </c>
-      <c r="G257" s="5" t="s">
-        <v>14</v>
+      <c r="G257" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -13657,11 +13657,11 @@
       <c r="E258">
         <v>5</v>
       </c>
-      <c r="F258" s="4">
+      <c r="F258" s="2">
         <v>354</v>
       </c>
-      <c r="G258" s="5" t="s">
-        <v>14</v>
+      <c r="G258" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -13680,11 +13680,11 @@
       <c r="E259">
         <v>5</v>
       </c>
-      <c r="F259" s="4">
+      <c r="F259" s="2">
         <v>88</v>
       </c>
-      <c r="G259" s="5" t="s">
-        <v>14</v>
+      <c r="G259" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -13703,11 +13703,11 @@
       <c r="E260">
         <v>5</v>
       </c>
-      <c r="F260" s="4">
+      <c r="F260" s="2">
         <v>286</v>
       </c>
-      <c r="G260" s="5" t="s">
-        <v>14</v>
+      <c r="G260" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -13726,11 +13726,11 @@
       <c r="E261">
         <v>5</v>
       </c>
-      <c r="F261" s="4">
+      <c r="F261" s="2">
         <v>71</v>
       </c>
-      <c r="G261" s="5" t="s">
-        <v>14</v>
+      <c r="G261" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -13749,11 +13749,11 @@
       <c r="E262">
         <v>5</v>
       </c>
-      <c r="F262" s="4">
+      <c r="F262" s="2">
         <v>327</v>
       </c>
-      <c r="G262" s="5" t="s">
-        <v>14</v>
+      <c r="G262" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -13772,11 +13772,11 @@
       <c r="E263">
         <v>5</v>
       </c>
-      <c r="F263" s="4">
+      <c r="F263" s="2">
         <v>238</v>
       </c>
-      <c r="G263" s="5" t="s">
-        <v>14</v>
+      <c r="G263" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -13795,11 +13795,11 @@
       <c r="E264">
         <v>5</v>
       </c>
-      <c r="F264" s="4">
+      <c r="F264" s="2">
         <v>162</v>
       </c>
-      <c r="G264" s="5" t="s">
-        <v>14</v>
+      <c r="G264" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -13818,11 +13818,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="4">
+      <c r="F265" s="2">
         <v>26</v>
       </c>
-      <c r="G265" s="5" t="s">
-        <v>14</v>
+      <c r="G265" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -13841,11 +13841,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="4">
+      <c r="F266" s="2">
         <v>25</v>
       </c>
-      <c r="G266" s="5" t="s">
-        <v>14</v>
+      <c r="G266" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -13907,11 +13907,11 @@
       <c r="E2">
         <v>288</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>20464</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -13930,11 +13930,11 @@
       <c r="E3">
         <v>144</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -13976,11 +13976,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>1262</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -13999,11 +13999,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>32</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14022,11 +14022,11 @@
       <c r="E7">
         <v>144</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>66009</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -14045,11 +14045,11 @@
       <c r="E8">
         <v>72</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>4589</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -14091,11 +14091,11 @@
       <c r="E10">
         <v>18</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>518</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -14114,11 +14114,11 @@
       <c r="E11">
         <v>144</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>44304</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -14137,11 +14137,11 @@
       <c r="E12">
         <v>144</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>8443</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -14160,11 +14160,11 @@
       <c r="E13">
         <v>144</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>498</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -14183,11 +14183,11 @@
       <c r="E14">
         <v>144</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>8391</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -14206,11 +14206,11 @@
       <c r="E15">
         <v>144</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>2994</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -14229,11 +14229,11 @@
       <c r="E16">
         <v>144</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>11098</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -14252,11 +14252,11 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>68721</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -14298,11 +14298,11 @@
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>2720</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -14367,11 +14367,11 @@
       <c r="E22">
         <v>12</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>4719</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -14390,11 +14390,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>8140</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>14</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -14413,11 +14413,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="4">
         <v>1</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -14436,11 +14436,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>15983</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -14459,11 +14459,11 @@
       <c r="E26">
         <v>60</v>
       </c>
-      <c r="F26" s="4">
-        <v>30691</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
+      <c r="F26" s="2">
+        <v>30749</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -14482,11 +14482,11 @@
       <c r="E27">
         <v>60</v>
       </c>
-      <c r="F27" s="4">
-        <v>58517</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>14</v>
+      <c r="F27" s="2">
+        <v>58601</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -14505,11 +14505,11 @@
       <c r="E28">
         <v>576</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>28024</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
+      <c r="G28" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -14528,11 +14528,11 @@
       <c r="E29">
         <v>576</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>47198</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -14551,11 +14551,11 @@
       <c r="E30">
         <v>576</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>28635</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -14574,11 +14574,11 @@
       <c r="E31">
         <v>576</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>9483</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -14597,11 +14597,11 @@
       <c r="E32">
         <v>576</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>11690</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -14620,11 +14620,11 @@
       <c r="E33">
         <v>576</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>8001</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>14</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -14643,11 +14643,11 @@
       <c r="E34">
         <v>576</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>46264</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>14</v>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -14666,11 +14666,11 @@
       <c r="E35">
         <v>576</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="4">
         <v>2302</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -14689,11 +14689,11 @@
       <c r="E36">
         <v>576</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>54254</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>14</v>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -14712,11 +14712,11 @@
       <c r="E37">
         <v>576</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="4">
         <v>1457</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -14735,11 +14735,11 @@
       <c r="E38">
         <v>576</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="4">
         <v>51</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -14758,11 +14758,11 @@
       <c r="E39">
         <v>576</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>6404</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>14</v>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -14781,11 +14781,11 @@
       <c r="E40">
         <v>576</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>39556</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>14</v>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14804,11 +14804,11 @@
       <c r="E41">
         <v>576</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="4">
         <v>2846</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -14827,11 +14827,11 @@
       <c r="E42">
         <v>576</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="4">
         <v>969</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -14873,11 +14873,11 @@
       <c r="E44">
         <v>576</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="4">
         <v>5</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -14896,11 +14896,11 @@
       <c r="E45">
         <v>72</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>21839</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>14</v>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -14919,11 +14919,11 @@
       <c r="E46">
         <v>72</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>2202</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -14942,11 +14942,11 @@
       <c r="E47">
         <v>288</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>6214</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>14</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -14965,11 +14965,11 @@
       <c r="E48">
         <v>144</v>
       </c>
-      <c r="F48" s="4">
-        <v>36422</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>14</v>
+      <c r="F48" s="2">
+        <v>36506</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -14988,11 +14988,11 @@
       <c r="E49">
         <v>36</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>18305</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>14</v>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -15011,11 +15011,11 @@
       <c r="E50">
         <v>360</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>8661</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>14</v>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -15034,11 +15034,11 @@
       <c r="E51">
         <v>360</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>23432</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>14</v>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -15057,11 +15057,11 @@
       <c r="E52">
         <v>360</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>9527</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>14</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -15080,11 +15080,11 @@
       <c r="E53">
         <v>360</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>39354</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>14</v>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -15103,11 +15103,11 @@
       <c r="E54">
         <v>360</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="2">
         <v>40675</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>14</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -15126,11 +15126,11 @@
       <c r="E55">
         <v>360</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="2">
         <v>9021</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>14</v>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -15149,11 +15149,11 @@
       <c r="E56">
         <v>360</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>30924</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>14</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -15172,11 +15172,11 @@
       <c r="E57">
         <v>360</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>31870</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>14</v>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -15195,11 +15195,11 @@
       <c r="E58">
         <v>360</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="2">
         <v>34748</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>14</v>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -15218,11 +15218,11 @@
       <c r="E59">
         <v>12</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>592</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>14</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -15264,11 +15264,11 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>3471</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>14</v>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -15333,11 +15333,11 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>2609</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>14</v>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -15356,11 +15356,11 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="4">
         <v>2</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -15517,11 +15517,11 @@
       <c r="E72">
         <v>144</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="2">
         <v>1039</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>14</v>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -15540,11 +15540,11 @@
       <c r="E73">
         <v>144</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="2">
         <v>924</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>14</v>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -15563,11 +15563,11 @@
       <c r="E74">
         <v>144</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>6934</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>14</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -15586,11 +15586,11 @@
       <c r="E75">
         <v>144</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="2">
         <v>1680</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>14</v>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -15609,11 +15609,11 @@
       <c r="E76">
         <v>144</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="2">
         <v>4366</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>14</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -15632,11 +15632,11 @@
       <c r="E77">
         <v>144</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="2">
         <v>4195</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>14</v>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -15698,11 +15698,11 @@
       <c r="E2">
         <v>144</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>59341</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -15721,11 +15721,11 @@
       <c r="E3">
         <v>144</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>30793</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -15744,11 +15744,11 @@
       <c r="E4">
         <v>144</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>23981</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -15767,11 +15767,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -15813,11 +15813,11 @@
       <c r="E7">
         <v>144</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>13587</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -15836,11 +15836,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>2903</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -15859,11 +15859,11 @@
       <c r="E9">
         <v>144</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>10360</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -15882,11 +15882,11 @@
       <c r="E10">
         <v>288</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>7912</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -15905,11 +15905,11 @@
       <c r="E11">
         <v>144</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>4572</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -15928,11 +15928,11 @@
       <c r="E12">
         <v>144</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>8143</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -15951,11 +15951,11 @@
       <c r="E13">
         <v>144</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>7</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -15974,11 +15974,11 @@
       <c r="E14">
         <v>96</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>6719</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -15997,11 +15997,11 @@
       <c r="E15">
         <v>96</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>4523</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -16020,11 +16020,11 @@
       <c r="E16">
         <v>96</v>
       </c>
-      <c r="F16" s="4">
-        <v>8957</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
+      <c r="F16" s="2">
+        <v>9006</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -16043,11 +16043,11 @@
       <c r="E17">
         <v>192</v>
       </c>
-      <c r="F17" s="4">
-        <v>13437</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
+      <c r="F17" s="2">
+        <v>13633</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -16066,11 +16066,11 @@
       <c r="E18">
         <v>192</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>14160</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -16089,11 +16089,11 @@
       <c r="E19">
         <v>192</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>7103</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -16112,11 +16112,11 @@
       <c r="E20">
         <v>192</v>
       </c>
-      <c r="F20" s="4">
-        <v>13925</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>14</v>
+      <c r="F20" s="2">
+        <v>14160</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -16135,11 +16135,11 @@
       <c r="E21">
         <v>192</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>7814</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -16250,11 +16250,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>11352</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -16273,11 +16273,11 @@
       <c r="E27">
         <v>192</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>30075</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>14</v>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -16319,11 +16319,11 @@
       <c r="E29">
         <v>192</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>10230</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -16342,11 +16342,11 @@
       <c r="E30">
         <v>192</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>29923</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -16365,11 +16365,11 @@
       <c r="E31">
         <v>96</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>7620</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -16388,11 +16388,11 @@
       <c r="E32">
         <v>72</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>1057</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -16411,11 +16411,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="4">
         <v>713</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16434,11 +16434,11 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="4">
         <v>146</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="G34" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -16457,11 +16457,11 @@
       <c r="E35">
         <v>144</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="4">
         <v>114</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -16480,11 +16480,11 @@
       <c r="E36">
         <v>72</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="4">
         <v>30</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -16503,11 +16503,11 @@
       <c r="E37">
         <v>144</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="4">
         <v>50</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -16526,11 +16526,11 @@
       <c r="E38">
         <v>72</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="4">
         <v>151</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -16549,11 +16549,11 @@
       <c r="E39">
         <v>144</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>870</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>14</v>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -16572,11 +16572,11 @@
       <c r="E40">
         <v>72</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="4">
         <v>167</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -16595,11 +16595,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="4">
         <v>166</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16618,11 +16618,11 @@
       <c r="E42">
         <v>72</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="4">
         <v>278</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16641,11 +16641,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="4">
         <v>253</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>10</v>
+      <c r="G43" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -16687,11 +16687,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="4">
         <v>126</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -16710,11 +16710,11 @@
       <c r="E46">
         <v>72</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>877</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -16733,11 +16733,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>1256</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>14</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -16756,11 +16756,11 @@
       <c r="E48">
         <v>96</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="2">
         <v>15257</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>14</v>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -16779,11 +16779,11 @@
       <c r="E49">
         <v>96</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>11401</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>14</v>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -16802,11 +16802,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>11542</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>14</v>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -16825,11 +16825,11 @@
       <c r="E51">
         <v>192</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>9001</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>14</v>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -16848,11 +16848,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="4">
         <v>239</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -16871,11 +16871,11 @@
       <c r="E53">
         <v>96</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>5931</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>14</v>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -16894,11 +16894,11 @@
       <c r="E54">
         <v>96</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="2">
         <v>2923</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>14</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -16917,11 +16917,11 @@
       <c r="E55">
         <v>96</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="2">
         <v>15269</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>14</v>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -16940,11 +16940,11 @@
       <c r="E56">
         <v>96</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>23226</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>14</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -16963,11 +16963,11 @@
       <c r="E57">
         <v>96</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>21705</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>14</v>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -16986,11 +16986,11 @@
       <c r="E58">
         <v>96</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="2">
         <v>2479</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>14</v>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -17009,11 +17009,11 @@
       <c r="E59">
         <v>48</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>5544</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>14</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -17032,11 +17032,11 @@
       <c r="E60">
         <v>48</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>4903</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>14</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -17078,11 +17078,11 @@
       <c r="E62">
         <v>576</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="2">
         <v>13760</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>14</v>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -17101,11 +17101,11 @@
       <c r="E63">
         <v>576</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="2">
         <v>3555</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>14</v>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -17147,11 +17147,11 @@
       <c r="E65">
         <v>200</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="4">
         <v>1</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -17170,11 +17170,11 @@
       <c r="E66">
         <v>200</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>268</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -17193,11 +17193,11 @@
       <c r="E67">
         <v>200</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="2">
         <v>25764</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>14</v>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -17216,11 +17216,11 @@
       <c r="E68">
         <v>200</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="4">
         <v>2</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -17239,11 +17239,11 @@
       <c r="E69">
         <v>200</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="2">
         <v>22498</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>14</v>
+      <c r="G69" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -17262,11 +17262,11 @@
       <c r="E70">
         <v>200</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="4">
         <v>63</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -17285,11 +17285,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="4">
         <v>236</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17308,11 +17308,11 @@
       <c r="E72">
         <v>200</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="4">
         <v>4</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -17354,11 +17354,11 @@
       <c r="E74">
         <v>200</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>228</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -17377,11 +17377,11 @@
       <c r="E75">
         <v>200</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="4">
         <v>200</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="G75" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -17400,11 +17400,11 @@
       <c r="E76">
         <v>200</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="2">
         <v>43096</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>14</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -17469,11 +17469,11 @@
       <c r="E79">
         <v>200</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="2">
         <v>1313</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>14</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17492,11 +17492,11 @@
       <c r="E80">
         <v>200</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="4">
         <v>1</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -17538,11 +17538,11 @@
       <c r="E82">
         <v>1152</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="4">
         <v>528</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="G82" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -17561,11 +17561,11 @@
       <c r="E83">
         <v>1152</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="4">
         <v>71</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -17607,11 +17607,11 @@
       <c r="E85">
         <v>1152</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="4">
         <v>2736</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -17630,11 +17630,11 @@
       <c r="E86">
         <v>576</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>5376</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>14</v>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -17653,11 +17653,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="4">
         <v>213</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17676,11 +17676,11 @@
       <c r="E88">
         <v>576</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="2">
         <v>3548</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>14</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17699,11 +17699,11 @@
       <c r="E89">
         <v>576</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="4">
         <v>111</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>10</v>
+      <c r="G89" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -17722,11 +17722,11 @@
       <c r="E90">
         <v>576</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="4">
         <v>532</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="G90" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -17745,11 +17745,11 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="4">
         <v>2763</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="G91" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -17768,11 +17768,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="4">
         <v>863</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="G92" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -17791,11 +17791,11 @@
       <c r="E93">
         <v>576</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="2">
         <v>12790</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>14</v>
+      <c r="G93" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -17814,11 +17814,11 @@
       <c r="E94">
         <v>576</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="4">
         <v>2</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="G94" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -17860,11 +17860,11 @@
       <c r="E96">
         <v>144</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="2">
         <v>171780</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>14</v>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -17906,11 +17906,11 @@
       <c r="E98">
         <v>144</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="4">
         <v>2</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -17952,11 +17952,11 @@
       <c r="E100">
         <v>144</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="2">
         <v>15720</v>
       </c>
-      <c r="G100" s="5" t="s">
-        <v>14</v>
+      <c r="G100" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -17975,11 +17975,11 @@
       <c r="E101">
         <v>144</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="4">
         <v>2</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>10</v>
+      <c r="G101" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -17998,11 +17998,11 @@
       <c r="E102">
         <v>144</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="2">
         <v>17342</v>
       </c>
-      <c r="G102" s="5" t="s">
-        <v>14</v>
+      <c r="G102" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -18021,11 +18021,11 @@
       <c r="E103">
         <v>144</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="2">
         <v>15828</v>
       </c>
-      <c r="G103" s="5" t="s">
-        <v>14</v>
+      <c r="G103" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -18044,11 +18044,11 @@
       <c r="E104">
         <v>144</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>5802</v>
       </c>
-      <c r="G104" s="5" t="s">
-        <v>14</v>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -18067,11 +18067,11 @@
       <c r="E105">
         <v>144</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="2">
         <v>6610</v>
       </c>
-      <c r="G105" s="5" t="s">
-        <v>14</v>
+      <c r="G105" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -18090,11 +18090,11 @@
       <c r="E106">
         <v>144</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="4">
         <v>299</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="G106" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -18113,11 +18113,11 @@
       <c r="E107">
         <v>144</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="2">
         <v>17670</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>14</v>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -18136,11 +18136,11 @@
       <c r="E108">
         <v>144</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="2">
         <v>3966</v>
       </c>
-      <c r="G108" s="5" t="s">
-        <v>14</v>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -18159,11 +18159,11 @@
       <c r="E109">
         <v>192</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="2">
         <v>13629</v>
       </c>
-      <c r="G109" s="5" t="s">
-        <v>14</v>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -18182,11 +18182,11 @@
       <c r="E110">
         <v>192</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="2">
         <v>1359</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>14</v>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -18205,11 +18205,11 @@
       <c r="E111">
         <v>192</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="2">
         <v>18571</v>
       </c>
-      <c r="G111" s="5" t="s">
-        <v>14</v>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -18228,11 +18228,11 @@
       <c r="E112">
         <v>192</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="2">
         <v>4391</v>
       </c>
-      <c r="G112" s="5" t="s">
-        <v>14</v>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -18251,11 +18251,11 @@
       <c r="E113">
         <v>192</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="2">
         <v>24801</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>14</v>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -18274,11 +18274,11 @@
       <c r="E114">
         <v>192</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="2">
         <v>6541</v>
       </c>
-      <c r="G114" s="5" t="s">
-        <v>14</v>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -18297,11 +18297,11 @@
       <c r="E115">
         <v>192</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="2">
         <v>15354</v>
       </c>
-      <c r="G115" s="5" t="s">
-        <v>14</v>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -18320,11 +18320,11 @@
       <c r="E116">
         <v>192</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="4">
         <v>46</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="G116" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -18343,11 +18343,11 @@
       <c r="E117">
         <v>192</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="4">
         <v>63</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="G117" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -18366,11 +18366,11 @@
       <c r="E118">
         <v>192</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="2">
         <v>2867</v>
       </c>
-      <c r="G118" s="5" t="s">
-        <v>14</v>
+      <c r="G118" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -18412,11 +18412,11 @@
       <c r="E120">
         <v>192</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="4">
         <v>212</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="G120" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -18435,11 +18435,11 @@
       <c r="E121">
         <v>192</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="4">
         <v>137</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -18458,11 +18458,11 @@
       <c r="E122">
         <v>192</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="2">
         <v>1954</v>
       </c>
-      <c r="G122" s="5" t="s">
-        <v>14</v>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -18481,11 +18481,11 @@
       <c r="E123">
         <v>192</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="2">
         <v>4010</v>
       </c>
-      <c r="G123" s="5" t="s">
-        <v>14</v>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -18504,11 +18504,11 @@
       <c r="E124">
         <v>192</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="2">
         <v>1674</v>
       </c>
-      <c r="G124" s="5" t="s">
-        <v>14</v>
+      <c r="G124" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -18527,11 +18527,11 @@
       <c r="E125">
         <v>192</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="2">
         <v>6331</v>
       </c>
-      <c r="G125" s="5" t="s">
-        <v>14</v>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -18550,11 +18550,11 @@
       <c r="E126">
         <v>192</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="2">
         <v>1714</v>
       </c>
-      <c r="G126" s="5" t="s">
-        <v>14</v>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -18573,11 +18573,11 @@
       <c r="E127">
         <v>192</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="2">
         <v>10781</v>
       </c>
-      <c r="G127" s="5" t="s">
-        <v>14</v>
+      <c r="G127" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -18596,11 +18596,11 @@
       <c r="E128">
         <v>192</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="2">
         <v>8737</v>
       </c>
-      <c r="G128" s="5" t="s">
-        <v>14</v>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -18619,11 +18619,11 @@
       <c r="E129">
         <v>192</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>3244</v>
       </c>
-      <c r="G129" s="5" t="s">
-        <v>14</v>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -18642,11 +18642,11 @@
       <c r="E130">
         <v>192</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>43731</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>14</v>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -18665,11 +18665,11 @@
       <c r="E131">
         <v>192</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="4">
         <v>287</v>
       </c>
-      <c r="G131" s="3" t="s">
-        <v>10</v>
+      <c r="G131" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -18688,11 +18688,11 @@
       <c r="E132">
         <v>192</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="2">
         <v>8436</v>
       </c>
-      <c r="G132" s="5" t="s">
-        <v>14</v>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -18711,11 +18711,11 @@
       <c r="E133">
         <v>192</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="4">
         <v>185</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="G133" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -18734,11 +18734,11 @@
       <c r="E134">
         <v>192</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>6726</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>14</v>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -18757,11 +18757,11 @@
       <c r="E135">
         <v>192</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="2">
         <v>12048</v>
       </c>
-      <c r="G135" s="5" t="s">
-        <v>14</v>
+      <c r="G135" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -18780,11 +18780,11 @@
       <c r="E136">
         <v>192</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="2">
         <v>2895</v>
       </c>
-      <c r="G136" s="5" t="s">
-        <v>14</v>
+      <c r="G136" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -18803,11 +18803,11 @@
       <c r="E137">
         <v>192</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="4">
         <v>108</v>
       </c>
-      <c r="G137" s="3" t="s">
-        <v>10</v>
+      <c r="G137" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -18826,11 +18826,11 @@
       <c r="E138">
         <v>192</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="4">
         <v>99</v>
       </c>
-      <c r="G138" s="3" t="s">
-        <v>10</v>
+      <c r="G138" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -18849,11 +18849,11 @@
       <c r="E139">
         <v>192</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="4">
         <v>125</v>
       </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="G139" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -18872,11 +18872,11 @@
       <c r="E140">
         <v>192</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="4">
         <v>17</v>
       </c>
-      <c r="G140" s="3" t="s">
-        <v>10</v>
+      <c r="G140" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -18895,11 +18895,11 @@
       <c r="E141">
         <v>192</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="4">
         <v>114</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -18918,11 +18918,11 @@
       <c r="E142">
         <v>192</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="4">
         <v>122</v>
       </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="G142" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -18941,11 +18941,11 @@
       <c r="E143">
         <v>192</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="4">
         <v>42</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="G143" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -18964,11 +18964,11 @@
       <c r="E144">
         <v>192</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="4">
         <v>66</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -19076,11 +19076,11 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>10117</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -19099,11 +19099,11 @@
       <c r="E5">
         <v>144</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>24475</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -19122,11 +19122,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>7099</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -19168,11 +19168,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>17217</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -19191,11 +19191,11 @@
       <c r="E9">
         <v>72</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>7876</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -19214,11 +19214,11 @@
       <c r="E10">
         <v>120</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>11163</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -19237,11 +19237,11 @@
       <c r="E11">
         <v>30</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>12365</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -19260,11 +19260,11 @@
       <c r="E12">
         <v>36</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>3135</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -19306,11 +19306,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>2047</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -19329,11 +19329,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>84</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -19352,11 +19352,11 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>24</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -19421,11 +19421,11 @@
       <c r="E19">
         <v>20</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>3775</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -19444,11 +19444,11 @@
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>5038</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>14</v>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -19467,11 +19467,11 @@
       <c r="E21">
         <v>40</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>35251</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -19490,11 +19490,11 @@
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>14823</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -19513,11 +19513,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="4">
         <v>4</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -19536,11 +19536,11 @@
       <c r="E24">
         <v>60</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>2769</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>14</v>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -19559,11 +19559,11 @@
       <c r="E25">
         <v>36</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>12681</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -19582,11 +19582,11 @@
       <c r="E26">
         <v>36</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>5180</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -19628,11 +19628,11 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>2762</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
+      <c r="G28" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -19651,11 +19651,11 @@
       <c r="E29">
         <v>36</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>4798</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -19674,11 +19674,11 @@
       <c r="E30">
         <v>48</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>5814</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -19697,11 +19697,11 @@
       <c r="E31">
         <v>144</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>92609</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -19720,11 +19720,11 @@
       <c r="E32">
         <v>120</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="4">
         <v>2</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="G32" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -19743,11 +19743,11 @@
       <c r="E33">
         <v>120</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="4">
         <v>17</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -19766,11 +19766,11 @@
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>12254</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>14</v>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -19812,11 +19812,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>8821</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>14</v>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -19858,11 +19858,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>83915</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>14</v>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -19881,11 +19881,11 @@
       <c r="E39">
         <v>120</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>15138</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>14</v>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -19904,11 +19904,11 @@
       <c r="E40">
         <v>120</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="4">
         <v>1</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -19950,11 +19950,11 @@
       <c r="E42">
         <v>144</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>10317</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>14</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -19973,11 +19973,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="2">
         <v>8038</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>14</v>
+      <c r="G43" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -19996,11 +19996,11 @@
       <c r="E44">
         <v>144</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="2">
         <v>8779</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>14</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -20019,11 +20019,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>9157</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>14</v>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -20042,11 +20042,11 @@
       <c r="E46">
         <v>144</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>6335</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -20065,11 +20065,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="4">
         <v>7</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -20088,11 +20088,11 @@
       <c r="E48">
         <v>144</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="2">
         <v>7831</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>14</v>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -20111,11 +20111,11 @@
       <c r="E49">
         <v>144</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>13343</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>14</v>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -20134,11 +20134,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="4">
         <v>1</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20180,11 +20180,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="4">
         <v>48</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -20203,11 +20203,11 @@
       <c r="E53">
         <v>144</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>5454</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>14</v>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -20272,11 +20272,11 @@
       <c r="E56">
         <v>144</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="4">
         <v>40</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -20341,11 +20341,11 @@
       <c r="E59">
         <v>144</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>3723</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>14</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -20364,11 +20364,11 @@
       <c r="E60">
         <v>144</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>2968</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>14</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -20387,11 +20387,11 @@
       <c r="E61">
         <v>96</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>2482</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>14</v>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -20433,11 +20433,11 @@
       <c r="E63">
         <v>120</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="2">
         <v>803</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>14</v>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -20479,11 +20479,11 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="4">
         <v>1</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -20502,11 +20502,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>413</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>14</v>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -20525,11 +20525,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="2">
         <v>366</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>14</v>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="2">
         <v>81</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>14</v>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20571,11 +20571,11 @@
       <c r="E69">
         <v>12</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="2">
         <v>660</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>14</v>
+      <c r="G69" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -20594,11 +20594,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="2">
         <v>102</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>14</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -20663,11 +20663,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="2">
         <v>5451</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>14</v>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -20686,11 +20686,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>2</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -20709,11 +20709,11 @@
       <c r="E75">
         <v>240</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="4">
         <v>12</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="G75" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -20732,11 +20732,11 @@
       <c r="E76">
         <v>180</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="4">
         <v>4</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -20755,11 +20755,11 @@
       <c r="E77">
         <v>144</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="2">
         <v>18903</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>14</v>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -20778,11 +20778,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="4">
         <v>2</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20801,11 +20801,11 @@
       <c r="E79">
         <v>144</v>
       </c>
-      <c r="F79" s="2">
-        <v>10</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>10</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -20893,11 +20893,11 @@
       <c r="E83">
         <v>144</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="2">
         <v>7450</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>14</v>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -20916,11 +20916,11 @@
       <c r="E84">
         <v>144</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="2">
         <v>43222</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>14</v>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -20962,11 +20962,11 @@
       <c r="E86">
         <v>144</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>21493</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>14</v>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -21008,11 +21008,11 @@
       <c r="E88">
         <v>144</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="2">
         <v>8070</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>14</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -21031,11 +21031,11 @@
       <c r="E89">
         <v>144</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="2">
         <v>6105</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>14</v>
+      <c r="G89" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -21054,11 +21054,11 @@
       <c r="E90">
         <v>144</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="2">
         <v>7492</v>
       </c>
-      <c r="G90" s="5" t="s">
-        <v>14</v>
+      <c r="G90" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -21077,11 +21077,11 @@
       <c r="E91">
         <v>144</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="2">
         <v>7743</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>14</v>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -21100,11 +21100,11 @@
       <c r="E92">
         <v>144</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="4">
         <v>4</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="G92" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -21123,11 +21123,11 @@
       <c r="E93">
         <v>144</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="2">
         <v>11800</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>14</v>
+      <c r="G93" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -21192,11 +21192,11 @@
       <c r="E96">
         <v>144</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="2">
         <v>29673</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>14</v>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -21258,11 +21258,11 @@
       <c r="E2">
         <v>72</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>110554</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21281,11 +21281,11 @@
       <c r="E3">
         <v>72</v>
       </c>
-      <c r="F3" s="4">
-        <v>190689</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="F3" s="2">
+        <v>190894</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21304,11 +21304,11 @@
       <c r="E4">
         <v>72</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>63969</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21327,11 +21327,11 @@
       <c r="E5">
         <v>72</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>24243</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -21393,11 +21393,11 @@
       <c r="E2">
         <v>12</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>1147</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21416,11 +21416,11 @@
       <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>1305</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21439,11 +21439,11 @@
       <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>958</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21462,11 +21462,11 @@
       <c r="E5">
         <v>12</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>671</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -21485,11 +21485,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>555</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -21508,11 +21508,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>309</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -21531,11 +21531,11 @@
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>645</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -21554,11 +21554,11 @@
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>468</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -21577,11 +21577,11 @@
       <c r="E10">
         <v>48</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>2024</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -21600,11 +21600,11 @@
       <c r="E11">
         <v>48</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>2095</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -21623,11 +21623,11 @@
       <c r="E12">
         <v>48</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>2744</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -21646,11 +21646,11 @@
       <c r="E13">
         <v>48</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>1616</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -21669,11 +21669,11 @@
       <c r="E14">
         <v>24</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>330</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -21692,11 +21692,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>535</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -21715,11 +21715,11 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>1074</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -21738,11 +21738,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>1161</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -21761,11 +21761,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>171</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -21784,11 +21784,11 @@
       <c r="E19">
         <v>6</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>61</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -21807,11 +21807,11 @@
       <c r="E20">
         <v>24</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>1150</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>14</v>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -21830,11 +21830,11 @@
       <c r="E21">
         <v>24</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>1296</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -21853,11 +21853,11 @@
       <c r="E22">
         <v>24</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>1061</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -21876,11 +21876,11 @@
       <c r="E23">
         <v>24</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>997</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>14</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -21899,11 +21899,11 @@
       <c r="E24">
         <v>24</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>474</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>14</v>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -21922,11 +21922,11 @@
       <c r="E25">
         <v>24</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>344</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -21945,11 +21945,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>189</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -21968,11 +21968,11 @@
       <c r="E27">
         <v>24</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>187</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>14</v>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -21991,11 +21991,11 @@
       <c r="E28">
         <v>12</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>496</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
+      <c r="G28" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -22014,11 +22014,11 @@
       <c r="E29">
         <v>12</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>478</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -22037,11 +22037,11 @@
       <c r="E30">
         <v>12</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>363</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -22060,11 +22060,11 @@
       <c r="E31">
         <v>12</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>255</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -22083,11 +22083,11 @@
       <c r="E32">
         <v>48</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="4">
         <v>2</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="G32" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -22149,11 +22149,11 @@
       <c r="E2">
         <v>288</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>8347</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22172,11 +22172,11 @@
       <c r="E3">
         <v>384</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>20515</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22195,11 +22195,11 @@
       <c r="E4">
         <v>384</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>19753</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22218,11 +22218,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>48313</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -22241,11 +22241,11 @@
       <c r="E6">
         <v>384</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>81337</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22264,11 +22264,11 @@
       <c r="E7">
         <v>384</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>47692</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -22310,11 +22310,11 @@
       <c r="E9">
         <v>144</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>23132</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -22333,11 +22333,11 @@
       <c r="E10">
         <v>36</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>12</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -22379,11 +22379,11 @@
       <c r="E12">
         <v>192</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>14791</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -22402,11 +22402,11 @@
       <c r="E13">
         <v>576</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>74919</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -22425,11 +22425,11 @@
       <c r="E14">
         <v>12</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>87772</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22448,11 +22448,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>34722</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -22471,11 +22471,11 @@
       <c r="E16">
         <v>48</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>22312</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -22517,11 +22517,11 @@
       <c r="E18">
         <v>144</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>12635</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -22540,11 +22540,11 @@
       <c r="E19">
         <v>144</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>2479</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -22563,11 +22563,11 @@
       <c r="E20">
         <v>144</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>16339</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>14</v>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -22609,11 +22609,11 @@
       <c r="E22">
         <v>144</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>13658</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -22721,11 +22721,11 @@
       <c r="E4">
         <v>1000</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>917</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22744,11 +22744,11 @@
       <c r="E5">
         <v>500</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>4141</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -22767,11 +22767,11 @@
       <c r="E6">
         <v>500</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>139</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22790,11 +22790,11 @@
       <c r="E7">
         <v>500</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>3528</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -22836,11 +22836,11 @@
       <c r="E9">
         <v>200</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>8887</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -22905,11 +22905,11 @@
       <c r="E12">
         <v>500</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>10957</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -22928,11 +22928,11 @@
       <c r="E13">
         <v>500</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>5</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -22951,11 +22951,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="2">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22974,11 +22974,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>8</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -22997,11 +22997,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>2</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -23020,11 +23020,11 @@
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>2078</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>27745</v>
+        <v>27529</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>190894</v>
+        <v>190869</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1147</v>
+        <v>1201</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1305</v>
+        <v>1375</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21440,7 +21440,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>958</v>
+        <v>1018</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21486,7 +21486,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>555</v>
+        <v>603</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -21532,7 +21532,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>645</v>
+        <v>805</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -21555,7 +21555,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="2">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -21762,7 +21762,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="2">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>115614</v>
+        <v>125664</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8184,7 +8184,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="4">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>17</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>33042</v>
+        <v>32942</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>61322</v>
+        <v>64522</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>39113</v>
+        <v>39013</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>27529</v>
+        <v>31369</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>68721</v>
+        <v>67724</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>58601</v>
+        <v>57676</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -16044,7 +16044,7 @@
         <v>192</v>
       </c>
       <c r="F17" s="2">
-        <v>13633</v>
+        <v>13585</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="2">
-        <v>14160</v>
+        <v>14112</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>7103</v>
+        <v>7055</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2">
-        <v>14160</v>
+        <v>14112</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -17355,7 +17355,7 @@
         <v>200</v>
       </c>
       <c r="F74" s="4">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>17</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>92609</v>
+        <v>98081</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7129,7 +7129,7 @@
         <v>48</v>
       </c>
       <c r="F6" s="2">
-        <v>12182</v>
+        <v>12179</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -16826,7 +16826,7 @@
         <v>192</v>
       </c>
       <c r="F51" s="2">
-        <v>9001</v>
+        <v>8998</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -17102,7 +17102,7 @@
         <v>576</v>
       </c>
       <c r="F63" s="2">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -9012,7 +9012,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="2">
-        <v>3517</v>
+        <v>3467</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>1262</v>
+        <v>1502</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="4">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>17</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>5376</v>
+        <v>4976</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17653,11 +17653,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="4">
-        <v>213</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>17</v>
+      <c r="F87" s="6">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>20515</v>
+        <v>19747</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>102278</v>
+        <v>106478</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="4">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>17</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>4644</v>
+        <v>4594</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>2732</v>
+        <v>2682</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>3422</v>
+        <v>3322</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>11356</v>
+        <v>11256</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>2484</v>
+        <v>2434</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="2">
-        <v>45718</v>
+        <v>48918</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>31369</v>
+        <v>31129</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>14823</v>
+        <v>15438</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>98081</v>
+        <v>106145</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>8779</v>
+        <v>9043</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20342,7 +20342,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="2">
-        <v>3723</v>
+        <v>4299</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -20870,11 +20870,11 @@
       <c r="E82">
         <v>144</v>
       </c>
-      <c r="F82" s="6">
-        <v>0</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>20</v>
+      <c r="F82" s="4">
+        <v>72</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1201</v>
+        <v>1237</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1375</v>
+        <v>1411</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21532,7 +21532,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -21555,7 +21555,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -21601,7 +21601,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="2">
-        <v>2095</v>
+        <v>2257</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -21624,7 +21624,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="2">
-        <v>2744</v>
+        <v>2944</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -21647,7 +21647,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="2">
-        <v>1616</v>
+        <v>1832</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -21716,7 +21716,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="2">
-        <v>1074</v>
+        <v>1170</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -21762,7 +21762,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -21854,7 +21854,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="2">
-        <v>1061</v>
+        <v>1253</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -21877,7 +21877,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="2">
-        <v>997</v>
+        <v>1093</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -21992,7 +21992,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="2">
-        <v>496</v>
+        <v>567</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -22015,7 +22015,7 @@
         <v>12</v>
       </c>
       <c r="F29" s="2">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -52,18 +52,21 @@
     <t>FORRO N VINIFAN OFICIO CRISTAL 26</t>
   </si>
   <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>02211</t>
+  </si>
+  <si>
+    <t>7754807020022</t>
+  </si>
+  <si>
+    <t>FORRO N VINIFAN A4 CRISTAL 26</t>
+  </si>
+  <si>
     <t>✓ OK</t>
   </si>
   <si>
-    <t>02211</t>
-  </si>
-  <si>
-    <t>7754807020022</t>
-  </si>
-  <si>
-    <t>FORRO N VINIFAN A4 CRISTAL 26</t>
-  </si>
-  <si>
     <t>02204</t>
   </si>
   <si>
@@ -71,9 +74,6 @@
   </si>
   <si>
     <t>FORRO N VINIFANCITO CRISTAL 25</t>
-  </si>
-  <si>
-    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>02212</t>
@@ -6228,12 +6228,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FF065F46"/>
       <sz val="12"/>
     </font>
     <font>
@@ -6256,12 +6256,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6717,11 +6717,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="2">
-        <v>106478</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="F3" s="4">
+        <v>106378</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6729,22 +6729,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>266</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6755,7 +6755,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -6786,11 +6786,11 @@
       <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>13</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6809,11 +6809,11 @@
       <c r="E7">
         <v>25</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>29372</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6832,11 +6832,11 @@
       <c r="E8">
         <v>48</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>17942</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6855,11 +6855,11 @@
       <c r="E9">
         <v>48</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>48292</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6878,11 +6878,11 @@
       <c r="E10">
         <v>18</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>17008</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6901,11 +6901,11 @@
       <c r="E11">
         <v>36</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>17935</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6924,11 +6924,11 @@
       <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" s="4">
-        <v>14</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>17</v>
+      <c r="F12" s="2">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6947,11 +6947,11 @@
       <c r="E13">
         <v>50</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>89799</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6970,11 +6970,11 @@
       <c r="E14">
         <v>100</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>87460</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7036,11 +7036,11 @@
       <c r="E2">
         <v>96</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>10734</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7059,11 +7059,11 @@
       <c r="E3">
         <v>96</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>12212</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7082,11 +7082,11 @@
       <c r="E4">
         <v>96</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>11268</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7105,11 +7105,11 @@
       <c r="E5">
         <v>96</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>3275</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7128,11 +7128,11 @@
       <c r="E6">
         <v>48</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>12179</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7151,11 +7151,11 @@
       <c r="E7">
         <v>48</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>1453</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7174,11 +7174,11 @@
       <c r="E8">
         <v>48</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>9792</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7243,11 +7243,11 @@
       <c r="E11">
         <v>96</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>17</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7289,11 +7289,11 @@
       <c r="E13">
         <v>96</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>1393</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7312,11 +7312,11 @@
       <c r="E14">
         <v>400</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>471</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>17</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7335,11 +7335,11 @@
       <c r="E15">
         <v>100</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>14197</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7358,11 +7358,11 @@
       <c r="E16">
         <v>72</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>1099</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7381,11 +7381,11 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>12890</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7404,11 +7404,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>1</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>17</v>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7427,11 +7427,11 @@
       <c r="E19">
         <v>48</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>10891</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7450,11 +7450,11 @@
       <c r="E20">
         <v>72</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>8</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>17</v>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7473,11 +7473,11 @@
       <c r="E21">
         <v>500</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>37382</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -7496,11 +7496,11 @@
       <c r="E22">
         <v>500</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>8783</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -7519,11 +7519,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>6</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>17</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -7588,11 +7588,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="4">
         <v>2098</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -7634,11 +7634,11 @@
       <c r="E28">
         <v>100</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="4">
         <v>21419</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -7657,11 +7657,11 @@
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="4">
         <v>2465</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -7680,11 +7680,11 @@
       <c r="E30">
         <v>30</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>1</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>17</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -7703,11 +7703,11 @@
       <c r="E31">
         <v>100</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="4">
         <v>1151</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7769,11 +7769,11 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>17</v>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7792,11 +7792,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>22869</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7838,11 +7838,11 @@
       <c r="E5">
         <v>50</v>
       </c>
-      <c r="F5" s="2">
-        <v>125664</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>125634</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7861,11 +7861,11 @@
       <c r="E6">
         <v>50</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>26</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7884,11 +7884,11 @@
       <c r="E7">
         <v>50</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>24</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>17</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7930,11 +7930,11 @@
       <c r="E9">
         <v>50</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>17</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7953,11 +7953,11 @@
       <c r="E10">
         <v>50</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>1131</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7976,11 +7976,11 @@
       <c r="E11">
         <v>50</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>19</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>17</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7999,11 +7999,11 @@
       <c r="E12">
         <v>50</v>
       </c>
-      <c r="F12" s="4">
-        <v>14</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>17</v>
+      <c r="F12" s="2">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>153</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>17</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>4594</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8091,11 +8091,11 @@
       <c r="E16">
         <v>50</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>1</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>17</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8114,11 +8114,11 @@
       <c r="E17">
         <v>50</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>17</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>17</v>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8137,11 +8137,11 @@
       <c r="E18">
         <v>50</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>2682</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8160,11 +8160,11 @@
       <c r="E19">
         <v>50</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>162</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>17</v>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8183,11 +8183,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>110</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>17</v>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>11</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>17</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8229,11 +8229,11 @@
       <c r="E22">
         <v>50</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>18</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>17</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -8275,11 +8275,11 @@
       <c r="E24">
         <v>50</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="4">
         <v>32942</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -8298,11 +8298,11 @@
       <c r="E25">
         <v>50</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="4">
         <v>3322</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -8321,11 +8321,11 @@
       <c r="E26">
         <v>50</v>
       </c>
-      <c r="F26" s="2">
-        <v>4950</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="F26" s="4">
+        <v>4944</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -8344,11 +8344,11 @@
       <c r="E27">
         <v>50</v>
       </c>
-      <c r="F27" s="4">
-        <v>7</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>17</v>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -8367,11 +8367,11 @@
       <c r="E28">
         <v>50</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="4">
         <v>11256</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -8390,11 +8390,11 @@
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="4">
         <v>4401</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -8413,11 +8413,11 @@
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>2347</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -8436,11 +8436,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="4">
-        <v>105</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>17</v>
+      <c r="F31" s="2">
+        <v>99</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -8459,11 +8459,11 @@
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="4">
         <v>2434</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="G32" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -8482,11 +8482,11 @@
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="2">
-        <v>4514</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="F33" s="4">
+        <v>4508</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -8505,11 +8505,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="4">
-        <v>6</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>17</v>
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -8528,11 +8528,11 @@
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="4">
         <v>8888</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -8551,11 +8551,11 @@
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="2">
-        <v>10676</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>10376</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,11 +8597,11 @@
       <c r="E38">
         <v>50</v>
       </c>
-      <c r="F38" s="4">
-        <v>50</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>17</v>
+      <c r="F38" s="2">
+        <v>44</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -8643,11 +8643,11 @@
       <c r="E40">
         <v>50</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="4">
         <v>4594</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -8666,11 +8666,11 @@
       <c r="E41">
         <v>50</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>1</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>17</v>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -8689,11 +8689,11 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>9</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>17</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -8735,11 +8735,11 @@
       <c r="E44">
         <v>100</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="4">
         <v>1349</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -8758,11 +8758,11 @@
       <c r="E45">
         <v>100</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="4">
         <v>1726</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -8781,11 +8781,11 @@
       <c r="E46">
         <v>100</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="4">
         <v>783</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,11 +8804,11 @@
       <c r="E47">
         <v>100</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="4">
         <v>711</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,11 +8850,11 @@
       <c r="E49">
         <v>100</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>267</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>17</v>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -8873,11 +8873,11 @@
       <c r="E50">
         <v>100</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="4">
         <v>1673</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,11 +8896,11 @@
       <c r="E51">
         <v>100</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>92</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>17</v>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -8919,11 +8919,11 @@
       <c r="E52">
         <v>100</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>5</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>17</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,11 +8942,11 @@
       <c r="E53">
         <v>100</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>101</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>17</v>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,11 +8965,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="2">
         <v>251</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>17</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -8988,11 +8988,11 @@
       <c r="E55">
         <v>100</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="4">
         <v>990</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -9011,11 +9011,11 @@
       <c r="E56">
         <v>100</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="4">
         <v>3467</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -9034,11 +9034,11 @@
       <c r="E57">
         <v>100</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="4">
         <v>8360</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,11 +9057,11 @@
       <c r="E58">
         <v>100</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="4">
         <v>4186</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -9080,11 +9080,11 @@
       <c r="E59">
         <v>100</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="4">
         <v>16008</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -9103,11 +9103,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>45</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>17</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -9126,11 +9126,11 @@
       <c r="E61">
         <v>100</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="4">
         <v>1260</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -9149,11 +9149,11 @@
       <c r="E62">
         <v>100</v>
       </c>
-      <c r="F62" s="2">
-        <v>1181</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>781</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -9172,11 +9172,11 @@
       <c r="E63">
         <v>100</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="4">
         <v>1254</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="G63" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -9195,11 +9195,11 @@
       <c r="E64">
         <v>100</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>153</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>17</v>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,11 +9241,11 @@
       <c r="E66">
         <v>50</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>84</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>17</v>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -9264,11 +9264,11 @@
       <c r="E67">
         <v>100</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="2">
         <v>67</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>17</v>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -9287,11 +9287,11 @@
       <c r="E68">
         <v>100</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="4">
         <v>64522</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,11 +9310,11 @@
       <c r="E69">
         <v>100</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="4">
         <v>27658</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="G69" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -9333,11 +9333,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="2">
         <v>67</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>17</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,11 +9379,11 @@
       <c r="E72">
         <v>100</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="4">
         <v>24247</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -9402,11 +9402,11 @@
       <c r="E73">
         <v>100</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="4">
         <v>14938</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,11 +9425,11 @@
       <c r="E74">
         <v>100</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>48918</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,11 +9448,11 @@
       <c r="E75">
         <v>100</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="4">
         <v>17370</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="G75" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,11 +9471,11 @@
       <c r="E76">
         <v>100</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="2">
         <v>87</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>17</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,11 +9494,11 @@
       <c r="E77">
         <v>100</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="4">
         <v>39013</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,11 +9517,11 @@
       <c r="E78">
         <v>100</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="4">
         <v>40009</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,11 +9540,11 @@
       <c r="E79">
         <v>100</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="4">
         <v>36136</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="G79" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,11 +9563,11 @@
       <c r="E80">
         <v>100</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="4">
         <v>15120</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,11 +9586,11 @@
       <c r="E81">
         <v>100</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="4">
         <v>9133</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>10</v>
+      <c r="G81" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,11 +9609,11 @@
       <c r="E82">
         <v>100</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="2">
         <v>5</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>17</v>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,11 +9632,11 @@
       <c r="E83">
         <v>100</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="4">
         <v>9991</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,11 +9655,11 @@
       <c r="E84">
         <v>100</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="4">
         <v>1167</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="G84" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,11 +9678,11 @@
       <c r="E85">
         <v>100</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="2">
         <v>1</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>17</v>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,11 +9701,11 @@
       <c r="E86">
         <v>100</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="4">
         <v>36118</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,11 +9724,11 @@
       <c r="E87">
         <v>100</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="4">
         <v>8384</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,11 +9747,11 @@
       <c r="E88">
         <v>100</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="4">
         <v>5865</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,11 +9770,11 @@
       <c r="E89">
         <v>100</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="4">
         <v>12129</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>10</v>
+      <c r="G89" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,11 +9793,11 @@
       <c r="E90">
         <v>100</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="4">
         <v>7597</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="G90" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -9816,11 +9816,11 @@
       <c r="E91">
         <v>100</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="4">
         <v>7636</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="G91" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -9839,11 +9839,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="2">
         <v>445</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>17</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -9862,11 +9862,11 @@
       <c r="E93">
         <v>100</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="4">
         <v>10229</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="G93" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -9885,11 +9885,11 @@
       <c r="E94">
         <v>100</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="4">
         <v>2682</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="G94" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -9908,11 +9908,11 @@
       <c r="E95">
         <v>100</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="4">
         <v>4316</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -9931,11 +9931,11 @@
       <c r="E96">
         <v>100</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="4">
         <v>14965</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -9954,11 +9954,11 @@
       <c r="E97">
         <v>120</v>
       </c>
-      <c r="F97" s="4">
+      <c r="F97" s="2">
         <v>2</v>
       </c>
-      <c r="G97" s="5" t="s">
-        <v>17</v>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -9977,11 +9977,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="2">
         <v>1</v>
       </c>
-      <c r="G98" s="5" t="s">
-        <v>17</v>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -10000,11 +10000,11 @@
       <c r="E99">
         <v>120</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="2">
         <v>1</v>
       </c>
-      <c r="G99" s="5" t="s">
-        <v>17</v>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,11 +10069,11 @@
       <c r="E102">
         <v>120</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="2">
         <v>2</v>
       </c>
-      <c r="G102" s="5" t="s">
-        <v>17</v>
+      <c r="G102" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,11 +10092,11 @@
       <c r="E103">
         <v>120</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="2">
         <v>35</v>
       </c>
-      <c r="G103" s="5" t="s">
-        <v>17</v>
+      <c r="G103" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -10115,11 +10115,11 @@
       <c r="E104">
         <v>120</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="4">
         <v>5926</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="G104" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -10138,11 +10138,11 @@
       <c r="E105">
         <v>120</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="4">
         <v>5634</v>
       </c>
-      <c r="G105" s="3" t="s">
-        <v>10</v>
+      <c r="G105" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -10161,11 +10161,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="4">
         <v>5695</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="G106" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -10184,11 +10184,11 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="4">
         <v>4844</v>
       </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="G107" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -10207,11 +10207,11 @@
       <c r="E108">
         <v>120</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="4">
         <v>2898</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="G108" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -10230,11 +10230,11 @@
       <c r="E109">
         <v>120</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="4">
         <v>4797</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="G109" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -10253,11 +10253,11 @@
       <c r="E110">
         <v>120</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="4">
         <v>4618</v>
       </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="G110" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,11 +10276,11 @@
       <c r="E111">
         <v>120</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="2">
         <v>8</v>
       </c>
-      <c r="G111" s="5" t="s">
-        <v>17</v>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -10299,11 +10299,11 @@
       <c r="E112">
         <v>120</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="4">
         <v>2768</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="G112" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,11 +10322,11 @@
       <c r="E113">
         <v>120</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="4">
         <v>2860</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="G113" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,11 +10345,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="2">
         <v>47</v>
       </c>
-      <c r="G114" s="5" t="s">
-        <v>17</v>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -10437,11 +10437,11 @@
       <c r="E118">
         <v>24</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="4">
         <v>1714</v>
       </c>
-      <c r="G118" s="3" t="s">
-        <v>10</v>
+      <c r="G118" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -10460,11 +10460,11 @@
       <c r="E119">
         <v>24</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="4">
         <v>31129</v>
       </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="G119" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -10483,11 +10483,11 @@
       <c r="E120">
         <v>24</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="4">
         <v>24871</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="G120" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -10506,11 +10506,11 @@
       <c r="E121">
         <v>24</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="4">
         <v>4500</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -10529,11 +10529,11 @@
       <c r="E122">
         <v>24</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="4">
         <v>4042</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="G122" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -10552,11 +10552,11 @@
       <c r="E123">
         <v>24</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="4">
         <v>1219</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="G123" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -10575,11 +10575,11 @@
       <c r="E124">
         <v>24</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="4">
         <v>8495</v>
       </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="G124" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -10598,11 +10598,11 @@
       <c r="E125">
         <v>24</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="4">
         <v>803</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="G125" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -10644,11 +10644,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="4">
         <v>430</v>
       </c>
-      <c r="G127" s="3" t="s">
-        <v>10</v>
+      <c r="G127" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -10667,11 +10667,11 @@
       <c r="E128">
         <v>24</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="4">
         <v>5188</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="G128" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -10690,11 +10690,11 @@
       <c r="E129">
         <v>24</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="4">
         <v>7817</v>
       </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="G129" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -10713,11 +10713,11 @@
       <c r="E130">
         <v>24</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="4">
         <v>14625</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="G130" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -10736,11 +10736,11 @@
       <c r="E131">
         <v>24</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="4">
         <v>9201</v>
       </c>
-      <c r="G131" s="3" t="s">
-        <v>10</v>
+      <c r="G131" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -10759,11 +10759,11 @@
       <c r="E132">
         <v>24</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="4">
         <v>9570</v>
       </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="G132" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -10805,11 +10805,11 @@
       <c r="E134">
         <v>24</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="4">
         <v>4578</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="G134" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -10851,11 +10851,11 @@
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="4">
         <v>14103</v>
       </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="G136" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -10920,11 +10920,11 @@
       <c r="E139">
         <v>30</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="2">
         <v>18</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>17</v>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -10943,11 +10943,11 @@
       <c r="E140">
         <v>30</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="2">
         <v>27</v>
       </c>
-      <c r="G140" s="5" t="s">
-        <v>17</v>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -11058,11 +11058,11 @@
       <c r="E145">
         <v>24</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="4">
         <v>408</v>
       </c>
-      <c r="G145" s="3" t="s">
-        <v>10</v>
+      <c r="G145" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -11081,11 +11081,11 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="2">
         <v>5</v>
       </c>
-      <c r="G146" s="5" t="s">
-        <v>17</v>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -11104,11 +11104,11 @@
       <c r="E147">
         <v>24</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="2">
         <v>4</v>
       </c>
-      <c r="G147" s="5" t="s">
-        <v>17</v>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -11127,11 +11127,11 @@
       <c r="E148">
         <v>12</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="4">
         <v>1134</v>
       </c>
-      <c r="G148" s="3" t="s">
-        <v>10</v>
+      <c r="G148" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -11173,11 +11173,11 @@
       <c r="E150">
         <v>12</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="2">
         <v>2</v>
       </c>
-      <c r="G150" s="5" t="s">
-        <v>17</v>
+      <c r="G150" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -11196,11 +11196,11 @@
       <c r="E151">
         <v>12</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="4">
         <v>127</v>
       </c>
-      <c r="G151" s="3" t="s">
-        <v>10</v>
+      <c r="G151" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -11219,11 +11219,11 @@
       <c r="E152">
         <v>12</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="4">
         <v>291</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="G152" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -11242,11 +11242,11 @@
       <c r="E153">
         <v>12</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="2">
         <v>3</v>
       </c>
-      <c r="G153" s="5" t="s">
-        <v>17</v>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -11265,11 +11265,11 @@
       <c r="E154">
         <v>6</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="2">
         <v>1</v>
       </c>
-      <c r="G154" s="5" t="s">
-        <v>17</v>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -11288,11 +11288,11 @@
       <c r="E155">
         <v>6</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="4">
         <v>583</v>
       </c>
-      <c r="G155" s="3" t="s">
-        <v>10</v>
+      <c r="G155" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -11311,11 +11311,11 @@
       <c r="E156">
         <v>6</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="2">
         <v>4</v>
       </c>
-      <c r="G156" s="5" t="s">
-        <v>17</v>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -11334,11 +11334,11 @@
       <c r="E157">
         <v>6</v>
       </c>
-      <c r="F157" s="4">
+      <c r="F157" s="2">
         <v>1</v>
       </c>
-      <c r="G157" s="5" t="s">
-        <v>17</v>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -11357,11 +11357,11 @@
       <c r="E158">
         <v>24</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="2">
         <v>5</v>
       </c>
-      <c r="G158" s="5" t="s">
-        <v>17</v>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -11449,11 +11449,11 @@
       <c r="E162">
         <v>24</v>
       </c>
-      <c r="F162" s="4">
+      <c r="F162" s="2">
         <v>1</v>
       </c>
-      <c r="G162" s="5" t="s">
-        <v>17</v>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -11472,11 +11472,11 @@
       <c r="E163">
         <v>24</v>
       </c>
-      <c r="F163" s="4">
+      <c r="F163" s="2">
         <v>4</v>
       </c>
-      <c r="G163" s="5" t="s">
-        <v>17</v>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -11495,11 +11495,11 @@
       <c r="E164">
         <v>24</v>
       </c>
-      <c r="F164" s="4">
+      <c r="F164" s="2">
         <v>2</v>
       </c>
-      <c r="G164" s="5" t="s">
-        <v>17</v>
+      <c r="G164" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -11518,11 +11518,11 @@
       <c r="E165">
         <v>24</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="4">
         <v>258</v>
       </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="G165" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -11564,11 +11564,11 @@
       <c r="E167">
         <v>72</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="4">
         <v>13947</v>
       </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="G167" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -11587,11 +11587,11 @@
       <c r="E168">
         <v>72</v>
       </c>
-      <c r="F168" s="4">
+      <c r="F168" s="2">
         <v>1</v>
       </c>
-      <c r="G168" s="5" t="s">
-        <v>17</v>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -11702,11 +11702,11 @@
       <c r="E173">
         <v>72</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="4">
         <v>1099</v>
       </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="G173" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -11725,11 +11725,11 @@
       <c r="E174">
         <v>72</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="4">
         <v>1474</v>
       </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="G174" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -11771,11 +11771,11 @@
       <c r="E176">
         <v>48</v>
       </c>
-      <c r="F176" s="4">
+      <c r="F176" s="2">
         <v>2</v>
       </c>
-      <c r="G176" s="5" t="s">
-        <v>17</v>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -11794,11 +11794,11 @@
       <c r="E177">
         <v>48</v>
       </c>
-      <c r="F177" s="4">
+      <c r="F177" s="2">
         <v>58</v>
       </c>
-      <c r="G177" s="5" t="s">
-        <v>17</v>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -11817,11 +11817,11 @@
       <c r="E178">
         <v>48</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="4">
         <v>386</v>
       </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="G178" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -11840,11 +11840,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="4">
+      <c r="F179" s="2">
         <v>126</v>
       </c>
-      <c r="G179" s="5" t="s">
-        <v>17</v>
+      <c r="G179" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -11909,11 +11909,11 @@
       <c r="E182">
         <v>36</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="4">
         <v>836</v>
       </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="G182" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -11932,11 +11932,11 @@
       <c r="E183">
         <v>120</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="4">
         <v>4041</v>
       </c>
-      <c r="G183" s="3" t="s">
-        <v>10</v>
+      <c r="G183" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -11955,11 +11955,11 @@
       <c r="E184">
         <v>96</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="4">
         <v>5005</v>
       </c>
-      <c r="G184" s="3" t="s">
-        <v>10</v>
+      <c r="G184" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -11978,11 +11978,11 @@
       <c r="E185">
         <v>240</v>
       </c>
-      <c r="F185" s="4">
+      <c r="F185" s="2">
         <v>808</v>
       </c>
-      <c r="G185" s="5" t="s">
-        <v>17</v>
+      <c r="G185" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -12001,11 +12001,11 @@
       <c r="E186">
         <v>240</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="4">
         <v>5779</v>
       </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="G186" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -12024,11 +12024,11 @@
       <c r="E187">
         <v>240</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="4">
         <v>4796</v>
       </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="G187" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -12047,11 +12047,11 @@
       <c r="E188">
         <v>240</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="4">
         <v>3110</v>
       </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="G188" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -12070,11 +12070,11 @@
       <c r="E189">
         <v>72</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="4">
         <v>1991</v>
       </c>
-      <c r="G189" s="3" t="s">
-        <v>10</v>
+      <c r="G189" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -12093,11 +12093,11 @@
       <c r="E190">
         <v>64</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="4">
         <v>2409</v>
       </c>
-      <c r="G190" s="3" t="s">
-        <v>10</v>
+      <c r="G190" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -12162,11 +12162,11 @@
       <c r="E193">
         <v>40</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="4">
         <v>8371</v>
       </c>
-      <c r="G193" s="3" t="s">
-        <v>10</v>
+      <c r="G193" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -12185,11 +12185,11 @@
       <c r="E194">
         <v>48</v>
       </c>
-      <c r="F194" s="4">
+      <c r="F194" s="2">
         <v>11</v>
       </c>
-      <c r="G194" s="5" t="s">
-        <v>17</v>
+      <c r="G194" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -12208,11 +12208,11 @@
       <c r="E195">
         <v>48</v>
       </c>
-      <c r="F195" s="4">
+      <c r="F195" s="2">
         <v>8</v>
       </c>
-      <c r="G195" s="5" t="s">
-        <v>17</v>
+      <c r="G195" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -12277,11 +12277,11 @@
       <c r="E198">
         <v>10</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="4">
         <v>164</v>
       </c>
-      <c r="G198" s="3" t="s">
-        <v>10</v>
+      <c r="G198" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -12323,11 +12323,11 @@
       <c r="E200">
         <v>120</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="4">
         <v>1573</v>
       </c>
-      <c r="G200" s="3" t="s">
-        <v>10</v>
+      <c r="G200" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -12346,11 +12346,11 @@
       <c r="E201">
         <v>120</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="4">
         <v>1831</v>
       </c>
-      <c r="G201" s="3" t="s">
-        <v>10</v>
+      <c r="G201" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -12369,11 +12369,11 @@
       <c r="E202">
         <v>120</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="4">
         <v>2404</v>
       </c>
-      <c r="G202" s="3" t="s">
-        <v>10</v>
+      <c r="G202" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -12392,11 +12392,11 @@
       <c r="E203">
         <v>120</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="4">
         <v>2176</v>
       </c>
-      <c r="G203" s="3" t="s">
-        <v>10</v>
+      <c r="G203" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -12415,11 +12415,11 @@
       <c r="E204">
         <v>160</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="4">
         <v>4468</v>
       </c>
-      <c r="G204" s="3" t="s">
-        <v>10</v>
+      <c r="G204" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -12438,11 +12438,11 @@
       <c r="E205">
         <v>280</v>
       </c>
-      <c r="F205" s="4">
+      <c r="F205" s="2">
         <v>40</v>
       </c>
-      <c r="G205" s="5" t="s">
-        <v>17</v>
+      <c r="G205" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -12461,11 +12461,11 @@
       <c r="E206">
         <v>360</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="4">
         <v>3845</v>
       </c>
-      <c r="G206" s="3" t="s">
-        <v>10</v>
+      <c r="G206" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -12484,11 +12484,11 @@
       <c r="E207">
         <v>240</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="4">
         <v>2747</v>
       </c>
-      <c r="G207" s="3" t="s">
-        <v>10</v>
+      <c r="G207" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -12507,11 +12507,11 @@
       <c r="E208">
         <v>720</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="4">
         <v>4250</v>
       </c>
-      <c r="G208" s="3" t="s">
-        <v>10</v>
+      <c r="G208" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -12530,11 +12530,11 @@
       <c r="E209">
         <v>720</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="4">
         <v>5052</v>
       </c>
-      <c r="G209" s="3" t="s">
-        <v>10</v>
+      <c r="G209" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -12599,11 +12599,11 @@
       <c r="E212">
         <v>720</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="4">
         <v>3954</v>
       </c>
-      <c r="G212" s="3" t="s">
-        <v>10</v>
+      <c r="G212" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -12622,11 +12622,11 @@
       <c r="E213">
         <v>720</v>
       </c>
-      <c r="F213" s="4">
+      <c r="F213" s="2">
         <v>7</v>
       </c>
-      <c r="G213" s="5" t="s">
-        <v>17</v>
+      <c r="G213" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -12645,11 +12645,11 @@
       <c r="E214">
         <v>720</v>
       </c>
-      <c r="F214" s="4">
+      <c r="F214" s="2">
         <v>3222</v>
       </c>
-      <c r="G214" s="5" t="s">
-        <v>17</v>
+      <c r="G214" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -12668,11 +12668,11 @@
       <c r="E215">
         <v>600</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="4">
         <v>5347</v>
       </c>
-      <c r="G215" s="3" t="s">
-        <v>10</v>
+      <c r="G215" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -12691,11 +12691,11 @@
       <c r="E216">
         <v>5</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="4">
         <v>90</v>
       </c>
-      <c r="G216" s="3" t="s">
-        <v>10</v>
+      <c r="G216" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -12714,11 +12714,11 @@
       <c r="E217">
         <v>5</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="4">
         <v>384</v>
       </c>
-      <c r="G217" s="3" t="s">
-        <v>10</v>
+      <c r="G217" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -12737,11 +12737,11 @@
       <c r="E218">
         <v>5</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="4">
         <v>125</v>
       </c>
-      <c r="G218" s="3" t="s">
-        <v>10</v>
+      <c r="G218" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -12760,11 +12760,11 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="4">
+      <c r="F219" s="2">
         <v>1</v>
       </c>
-      <c r="G219" s="5" t="s">
-        <v>17</v>
+      <c r="G219" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -12806,11 +12806,11 @@
       <c r="E221">
         <v>10</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="4">
         <v>3242</v>
       </c>
-      <c r="G221" s="3" t="s">
-        <v>10</v>
+      <c r="G221" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -12829,11 +12829,11 @@
       <c r="E222">
         <v>10</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="4">
         <v>873</v>
       </c>
-      <c r="G222" s="3" t="s">
-        <v>10</v>
+      <c r="G222" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -12852,11 +12852,11 @@
       <c r="E223">
         <v>10</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="4">
         <v>2154</v>
       </c>
-      <c r="G223" s="3" t="s">
-        <v>10</v>
+      <c r="G223" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -12875,11 +12875,11 @@
       <c r="E224">
         <v>10</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="4">
         <v>1484</v>
       </c>
-      <c r="G224" s="3" t="s">
-        <v>10</v>
+      <c r="G224" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -12898,11 +12898,11 @@
       <c r="E225">
         <v>10</v>
       </c>
-      <c r="F225" s="4">
+      <c r="F225" s="2">
         <v>30</v>
       </c>
-      <c r="G225" s="5" t="s">
-        <v>17</v>
+      <c r="G225" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -12921,11 +12921,11 @@
       <c r="E226">
         <v>10</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="4">
         <v>1681</v>
       </c>
-      <c r="G226" s="3" t="s">
-        <v>10</v>
+      <c r="G226" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -12944,11 +12944,11 @@
       <c r="E227">
         <v>10</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="4">
         <v>206</v>
       </c>
-      <c r="G227" s="3" t="s">
-        <v>10</v>
+      <c r="G227" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -12990,11 +12990,11 @@
       <c r="E229">
         <v>10</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="4">
         <v>444</v>
       </c>
-      <c r="G229" s="3" t="s">
-        <v>10</v>
+      <c r="G229" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -13013,11 +13013,11 @@
       <c r="E230">
         <v>5</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="4">
         <v>566</v>
       </c>
-      <c r="G230" s="3" t="s">
-        <v>10</v>
+      <c r="G230" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -13059,11 +13059,11 @@
       <c r="E232">
         <v>5</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="4">
         <v>252</v>
       </c>
-      <c r="G232" s="3" t="s">
-        <v>10</v>
+      <c r="G232" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -13082,11 +13082,11 @@
       <c r="E233">
         <v>5</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="4">
         <v>170</v>
       </c>
-      <c r="G233" s="3" t="s">
-        <v>10</v>
+      <c r="G233" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="4">
+      <c r="F234" s="2">
         <v>1</v>
       </c>
-      <c r="G234" s="5" t="s">
-        <v>17</v>
+      <c r="G234" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13128,11 +13128,11 @@
       <c r="E235">
         <v>5</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="4">
         <v>290</v>
       </c>
-      <c r="G235" s="3" t="s">
-        <v>10</v>
+      <c r="G235" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -13151,11 +13151,11 @@
       <c r="E236">
         <v>5</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="4">
         <v>222</v>
       </c>
-      <c r="G236" s="3" t="s">
-        <v>10</v>
+      <c r="G236" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -13174,11 +13174,11 @@
       <c r="E237">
         <v>5</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="4">
         <v>256</v>
       </c>
-      <c r="G237" s="3" t="s">
-        <v>10</v>
+      <c r="G237" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -13197,11 +13197,11 @@
       <c r="E238">
         <v>5</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="4">
         <v>204</v>
       </c>
-      <c r="G238" s="3" t="s">
-        <v>10</v>
+      <c r="G238" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -13220,11 +13220,11 @@
       <c r="E239">
         <v>5</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="4">
         <v>262</v>
       </c>
-      <c r="G239" s="3" t="s">
-        <v>10</v>
+      <c r="G239" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -13243,11 +13243,11 @@
       <c r="E240">
         <v>5</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="4">
         <v>117</v>
       </c>
-      <c r="G240" s="3" t="s">
-        <v>10</v>
+      <c r="G240" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -13266,11 +13266,11 @@
       <c r="E241">
         <v>5</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="4">
         <v>1329</v>
       </c>
-      <c r="G241" s="3" t="s">
-        <v>10</v>
+      <c r="G241" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -13312,11 +13312,11 @@
       <c r="E243">
         <v>5</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="4">
         <v>155</v>
       </c>
-      <c r="G243" s="3" t="s">
-        <v>10</v>
+      <c r="G243" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -13335,11 +13335,11 @@
       <c r="E244">
         <v>5</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="4">
         <v>116</v>
       </c>
-      <c r="G244" s="3" t="s">
-        <v>10</v>
+      <c r="G244" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -13381,11 +13381,11 @@
       <c r="E246">
         <v>5</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="4">
         <v>91</v>
       </c>
-      <c r="G246" s="3" t="s">
-        <v>10</v>
+      <c r="G246" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -13404,11 +13404,11 @@
       <c r="E247">
         <v>5</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="4">
         <v>172</v>
       </c>
-      <c r="G247" s="3" t="s">
-        <v>10</v>
+      <c r="G247" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -13427,11 +13427,11 @@
       <c r="E248">
         <v>5</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="4">
         <v>32</v>
       </c>
-      <c r="G248" s="3" t="s">
-        <v>10</v>
+      <c r="G248" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -13473,11 +13473,11 @@
       <c r="E250">
         <v>5</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="4">
         <v>214</v>
       </c>
-      <c r="G250" s="3" t="s">
-        <v>10</v>
+      <c r="G250" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -13565,11 +13565,11 @@
       <c r="E254">
         <v>40</v>
       </c>
-      <c r="F254" s="4">
+      <c r="F254" s="2">
         <v>11</v>
       </c>
-      <c r="G254" s="5" t="s">
-        <v>17</v>
+      <c r="G254" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -13588,11 +13588,11 @@
       <c r="E255">
         <v>100</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="4">
         <v>197267</v>
       </c>
-      <c r="G255" s="3" t="s">
-        <v>10</v>
+      <c r="G255" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -13611,11 +13611,11 @@
       <c r="E256">
         <v>100</v>
       </c>
-      <c r="F256" s="2">
-        <v>89825</v>
-      </c>
-      <c r="G256" s="3" t="s">
-        <v>10</v>
+      <c r="F256" s="4">
+        <v>89725</v>
+      </c>
+      <c r="G256" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -13634,11 +13634,11 @@
       <c r="E257">
         <v>5</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="4">
         <v>606</v>
       </c>
-      <c r="G257" s="3" t="s">
-        <v>10</v>
+      <c r="G257" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -13657,11 +13657,11 @@
       <c r="E258">
         <v>5</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="4">
         <v>354</v>
       </c>
-      <c r="G258" s="3" t="s">
-        <v>10</v>
+      <c r="G258" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -13680,11 +13680,11 @@
       <c r="E259">
         <v>5</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="4">
         <v>88</v>
       </c>
-      <c r="G259" s="3" t="s">
-        <v>10</v>
+      <c r="G259" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -13703,11 +13703,11 @@
       <c r="E260">
         <v>5</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="4">
         <v>286</v>
       </c>
-      <c r="G260" s="3" t="s">
-        <v>10</v>
+      <c r="G260" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -13726,11 +13726,11 @@
       <c r="E261">
         <v>5</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="4">
         <v>71</v>
       </c>
-      <c r="G261" s="3" t="s">
-        <v>10</v>
+      <c r="G261" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -13749,11 +13749,11 @@
       <c r="E262">
         <v>5</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="4">
         <v>327</v>
       </c>
-      <c r="G262" s="3" t="s">
-        <v>10</v>
+      <c r="G262" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -13772,11 +13772,11 @@
       <c r="E263">
         <v>5</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="4">
         <v>238</v>
       </c>
-      <c r="G263" s="3" t="s">
-        <v>10</v>
+      <c r="G263" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -13795,11 +13795,11 @@
       <c r="E264">
         <v>5</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="4">
         <v>162</v>
       </c>
-      <c r="G264" s="3" t="s">
-        <v>10</v>
+      <c r="G264" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -13818,11 +13818,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="4">
         <v>26</v>
       </c>
-      <c r="G265" s="3" t="s">
-        <v>10</v>
+      <c r="G265" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -13841,11 +13841,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="4">
         <v>25</v>
       </c>
-      <c r="G266" s="3" t="s">
-        <v>10</v>
+      <c r="G266" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -13907,11 +13907,11 @@
       <c r="E2">
         <v>288</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>20464</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -13930,11 +13930,11 @@
       <c r="E3">
         <v>144</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>12</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>17</v>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -13976,11 +13976,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="2">
-        <v>1502</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>1262</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -13999,11 +13999,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>32</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14022,11 +14022,11 @@
       <c r="E7">
         <v>144</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>66009</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -14045,11 +14045,11 @@
       <c r="E8">
         <v>72</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>4589</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -14091,11 +14091,11 @@
       <c r="E10">
         <v>18</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>518</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -14114,11 +14114,11 @@
       <c r="E11">
         <v>144</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>44304</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -14137,11 +14137,11 @@
       <c r="E12">
         <v>144</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>8443</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -14160,11 +14160,11 @@
       <c r="E13">
         <v>144</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>498</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>17</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -14183,11 +14183,11 @@
       <c r="E14">
         <v>144</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>8391</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -14206,11 +14206,11 @@
       <c r="E15">
         <v>144</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>2994</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -14229,11 +14229,11 @@
       <c r="E16">
         <v>144</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>11098</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -14252,11 +14252,11 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="2">
-        <v>67724</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="F17" s="4">
+        <v>67628</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -14298,11 +14298,11 @@
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>2720</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -14367,11 +14367,11 @@
       <c r="E22">
         <v>12</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>4719</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -14390,11 +14390,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="4">
         <v>8140</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -14413,11 +14413,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>1</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>17</v>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -14436,11 +14436,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="4">
         <v>15983</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -14459,11 +14459,11 @@
       <c r="E26">
         <v>60</v>
       </c>
-      <c r="F26" s="2">
-        <v>30749</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="F26" s="4">
+        <v>30491</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -14482,11 +14482,11 @@
       <c r="E27">
         <v>60</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="4">
         <v>57676</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -14505,11 +14505,11 @@
       <c r="E28">
         <v>576</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="4">
         <v>28024</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -14528,11 +14528,11 @@
       <c r="E29">
         <v>576</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="4">
         <v>47198</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -14551,11 +14551,11 @@
       <c r="E30">
         <v>576</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>28635</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -14574,11 +14574,11 @@
       <c r="E31">
         <v>576</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="4">
         <v>9483</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -14597,11 +14597,11 @@
       <c r="E32">
         <v>576</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="4">
         <v>11690</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="G32" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -14620,11 +14620,11 @@
       <c r="E33">
         <v>576</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="4">
         <v>8001</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -14643,11 +14643,11 @@
       <c r="E34">
         <v>576</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="4">
         <v>46264</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="G34" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -14666,11 +14666,11 @@
       <c r="E35">
         <v>576</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>2302</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>17</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -14689,11 +14689,11 @@
       <c r="E36">
         <v>576</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="4">
         <v>54254</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -14712,11 +14712,11 @@
       <c r="E37">
         <v>576</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="2">
         <v>1457</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>17</v>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -14735,11 +14735,11 @@
       <c r="E38">
         <v>576</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>51</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>17</v>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -14758,11 +14758,11 @@
       <c r="E39">
         <v>576</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="4">
         <v>6404</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -14781,11 +14781,11 @@
       <c r="E40">
         <v>576</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="4">
         <v>39556</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14804,11 +14804,11 @@
       <c r="E41">
         <v>576</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>2846</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>17</v>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -14827,11 +14827,11 @@
       <c r="E42">
         <v>576</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>969</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>17</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -14873,11 +14873,11 @@
       <c r="E44">
         <v>576</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="2">
         <v>5</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>17</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -14896,11 +14896,11 @@
       <c r="E45">
         <v>72</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="4">
         <v>21839</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -14919,11 +14919,11 @@
       <c r="E46">
         <v>72</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="4">
         <v>2202</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -14942,11 +14942,11 @@
       <c r="E47">
         <v>288</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="4">
         <v>6214</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -14965,11 +14965,11 @@
       <c r="E48">
         <v>144</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="4">
         <v>36506</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -14988,11 +14988,11 @@
       <c r="E49">
         <v>36</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="4">
         <v>18305</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -15011,11 +15011,11 @@
       <c r="E50">
         <v>360</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="4">
         <v>8661</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -15034,11 +15034,11 @@
       <c r="E51">
         <v>360</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="4">
         <v>23432</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="G51" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -15057,11 +15057,11 @@
       <c r="E52">
         <v>360</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="4">
         <v>9527</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -15080,11 +15080,11 @@
       <c r="E53">
         <v>360</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="4">
         <v>39354</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="G53" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -15103,11 +15103,11 @@
       <c r="E54">
         <v>360</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="4">
         <v>40675</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -15126,11 +15126,11 @@
       <c r="E55">
         <v>360</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="4">
         <v>9021</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -15149,11 +15149,11 @@
       <c r="E56">
         <v>360</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="4">
         <v>30924</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -15172,11 +15172,11 @@
       <c r="E57">
         <v>360</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="4">
         <v>31870</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -15195,11 +15195,11 @@
       <c r="E58">
         <v>360</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="4">
         <v>34748</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -15218,11 +15218,11 @@
       <c r="E59">
         <v>12</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="4">
         <v>592</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -15264,11 +15264,11 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="4">
         <v>3471</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -15333,11 +15333,11 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="4">
         <v>2609</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -15356,11 +15356,11 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="2">
         <v>2</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>17</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -15517,11 +15517,11 @@
       <c r="E72">
         <v>144</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="4">
         <v>1039</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -15540,11 +15540,11 @@
       <c r="E73">
         <v>144</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="4">
         <v>924</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -15563,11 +15563,11 @@
       <c r="E74">
         <v>144</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>6934</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -15586,11 +15586,11 @@
       <c r="E75">
         <v>144</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="4">
         <v>1680</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="G75" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -15609,11 +15609,11 @@
       <c r="E76">
         <v>144</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="4">
         <v>4366</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -15632,11 +15632,11 @@
       <c r="E77">
         <v>144</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="4">
         <v>4195</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -15698,11 +15698,11 @@
       <c r="E2">
         <v>144</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>59341</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -15721,11 +15721,11 @@
       <c r="E3">
         <v>144</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>30793</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -15744,11 +15744,11 @@
       <c r="E4">
         <v>144</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>23981</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -15767,11 +15767,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>17</v>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -15813,11 +15813,11 @@
       <c r="E7">
         <v>144</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>13587</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -15836,11 +15836,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>2903</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -15859,11 +15859,11 @@
       <c r="E9">
         <v>144</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>10360</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -15882,11 +15882,11 @@
       <c r="E10">
         <v>288</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>7912</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -15905,11 +15905,11 @@
       <c r="E11">
         <v>144</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>4572</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -15928,11 +15928,11 @@
       <c r="E12">
         <v>144</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>8143</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -15951,11 +15951,11 @@
       <c r="E13">
         <v>144</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>7</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>17</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -15974,11 +15974,11 @@
       <c r="E14">
         <v>96</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>6719</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -15997,11 +15997,11 @@
       <c r="E15">
         <v>96</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>4523</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -16020,11 +16020,11 @@
       <c r="E16">
         <v>96</v>
       </c>
-      <c r="F16" s="2">
-        <v>9006</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="4">
+        <v>8994</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -16043,11 +16043,11 @@
       <c r="E17">
         <v>192</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>13585</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -16066,11 +16066,11 @@
       <c r="E18">
         <v>192</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>14112</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -16089,11 +16089,11 @@
       <c r="E19">
         <v>192</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>7055</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -16112,11 +16112,11 @@
       <c r="E20">
         <v>192</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>14112</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -16135,11 +16135,11 @@
       <c r="E21">
         <v>192</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>7814</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -16250,11 +16250,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="4">
         <v>11352</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -16273,11 +16273,11 @@
       <c r="E27">
         <v>192</v>
       </c>
-      <c r="F27" s="2">
-        <v>30075</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="F27" s="4">
+        <v>30069</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -16319,11 +16319,11 @@
       <c r="E29">
         <v>192</v>
       </c>
-      <c r="F29" s="2">
-        <v>10230</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>10224</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -16342,11 +16342,11 @@
       <c r="E30">
         <v>192</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>29923</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -16365,11 +16365,11 @@
       <c r="E31">
         <v>96</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="4">
         <v>7620</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -16388,11 +16388,11 @@
       <c r="E32">
         <v>72</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="4">
         <v>1057</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="G32" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -16411,11 +16411,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>713</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>17</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16434,11 +16434,11 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>146</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>17</v>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -16457,11 +16457,11 @@
       <c r="E35">
         <v>144</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>114</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>17</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -16480,11 +16480,11 @@
       <c r="E36">
         <v>72</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>30</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>17</v>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -16503,11 +16503,11 @@
       <c r="E37">
         <v>144</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="2">
         <v>50</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>17</v>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -16526,11 +16526,11 @@
       <c r="E38">
         <v>72</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>151</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>17</v>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -16549,11 +16549,11 @@
       <c r="E39">
         <v>144</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="4">
         <v>870</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -16572,11 +16572,11 @@
       <c r="E40">
         <v>72</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>167</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>17</v>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -16595,11 +16595,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>166</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>17</v>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16618,11 +16618,11 @@
       <c r="E42">
         <v>72</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>278</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>17</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16641,11 +16641,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="2">
         <v>253</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>17</v>
+      <c r="G43" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -16687,11 +16687,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>126</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>17</v>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -16710,11 +16710,11 @@
       <c r="E46">
         <v>72</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="4">
         <v>877</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -16733,11 +16733,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="4">
         <v>1256</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -16756,11 +16756,11 @@
       <c r="E48">
         <v>96</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="4">
         <v>15257</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -16779,11 +16779,11 @@
       <c r="E49">
         <v>96</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="4">
         <v>11401</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -16802,11 +16802,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="4">
         <v>11542</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -16825,11 +16825,11 @@
       <c r="E51">
         <v>192</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="4">
         <v>8998</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="G51" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -16848,11 +16848,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>239</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>17</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -16871,11 +16871,11 @@
       <c r="E53">
         <v>96</v>
       </c>
-      <c r="F53" s="2">
-        <v>5931</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="F53" s="4">
+        <v>5919</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -16894,11 +16894,11 @@
       <c r="E54">
         <v>96</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="4">
         <v>2923</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -16917,11 +16917,11 @@
       <c r="E55">
         <v>96</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="4">
         <v>15269</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -16940,11 +16940,11 @@
       <c r="E56">
         <v>96</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="4">
         <v>23226</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -16963,11 +16963,11 @@
       <c r="E57">
         <v>96</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="4">
         <v>21705</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -16986,11 +16986,11 @@
       <c r="E58">
         <v>96</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="4">
         <v>2479</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -17009,11 +17009,11 @@
       <c r="E59">
         <v>48</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="4">
         <v>5544</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -17032,11 +17032,11 @@
       <c r="E60">
         <v>48</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="4">
         <v>4903</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -17078,11 +17078,11 @@
       <c r="E62">
         <v>576</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="4">
         <v>13760</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="G62" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -17101,11 +17101,11 @@
       <c r="E63">
         <v>576</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="4">
         <v>3554</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="G63" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -17147,11 +17147,11 @@
       <c r="E65">
         <v>200</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="2">
         <v>1</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>17</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -17170,11 +17170,11 @@
       <c r="E66">
         <v>200</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>268</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>17</v>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -17193,11 +17193,11 @@
       <c r="E67">
         <v>200</v>
       </c>
-      <c r="F67" s="2">
-        <v>25764</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>25714</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -17216,11 +17216,11 @@
       <c r="E68">
         <v>200</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="2">
         <v>2</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>17</v>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -17239,11 +17239,11 @@
       <c r="E69">
         <v>200</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="4">
         <v>22498</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="G69" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -17262,11 +17262,11 @@
       <c r="E70">
         <v>200</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="2">
         <v>63</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>17</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -17285,11 +17285,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="2">
         <v>236</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>17</v>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17308,11 +17308,11 @@
       <c r="E72">
         <v>200</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="2">
         <v>4</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>17</v>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -17354,11 +17354,11 @@
       <c r="E74">
         <v>200</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>28</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>17</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -17377,11 +17377,11 @@
       <c r="E75">
         <v>200</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="2">
         <v>200</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>17</v>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -17400,11 +17400,11 @@
       <c r="E76">
         <v>200</v>
       </c>
-      <c r="F76" s="2">
-        <v>43096</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="F76" s="4">
+        <v>42696</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -17469,11 +17469,11 @@
       <c r="E79">
         <v>200</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="4">
         <v>1313</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="G79" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17492,11 +17492,11 @@
       <c r="E80">
         <v>200</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="2">
         <v>1</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>17</v>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -17538,11 +17538,11 @@
       <c r="E82">
         <v>1152</v>
       </c>
-      <c r="F82" s="4">
-        <v>504</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>17</v>
+      <c r="F82" s="2">
+        <v>528</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -17561,11 +17561,11 @@
       <c r="E83">
         <v>1152</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="2">
         <v>71</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>17</v>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -17607,11 +17607,11 @@
       <c r="E85">
         <v>1152</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="2">
         <v>2736</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>17</v>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -17630,11 +17630,11 @@
       <c r="E86">
         <v>576</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="4">
         <v>4976</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -17676,11 +17676,11 @@
       <c r="E88">
         <v>576</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="4">
         <v>3548</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17699,11 +17699,11 @@
       <c r="E89">
         <v>576</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="2">
         <v>111</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>17</v>
+      <c r="G89" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -17722,11 +17722,11 @@
       <c r="E90">
         <v>576</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="2">
         <v>532</v>
       </c>
-      <c r="G90" s="5" t="s">
-        <v>17</v>
+      <c r="G90" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -17745,11 +17745,11 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="2">
         <v>2763</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>17</v>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -17768,11 +17768,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="2">
         <v>863</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>17</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -17791,11 +17791,11 @@
       <c r="E93">
         <v>576</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="4">
         <v>12790</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="G93" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -17814,11 +17814,11 @@
       <c r="E94">
         <v>576</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="2">
         <v>2</v>
       </c>
-      <c r="G94" s="5" t="s">
-        <v>17</v>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -17860,11 +17860,11 @@
       <c r="E96">
         <v>144</v>
       </c>
-      <c r="F96" s="2">
-        <v>171780</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="F96" s="4">
+        <v>171751</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -17906,11 +17906,11 @@
       <c r="E98">
         <v>144</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="2">
         <v>2</v>
       </c>
-      <c r="G98" s="5" t="s">
-        <v>17</v>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -17952,11 +17952,11 @@
       <c r="E100">
         <v>144</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="4">
         <v>15720</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>10</v>
+      <c r="G100" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -17975,11 +17975,11 @@
       <c r="E101">
         <v>144</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="2">
         <v>2</v>
       </c>
-      <c r="G101" s="5" t="s">
-        <v>17</v>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -17998,11 +17998,11 @@
       <c r="E102">
         <v>144</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="4">
         <v>17342</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>10</v>
+      <c r="G102" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -18021,11 +18021,11 @@
       <c r="E103">
         <v>144</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="4">
         <v>15828</v>
       </c>
-      <c r="G103" s="3" t="s">
-        <v>10</v>
+      <c r="G103" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -18044,11 +18044,11 @@
       <c r="E104">
         <v>144</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="4">
         <v>5802</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="G104" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -18067,11 +18067,11 @@
       <c r="E105">
         <v>144</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="4">
         <v>6610</v>
       </c>
-      <c r="G105" s="3" t="s">
-        <v>10</v>
+      <c r="G105" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -18090,11 +18090,11 @@
       <c r="E106">
         <v>144</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="2">
         <v>299</v>
       </c>
-      <c r="G106" s="5" t="s">
-        <v>17</v>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -18113,11 +18113,11 @@
       <c r="E107">
         <v>144</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="4">
         <v>17670</v>
       </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="G107" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -18136,11 +18136,11 @@
       <c r="E108">
         <v>144</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="4">
         <v>3966</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="G108" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -18159,11 +18159,11 @@
       <c r="E109">
         <v>192</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="4">
         <v>13629</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="G109" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -18182,11 +18182,11 @@
       <c r="E110">
         <v>192</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="4">
         <v>1359</v>
       </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="G110" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -18205,11 +18205,11 @@
       <c r="E111">
         <v>192</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="4">
         <v>18571</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="G111" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -18228,11 +18228,11 @@
       <c r="E112">
         <v>192</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="4">
         <v>4391</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="G112" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -18251,11 +18251,11 @@
       <c r="E113">
         <v>192</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="4">
         <v>24801</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="G113" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -18274,11 +18274,11 @@
       <c r="E114">
         <v>192</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="4">
         <v>6541</v>
       </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="G114" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -18297,11 +18297,11 @@
       <c r="E115">
         <v>192</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="4">
         <v>15354</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="G115" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -18320,11 +18320,11 @@
       <c r="E116">
         <v>192</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="2">
         <v>46</v>
       </c>
-      <c r="G116" s="5" t="s">
-        <v>17</v>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -18343,11 +18343,11 @@
       <c r="E117">
         <v>192</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="2">
         <v>63</v>
       </c>
-      <c r="G117" s="5" t="s">
-        <v>17</v>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -18366,11 +18366,11 @@
       <c r="E118">
         <v>192</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="4">
         <v>2867</v>
       </c>
-      <c r="G118" s="3" t="s">
-        <v>10</v>
+      <c r="G118" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -18412,11 +18412,11 @@
       <c r="E120">
         <v>192</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>212</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>17</v>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -18435,11 +18435,11 @@
       <c r="E121">
         <v>192</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="2">
         <v>137</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>17</v>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -18458,11 +18458,11 @@
       <c r="E122">
         <v>192</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="4">
         <v>1954</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="G122" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -18481,11 +18481,11 @@
       <c r="E123">
         <v>192</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="4">
         <v>4010</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="G123" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -18504,11 +18504,11 @@
       <c r="E124">
         <v>192</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="4">
         <v>1674</v>
       </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="G124" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -18527,11 +18527,11 @@
       <c r="E125">
         <v>192</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="4">
         <v>6331</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="G125" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -18550,11 +18550,11 @@
       <c r="E126">
         <v>192</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="4">
         <v>1714</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="G126" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -18573,11 +18573,11 @@
       <c r="E127">
         <v>192</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="4">
         <v>10781</v>
       </c>
-      <c r="G127" s="3" t="s">
-        <v>10</v>
+      <c r="G127" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -18596,11 +18596,11 @@
       <c r="E128">
         <v>192</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="4">
         <v>8737</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="G128" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -18619,11 +18619,11 @@
       <c r="E129">
         <v>192</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="4">
         <v>3244</v>
       </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="G129" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -18642,11 +18642,11 @@
       <c r="E130">
         <v>192</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="4">
         <v>43731</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="G130" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -18665,11 +18665,11 @@
       <c r="E131">
         <v>192</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="2">
         <v>287</v>
       </c>
-      <c r="G131" s="5" t="s">
-        <v>17</v>
+      <c r="G131" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -18688,11 +18688,11 @@
       <c r="E132">
         <v>192</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="4">
         <v>8436</v>
       </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="G132" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -18711,11 +18711,11 @@
       <c r="E133">
         <v>192</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="2">
         <v>185</v>
       </c>
-      <c r="G133" s="5" t="s">
-        <v>17</v>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -18734,11 +18734,11 @@
       <c r="E134">
         <v>192</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="4">
         <v>6726</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="G134" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -18757,11 +18757,11 @@
       <c r="E135">
         <v>192</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="4">
         <v>12048</v>
       </c>
-      <c r="G135" s="3" t="s">
-        <v>10</v>
+      <c r="G135" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -18780,11 +18780,11 @@
       <c r="E136">
         <v>192</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="4">
         <v>2895</v>
       </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="G136" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -18803,11 +18803,11 @@
       <c r="E137">
         <v>192</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="2">
         <v>108</v>
       </c>
-      <c r="G137" s="5" t="s">
-        <v>17</v>
+      <c r="G137" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -18826,11 +18826,11 @@
       <c r="E138">
         <v>192</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="2">
         <v>99</v>
       </c>
-      <c r="G138" s="5" t="s">
-        <v>17</v>
+      <c r="G138" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -18849,11 +18849,11 @@
       <c r="E139">
         <v>192</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="2">
         <v>125</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>17</v>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -18872,11 +18872,11 @@
       <c r="E140">
         <v>192</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="2">
         <v>17</v>
       </c>
-      <c r="G140" s="5" t="s">
-        <v>17</v>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -18895,11 +18895,11 @@
       <c r="E141">
         <v>192</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="2">
         <v>114</v>
       </c>
-      <c r="G141" s="5" t="s">
-        <v>17</v>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -18918,11 +18918,11 @@
       <c r="E142">
         <v>192</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="2">
         <v>122</v>
       </c>
-      <c r="G142" s="5" t="s">
-        <v>17</v>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -18941,11 +18941,11 @@
       <c r="E143">
         <v>192</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="2">
         <v>42</v>
       </c>
-      <c r="G143" s="5" t="s">
-        <v>17</v>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -18964,11 +18964,11 @@
       <c r="E144">
         <v>192</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="2">
         <v>66</v>
       </c>
-      <c r="G144" s="5" t="s">
-        <v>17</v>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -19076,11 +19076,11 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>10117</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -19099,11 +19099,11 @@
       <c r="E5">
         <v>144</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>24475</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -19122,11 +19122,11 @@
       <c r="E6">
         <v>144</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>7099</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -19168,11 +19168,11 @@
       <c r="E8">
         <v>144</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>17217</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -19191,11 +19191,11 @@
       <c r="E9">
         <v>72</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>7876</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -19214,11 +19214,11 @@
       <c r="E10">
         <v>120</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>11163</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -19237,11 +19237,11 @@
       <c r="E11">
         <v>30</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>12365</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -19260,11 +19260,11 @@
       <c r="E12">
         <v>36</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>3135</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -19306,11 +19306,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>2047</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -19329,11 +19329,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>84</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>17</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -19352,11 +19352,11 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>24</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>17</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -19421,11 +19421,11 @@
       <c r="E19">
         <v>20</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>3775</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -19444,11 +19444,11 @@
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>5038</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -19467,11 +19467,11 @@
       <c r="E21">
         <v>40</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>35251</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -19490,11 +19490,11 @@
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>15438</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -19513,11 +19513,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>4</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>17</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -19536,11 +19536,11 @@
       <c r="E24">
         <v>60</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="4">
         <v>2769</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -19559,11 +19559,11 @@
       <c r="E25">
         <v>36</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="4">
         <v>12681</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -19582,11 +19582,11 @@
       <c r="E26">
         <v>36</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="4">
         <v>5180</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -19628,11 +19628,11 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="4">
         <v>2762</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -19651,11 +19651,11 @@
       <c r="E29">
         <v>36</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="4">
         <v>4798</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -19674,11 +19674,11 @@
       <c r="E30">
         <v>48</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>5814</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -19697,11 +19697,11 @@
       <c r="E31">
         <v>144</v>
       </c>
-      <c r="F31" s="2">
-        <v>106145</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="F31" s="4">
+        <v>106115</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -19720,11 +19720,11 @@
       <c r="E32">
         <v>120</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>2</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>17</v>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -19743,11 +19743,11 @@
       <c r="E33">
         <v>120</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>17</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>17</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -19766,11 +19766,11 @@
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="4">
         <v>12254</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="G34" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -19812,11 +19812,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="4">
         <v>8821</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -19858,11 +19858,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="4">
         <v>83915</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -19881,11 +19881,11 @@
       <c r="E39">
         <v>120</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="4">
         <v>15138</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -19904,11 +19904,11 @@
       <c r="E40">
         <v>120</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>17</v>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -19950,11 +19950,11 @@
       <c r="E42">
         <v>144</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="4">
         <v>10317</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -19973,11 +19973,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="4">
         <v>8038</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>10</v>
+      <c r="G43" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -19996,11 +19996,11 @@
       <c r="E44">
         <v>144</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="4">
         <v>9043</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -20019,11 +20019,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="4">
         <v>9157</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -20042,11 +20042,11 @@
       <c r="E46">
         <v>144</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="4">
         <v>6335</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -20065,11 +20065,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>7</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>17</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -20088,11 +20088,11 @@
       <c r="E48">
         <v>144</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="4">
         <v>7831</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -20111,11 +20111,11 @@
       <c r="E49">
         <v>144</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="4">
         <v>13343</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -20134,11 +20134,11 @@
       <c r="E50">
         <v>144</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>17</v>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20180,11 +20180,11 @@
       <c r="E52">
         <v>144</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>48</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>17</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -20203,11 +20203,11 @@
       <c r="E53">
         <v>144</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="4">
         <v>5454</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="G53" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -20272,11 +20272,11 @@
       <c r="E56">
         <v>144</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>40</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>17</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -20341,11 +20341,11 @@
       <c r="E59">
         <v>144</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="4">
         <v>4299</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -20364,11 +20364,11 @@
       <c r="E60">
         <v>144</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="4">
         <v>2968</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -20387,11 +20387,11 @@
       <c r="E61">
         <v>96</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="4">
         <v>2482</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -20433,11 +20433,11 @@
       <c r="E63">
         <v>120</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="4">
         <v>803</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="G63" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -20479,11 +20479,11 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="2">
         <v>1</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>17</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -20502,11 +20502,11 @@
       <c r="E66">
         <v>12</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>413</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -20525,11 +20525,11 @@
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="4">
         <v>366</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -20548,11 +20548,11 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="4">
         <v>81</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20571,11 +20571,11 @@
       <c r="E69">
         <v>12</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="4">
         <v>660</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="G69" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -20594,11 +20594,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="4">
         <v>102</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -20663,11 +20663,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="4">
         <v>5451</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -20686,11 +20686,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>2</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>17</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -20709,11 +20709,11 @@
       <c r="E75">
         <v>240</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="2">
         <v>12</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>17</v>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -20732,11 +20732,11 @@
       <c r="E76">
         <v>180</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="2">
         <v>4</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>17</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -20755,11 +20755,11 @@
       <c r="E77">
         <v>144</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="4">
         <v>18903</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -20778,11 +20778,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="2">
         <v>2</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>17</v>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20801,11 +20801,11 @@
       <c r="E79">
         <v>144</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="2">
         <v>10</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>17</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -20870,11 +20870,11 @@
       <c r="E82">
         <v>144</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="2">
         <v>72</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>17</v>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -20893,11 +20893,11 @@
       <c r="E83">
         <v>144</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="4">
         <v>7450</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -20916,11 +20916,11 @@
       <c r="E84">
         <v>144</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="4">
         <v>43222</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="G84" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -20962,11 +20962,11 @@
       <c r="E86">
         <v>144</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="4">
         <v>21493</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -21008,11 +21008,11 @@
       <c r="E88">
         <v>144</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="4">
         <v>8070</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -21031,11 +21031,11 @@
       <c r="E89">
         <v>144</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="4">
         <v>6105</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>10</v>
+      <c r="G89" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -21054,11 +21054,11 @@
       <c r="E90">
         <v>144</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="4">
         <v>7492</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="G90" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -21077,11 +21077,11 @@
       <c r="E91">
         <v>144</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="4">
         <v>7743</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="G91" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -21100,11 +21100,11 @@
       <c r="E92">
         <v>144</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="2">
         <v>4</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>17</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -21123,11 +21123,11 @@
       <c r="E93">
         <v>144</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="4">
         <v>11800</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="G93" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -21192,11 +21192,11 @@
       <c r="E96">
         <v>144</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="4">
         <v>29673</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -21258,11 +21258,11 @@
       <c r="E2">
         <v>72</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>110554</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21281,11 +21281,11 @@
       <c r="E3">
         <v>72</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>190869</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21304,11 +21304,11 @@
       <c r="E4">
         <v>72</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>63969</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21327,11 +21327,11 @@
       <c r="E5">
         <v>72</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>24243</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -21393,11 +21393,11 @@
       <c r="E2">
         <v>12</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>1237</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -21416,11 +21416,11 @@
       <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>1411</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21439,11 +21439,11 @@
       <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>1018</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21462,11 +21462,11 @@
       <c r="E5">
         <v>12</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>671</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -21485,11 +21485,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>603</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -21508,11 +21508,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>309</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -21531,11 +21531,11 @@
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>811</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -21554,11 +21554,11 @@
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>623</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -21577,11 +21577,11 @@
       <c r="E10">
         <v>48</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>2024</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -21600,11 +21600,11 @@
       <c r="E11">
         <v>48</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>2257</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -21623,11 +21623,11 @@
       <c r="E12">
         <v>48</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>2944</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -21646,11 +21646,11 @@
       <c r="E13">
         <v>48</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>1832</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -21669,11 +21669,11 @@
       <c r="E14">
         <v>24</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>330</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -21692,11 +21692,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>535</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -21715,11 +21715,11 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>1170</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -21738,11 +21738,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>1161</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -21761,11 +21761,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>319</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -21784,11 +21784,11 @@
       <c r="E19">
         <v>6</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>61</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -21807,11 +21807,11 @@
       <c r="E20">
         <v>24</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>1150</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -21830,11 +21830,11 @@
       <c r="E21">
         <v>24</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>1296</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -21853,11 +21853,11 @@
       <c r="E22">
         <v>24</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>1253</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -21876,11 +21876,11 @@
       <c r="E23">
         <v>24</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="4">
         <v>1093</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -21899,11 +21899,11 @@
       <c r="E24">
         <v>24</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="4">
         <v>474</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -21922,11 +21922,11 @@
       <c r="E25">
         <v>24</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="4">
         <v>344</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -21945,11 +21945,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="4">
         <v>189</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -21968,11 +21968,11 @@
       <c r="E27">
         <v>24</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="4">
         <v>187</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -21991,11 +21991,11 @@
       <c r="E28">
         <v>12</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="4">
         <v>567</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -22014,11 +22014,11 @@
       <c r="E29">
         <v>12</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="4">
         <v>502</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -22037,11 +22037,11 @@
       <c r="E30">
         <v>12</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>363</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -22060,11 +22060,11 @@
       <c r="E31">
         <v>12</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="4">
         <v>255</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>10</v>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -22083,11 +22083,11 @@
       <c r="E32">
         <v>48</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>2</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>17</v>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -22149,11 +22149,11 @@
       <c r="E2">
         <v>288</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>8347</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22172,11 +22172,11 @@
       <c r="E3">
         <v>384</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>19747</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -22195,11 +22195,11 @@
       <c r="E4">
         <v>384</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>19753</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22218,11 +22218,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>48313</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -22241,11 +22241,11 @@
       <c r="E6">
         <v>384</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>81337</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22264,11 +22264,11 @@
       <c r="E7">
         <v>384</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>47692</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -22310,11 +22310,11 @@
       <c r="E9">
         <v>144</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>23132</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -22333,11 +22333,11 @@
       <c r="E10">
         <v>36</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>12</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>17</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -22379,11 +22379,11 @@
       <c r="E12">
         <v>192</v>
       </c>
-      <c r="F12" s="2">
-        <v>14791</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>14533</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -22402,11 +22402,11 @@
       <c r="E13">
         <v>576</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>74919</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -22425,11 +22425,11 @@
       <c r="E14">
         <v>12</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>87772</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22448,11 +22448,11 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>34722</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -22471,11 +22471,11 @@
       <c r="E16">
         <v>48</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>22312</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -22517,11 +22517,11 @@
       <c r="E18">
         <v>144</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>12635</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -22540,11 +22540,11 @@
       <c r="E19">
         <v>144</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>2479</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -22563,11 +22563,11 @@
       <c r="E20">
         <v>144</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>16339</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -22609,11 +22609,11 @@
       <c r="E22">
         <v>144</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>13658</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -22721,11 +22721,11 @@
       <c r="E4">
         <v>1000</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>917</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22744,11 +22744,11 @@
       <c r="E5">
         <v>500</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>4141</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -22767,11 +22767,11 @@
       <c r="E6">
         <v>500</v>
       </c>
-      <c r="F6" s="4">
-        <v>139</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
+      <c r="F6" s="2">
+        <v>89</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22790,11 +22790,11 @@
       <c r="E7">
         <v>500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>3528</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -22836,11 +22836,11 @@
       <c r="E9">
         <v>200</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>8887</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -22905,11 +22905,11 @@
       <c r="E12">
         <v>500</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>10957</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -22928,11 +22928,11 @@
       <c r="E13">
         <v>500</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>5</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>17</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -22951,11 +22951,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>10</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>17</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22974,11 +22974,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>8</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>17</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -22997,11 +22997,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>2</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>17</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -23020,11 +23020,11 @@
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>2078</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/reports/StockPulse_ESCOLAR.xlsx
+++ b/reports/StockPulse_ESCOLAR.xlsx
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="4">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="4">
-        <v>4589</v>
+        <v>4588</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="4">
-        <v>67628</v>
+        <v>67627</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>14</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="4">
-        <v>36506</v>
+        <v>36505</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>14</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="4">
-        <v>18305</v>
+        <v>18304</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>14</v>
@@ -15219,7 +15219,7 @@
         <v>12</v>
       </c>
       <c r="F59" s="4">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>14</v>
@@ -15265,7 +15265,7 @@
         <v>12</v>
       </c>
       <c r="F61" s="4">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>14</v>
@@ -17010,7 +17010,7 @@
         <v>48</v>
       </c>
       <c r="F59" s="4">
-        <v>5544</v>
+        <v>5543</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>14</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="4">
-        <v>171751</v>
+        <v>171750</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>14</v>
@@ -18321,7 +18321,7 @@
         <v>192</v>
       </c>
       <c r="F116" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -18482,7 +18482,7 @@
         <v>192</v>
       </c>
       <c r="F123" s="4">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>87772</v>
+        <v>87771</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
